--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B526"/>
+  <dimension ref="A1:B528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1717,7 +1717,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare Noir</t>
+          <t>Donner Go ampli guitare - Donner Go【Noir】</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -1727,137 +1727,137 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
+          <t>Donner Go ampli guitare - Donner Go II【Noir】</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>69.98999999999999</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>【Donner】Pour la différence de prix</t>
+          <t>Donner Go ampli guitare - Donner Go II【Blanc】</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>180</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>469.99</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>【Donner】Pour la différence de prix</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>539.98</v>
+        <v>180</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>559.98</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>579.98</v>
+        <v>539.98</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>399.99</v>
+        <v>559.98</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>485.98</v>
+        <v>579.98</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>489.98</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>509.98</v>
+        <v>485.98</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>159.99</v>
+        <v>489.98</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>209.99</v>
+        <v>509.98</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
+          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>209.99</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -1867,7 +1867,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -1877,117 +1877,117 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 4 Cymbales</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>499.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - Nouvelle 5 Tambours et 4 Cymbales</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>599.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 3 Cymbales</t>
+          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 4 Cymbales</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>589.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Donner Beat Go Kit de batterie électronique portable</t>
+          <t>Donner DED-200X Batterie Électronique - Nouvelle 5 Tambours et 4 Cymbales</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>289.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
+          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 3 Cymbales</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>119.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
+          <t>Donner Beat Go Kit de batterie électronique portable</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>119.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Donner Table de percussion</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>39.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>599.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>Donner Table de percussion</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>699.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>699.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>599.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -1997,637 +1997,637 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>699.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Bleu clair</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>69.98999999999999</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Rose clair</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>69.98999999999999</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Bleu clair</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Bleu clair</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>89.98999999999999</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Rose clair</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Rose clair</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>89.98999999999999</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Bleu clair</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>269.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Rose clair</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>149.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
+          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>129.99</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
+          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>339.99</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
+          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>479.98</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>479.98</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>499.98</v>
+        <v>479.98</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>539.97</v>
+        <v>479.98</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>539.97</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>559.97</v>
+        <v>539.97</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>519.98</v>
+        <v>539.97</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>829.99</v>
+        <v>559.97</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>909.98</v>
+        <v>519.98</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>925.98</v>
+        <v>829.99</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>899.98</v>
+        <v>909.98</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>979.97</v>
+        <v>925.98</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>995.97</v>
+        <v>899.98</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Eastar EDA-100 Digital Aerophone Noir</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>122.99</v>
+        <v>979.97</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>299.99</v>
+        <v>995.97</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
+          <t>Eastar EDA-100 Digital Aerophone Noir</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>418.99</v>
+        <v>122.99</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>419.98</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>369.98</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>369.98</v>
+        <v>419.98</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>279.99</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>418.99</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>419.98</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>369.98</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>369.98</v>
+        <v>419.98</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>299.99</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>398.99</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>399.98</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>352.98</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>352.98</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>299.99</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>398.99</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>399.98</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>352.98</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>352.98</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>99.98999999999999</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>99.98999999999999</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
+          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>126.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
+          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>62.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
+          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>59.99</v>
+        <v>126.99</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
+          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>56.99</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Donner DK-10S 61 Touches Clavier Électronique - clavier électronique</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>139.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Donner DK-10S 61 Touches Clavier Électronique - Clavier + Banc X-Style</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>219.98</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Donner DK-10S 61 Touches Clavier Électronique - Clavier + Banc de Piano</t>
+          <t>Donner DK-10S 61 Touches Clavier Électronique - clavier électronique</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>219.98</v>
+        <v>139.99</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
+          <t>Donner DK-10S 61 Touches Clavier Électronique - Clavier + Banc X-Style</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>119.99</v>
+        <v>219.98</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>Donner DK-10S 61 Touches Clavier Électronique - Clavier + Banc de Piano</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>284.99</v>
+        <v>219.98</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>284.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable Confort</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>115.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Donner M100 Casque de monitoring studio</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>59.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano</t>
+          <t>Donner Banquette Piano Duo Réglable Confort</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>229.99</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
+          <t>Donner M100 Casque de monitoring studio</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>359.98</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
+          <t>Donner DEP-08 Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>359.98</v>
+        <v>229.99</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>199.99</v>
+        <v>359.98</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>299.98</v>
+        <v>359.98</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>299.98</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -2637,107 +2637,107 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>367.97</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>392.97</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie Electronique</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>199.99</v>
+        <v>367.97</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Noir</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>219.99</v>
+        <v>392.97</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Blanc</t>
+          <t>Donner DED-70 Batterie Electronique</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>219.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - L1</t>
+          <t>Donner DED-80 Batterie électrique - Noir</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>279.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>Donner DED-80 Batterie électrique - Blanc</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>119.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - Pack</t>
+          <t>Donner Essential L1 Synthétiseur - L1</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>399.98</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>799.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
+          <t>Donner Essential L1 Synthétiseur - Pack</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>799.99</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -2747,157 +2747,157 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>102.99</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>409.99</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
+          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>498.99</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>499.98</v>
+        <v>409.99</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>409.99</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>498.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>499.98</v>
+        <v>409.99</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>399.99</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>498.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>499.98</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>399.99</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>474.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>499.98</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>899.99</v>
+        <v>474.99</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>899.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -2907,7 +2907,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -2917,7 +2917,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -2927,7 +2927,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -2937,337 +2937,337 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>109.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>359.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>446.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>549.98</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>584.99</v>
+        <v>446.99</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>359.99</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>446.99</v>
+        <v>584.99</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>549.98</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>584.99</v>
+        <v>446.99</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Donner DED-300X Batterie Electronique</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>539.99</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>130.99</v>
+        <v>584.99</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
+          <t>Donner DED-300X Batterie Electronique</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>129.99</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>659.99</v>
+        <v>130.99</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>782.98</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>765.98</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>842.97</v>
+        <v>782.98</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>825.97</v>
+        <v>765.98</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>785.98</v>
+        <v>842.97</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>801.98</v>
+        <v>825.97</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>659.99</v>
+        <v>785.98</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>765.98</v>
+        <v>801.98</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>765.98</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>825.97</v>
+        <v>765.98</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>825.97</v>
+        <v>765.98</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>785.98</v>
+        <v>825.97</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>801.98</v>
+        <v>825.97</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>102.99</v>
+        <v>785.98</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>92.98999999999999</v>
+        <v>801.98</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
+          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>109.99</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>99</v>
+        <v>92.98999999999999</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Donner DT-50 Tabouret de Batterie</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>72.98999999999999</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Bleu</t>
+          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>169.99</v>
+        <v>99</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
+          <t>Donner DT-50 Tabouret de Batterie</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>199.99</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Blanc</t>
+          <t>Donner DST-550 Guitare Électrique - Bleu</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -3277,1737 +3277,1737 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
+          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>289.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
+          <t>Donner DST-550 Guitare Électrique - Blanc</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>379.98</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>279.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>409.98</v>
+        <v>379.98</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>389.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>495.98</v>
+        <v>409.98</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>519.98</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>389.99</v>
+        <v>495.98</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>479.98</v>
+        <v>519.98</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>519.98</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>209.99</v>
+        <v>479.98</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>284.99</v>
+        <v>519.98</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>315.98</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>309.98</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>359.97</v>
+        <v>315.98</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>385.97</v>
+        <v>309.98</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>379.97</v>
+        <v>359.97</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>319.98</v>
+        <v>385.97</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>389.97</v>
+        <v>379.97</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>179.99</v>
+        <v>319.98</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>259.98</v>
+        <v>389.97</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>267.98</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>276.98</v>
+        <v>259.98</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>319.97</v>
+        <v>267.98</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>327.97</v>
+        <v>276.98</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>336.97</v>
+        <v>319.97</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>279.98</v>
+        <v>327.97</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>339.97</v>
+        <v>336.97</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>189.99</v>
+        <v>279.98</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>265.98</v>
+        <v>339.97</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>273.98</v>
+        <v>189.99</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>282.98</v>
+        <v>265.98</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>335.97</v>
+        <v>273.98</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>343.97</v>
+        <v>282.98</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>352.97</v>
+        <v>335.97</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>285.98</v>
+        <v>343.97</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>355.97</v>
+        <v>352.97</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>209.99</v>
+        <v>285.98</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>289.98</v>
+        <v>355.97</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>315.98</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>309.98</v>
+        <v>289.98</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>359.97</v>
+        <v>315.98</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>385.97</v>
+        <v>309.98</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>379.97</v>
+        <v>359.97</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>319.98</v>
+        <v>385.97</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>389.97</v>
+        <v>379.97</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>169.99</v>
+        <v>319.98</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>239.98</v>
+        <v>389.97</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>359.99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>559.99</v>
+        <v>239.98</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>458.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>309.99</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>559.99</v>
+        <v>458.99</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>458.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>359.99</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>559.99</v>
+        <v>458.99</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>458.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>359.99</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>559.99</v>
+        <v>458.99</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>458.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>309.99</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>559.99</v>
+        <v>458.99</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>458.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>309.99</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>559.99</v>
+        <v>458.99</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>458.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Donner DED-200 Max Batteries Electroniques</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>499.99</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>1099.99</v>
+        <v>458.99</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
+          <t>Donner DED-200 Max Batteries Electroniques</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>1114.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>899</v>
+        <v>1099.99</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>995.99</v>
+        <v>1114.99</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>998.99</v>
+        <v>899</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>125.99</v>
+        <v>995.99</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>166.99</v>
+        <v>998.99</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>299.99</v>
+        <v>125.99</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>536.98</v>
+        <v>166.99</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>448.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>299.99</v>
+        <v>536.98</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>536.98</v>
+        <v>448.99</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>448.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>299.99</v>
+        <v>536.98</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>536.98</v>
+        <v>448.99</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>448.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>299.99</v>
+        <v>536.98</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>536.98</v>
+        <v>448.99</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>448.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>109.99</v>
+        <v>536.98</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>319.99</v>
+        <v>448.99</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>408.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>425.98</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>417.98</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>429.98</v>
+        <v>425.98</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>489.97</v>
+        <v>417.98</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>445.98</v>
+        <v>429.98</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>505.97</v>
+        <v>489.97</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>449.98</v>
+        <v>445.98</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>329.99</v>
+        <v>505.97</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>428.98</v>
+        <v>449.98</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>425.98</v>
+        <v>329.99</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>417.98</v>
+        <v>428.98</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>429.98</v>
+        <v>425.98</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>489.97</v>
+        <v>417.98</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>445.98</v>
+        <v>429.98</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>505.97</v>
+        <v>489.97</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>449.98</v>
+        <v>445.98</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>499.99</v>
+        <v>505.97</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>627.98</v>
+        <v>449.98</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>636.98</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>697.97</v>
+        <v>627.98</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>706.97</v>
+        <v>636.98</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>639.98</v>
+        <v>697.97</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>699.97</v>
+        <v>706.97</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>655.98</v>
+        <v>639.98</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>715.97</v>
+        <v>699.97</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>659.98</v>
+        <v>655.98</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>499.99</v>
+        <v>715.97</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc X-Style</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>579.99</v>
+        <v>659.98</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>579.98</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>639.97</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>615.98</v>
+        <v>579.98</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>675.97</v>
+        <v>639.97</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>599.98</v>
+        <v>615.98</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>659.97</v>
+        <v>675.97</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>619.98</v>
+        <v>599.98</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>459.99</v>
+        <v>659.97</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc X-Style</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>539.99</v>
+        <v>619.98</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>579.98</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>639.97</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>605.98</v>
+        <v>579.98</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>665.97</v>
+        <v>639.97</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>629.99</v>
+        <v>605.98</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>825.98</v>
+        <v>665.97</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>895.97</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>809.98</v>
+        <v>825.98</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>845.98</v>
+        <v>895.97</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>849.98</v>
+        <v>809.98</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>761.75</v>
+        <v>845.98</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>851.4299999999999</v>
+        <v>849.98</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>927.86</v>
+        <v>761.75</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>840.65</v>
+        <v>851.4299999999999</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>977.62</v>
+        <v>927.86</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>629.99</v>
+        <v>840.65</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>787.98</v>
+        <v>977.62</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>857.97</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>799.98</v>
+        <v>787.98</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>859.97</v>
+        <v>857.97</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>815.98</v>
+        <v>799.98</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>875.97</v>
+        <v>859.97</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>559.99</v>
+        <v>815.98</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>737.98</v>
+        <v>875.97</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>807.97</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>749.98</v>
+        <v>737.98</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>809.97</v>
+        <v>807.97</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>765.98</v>
+        <v>749.98</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>825.97</v>
+        <v>809.97</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>186.99</v>
+        <v>765.98</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>99.98999999999999</v>
+        <v>825.97</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
+          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>99.98999999999999</v>
+        <v>186.99</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Donner DMK-25 Pro Clavier MIDI</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>89.98999999999999</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>236.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
+          <t>Donner DMK-25 Pro Clavier MIDI</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>370.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>491.98</v>
+        <v>236.99</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>219.99</v>
+        <v>370.99</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>370.99</v>
+        <v>491.98</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>491.98</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>281.99</v>
+        <v>370.99</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>373.37</v>
+        <v>491.98</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>530.16</v>
+        <v>281.99</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>89</v>
+        <v>373.37</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>109.99</v>
+        <v>530.16</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Pour la différence de prix</t>
+          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>7.69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>152.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
+          <t>Pour la différence de prix</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>352.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -5017,7 +5017,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -5027,7 +5027,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -5037,7 +5037,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -5047,7 +5047,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -5057,7 +5057,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -5067,147 +5067,147 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>86.98999999999999</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>69.98999999999999</v>
+        <v>352.99</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>389.99</v>
+        <v>86.98999999999999</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>479.98</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>479.98</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>495.98</v>
+        <v>479.98</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>519.98</v>
+        <v>479.98</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>399.99</v>
+        <v>495.98</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>479.98</v>
+        <v>519.98</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>479.98</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>495.98</v>
+        <v>479.98</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>519.98</v>
+        <v>479.98</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>89.98999999999999</v>
+        <v>495.98</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>79.47</v>
+        <v>519.98</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -5217,480 +5217,500 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>469.99</v>
+        <v>79.47</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>518.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>566.98</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>557.98</v>
+        <v>518.99</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>636.97</v>
+        <v>566.98</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>627.97</v>
+        <v>557.98</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>549.98</v>
+        <v>636.97</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>569.98</v>
+        <v>627.97</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>629.97</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>585.98</v>
+        <v>569.98</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>645.97</v>
+        <v>629.97</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>589.98</v>
+        <v>585.98</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>429.99</v>
+        <v>645.97</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>489.99</v>
+        <v>589.98</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>536.98</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>527.98</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>606.97</v>
+        <v>536.98</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>597.97</v>
+        <v>527.98</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>519.98</v>
+        <v>606.97</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>539.98</v>
+        <v>597.97</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>599.97</v>
+        <v>519.98</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>555.98</v>
+        <v>539.98</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>615.97</v>
+        <v>599.97</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>559.98</v>
+        <v>555.98</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>469.99</v>
+        <v>615.97</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>529.99</v>
+        <v>559.98</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>566.98</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>557.98</v>
+        <v>529.99</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>636.97</v>
+        <v>566.98</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>627.97</v>
+        <v>557.98</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>549.98</v>
+        <v>636.97</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>569.98</v>
+        <v>627.97</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>629.97</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>585.98</v>
+        <v>569.98</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>645.97</v>
+        <v>629.97</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>589.98</v>
+        <v>585.98</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>429.99</v>
+        <v>645.97</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>499.99</v>
+        <v>589.98</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>536.98</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>527.98</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B519" t="n">
-        <v>606.97</v>
+        <v>536.98</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B520" t="n">
-        <v>597.97</v>
+        <v>527.98</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B521" t="n">
-        <v>519.98</v>
+        <v>606.97</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B522" t="n">
-        <v>539.98</v>
+        <v>597.97</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B523" t="n">
-        <v>599.97</v>
+        <v>519.98</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>555.98</v>
+        <v>539.98</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B525" t="n">
-        <v>615.97</v>
+        <v>599.97</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>555.98</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>615.97</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
           <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
-      <c r="B526" t="n">
+      <c r="B528" t="n">
         <v>559.98</v>
       </c>
     </row>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B528"/>
+  <dimension ref="A1:B525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>539.98</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="136">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>559.98</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="137">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>579.98</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="138">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>485.98</v>
+        <v>485.99</v>
       </c>
     </row>
     <row r="140">
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>489.98</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="141">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>509.98</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="142">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>479.98</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="169">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>479.98</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="170">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>499.98</v>
+        <v>442.99</v>
       </c>
     </row>
     <row r="171">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>539.97</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="172">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>539.97</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="173">
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>559.97</v>
+        <v>512.99</v>
       </c>
     </row>
     <row r="174">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>519.98</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="175">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>909.98</v>
+        <v>909.99</v>
       </c>
     </row>
     <row r="177">
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>925.98</v>
+        <v>925.99</v>
       </c>
     </row>
     <row r="178">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>899.98</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="179">
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>979.97</v>
+        <v>979.99</v>
       </c>
     </row>
     <row r="180">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>995.97</v>
+        <v>999.99</v>
       </c>
     </row>
     <row r="181">
@@ -2507,277 +2507,277 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Donner DK-10S 61 Touches Clavier Électronique - clavier électronique</t>
+          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>139.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Donner DK-10S 61 Touches Clavier Électronique - Clavier + Banc X-Style</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>219.98</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Donner DK-10S 61 Touches Clavier Électronique - Clavier + Banc de Piano</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>219.98</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
+          <t>Donner Banquette Piano Duo Réglable Confort</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>119.99</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>Donner M100 Casque de monitoring studio</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>284.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>Donner DEP-08 Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>284.99</v>
+        <v>229.99</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable Confort</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>115.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Donner M100 Casque de monitoring studio</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>59.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>229.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>359.98</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>359.98</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>199.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>299.98</v>
+        <v>367.99</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>299.98</v>
+        <v>392.99</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
+          <t>Donner DED-70 Batterie Electronique</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>299.98</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
+          <t>Donner DED-80 Batterie électrique - Noir</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>367.97</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
+          <t>Donner DED-80 Batterie électrique - Blanc</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>392.97</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie Electronique</t>
+          <t>Donner Essential L1 Synthétiseur - L1</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>199.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Noir</t>
+          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>219.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Blanc</t>
+          <t>Donner Essential L1 Synthétiseur - Pack</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>219.99</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - L1</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>279.99</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>119.99</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - Pack</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>399.98</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>799.99</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>799.99</v>
+        <v>409.99</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>799.99</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>102.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -2787,7 +2787,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -2797,7 +2797,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -2807,17 +2807,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>409.99</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -2827,7 +2827,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -2837,7 +2837,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -2847,17 +2847,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>498.99</v>
+        <v>474.99</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -2867,37 +2867,37 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>399.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>474.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>499.98</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -2907,7 +2907,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -2917,7 +2917,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -2927,417 +2927,417 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>899.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>899.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>899.99</v>
+        <v>446.99</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>109.99</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>359.99</v>
+        <v>584.99</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>446.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>549.98</v>
+        <v>446.99</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>584.99</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>359.99</v>
+        <v>584.99</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>Donner DED-300X Batterie Electronique</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>446.99</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>549.98</v>
+        <v>130.99</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>584.99</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Donner DED-300X Batterie Electronique</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>539.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>130.99</v>
+        <v>769.99</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>129.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>659.99</v>
+        <v>839.99</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>782.98</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>765.98</v>
+        <v>775.99</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>842.97</v>
+        <v>779.99</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>825.97</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>785.98</v>
+        <v>769.99</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>801.98</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>659.99</v>
+        <v>839.99</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>765.98</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>765.98</v>
+        <v>775.99</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>825.97</v>
+        <v>779.99</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>825.97</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>785.98</v>
+        <v>92.98999999999999</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>801.98</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
+          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>102.99</v>
+        <v>99</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
+          <t>Donner DT-50 Tabouret de Batterie</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>92.98999999999999</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
+          <t>Donner DST-550 Guitare Électrique - Bleu</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>109.99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
+          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Donner DT-50 Tabouret de Batterie</t>
+          <t>Donner DST-550 Guitare Électrique - Blanc</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>72.98999999999999</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Bleu</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>169.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>199.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Blanc</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>169.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>289.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>379.98</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>279.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>409.98</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -3347,497 +3347,497 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>495.98</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>519.98</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>389.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>479.98</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>519.98</v>
+        <v>315.99</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>209.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>284.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>315.98</v>
+        <v>385.99</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>309.98</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>359.97</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>385.97</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>379.97</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>319.98</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>389.97</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>179.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>259.98</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>267.98</v>
+        <v>349.99</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>276.98</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>319.97</v>
+        <v>295.99</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>327.97</v>
+        <v>365.99</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>336.97</v>
+        <v>189.99</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>279.98</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>339.97</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>189.99</v>
+        <v>282.99</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>265.98</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>273.98</v>
+        <v>343.99</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>282.98</v>
+        <v>352.99</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>335.97</v>
+        <v>285.99</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>343.97</v>
+        <v>355.99</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>352.97</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>285.98</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>355.97</v>
+        <v>315.99</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>209.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>289.98</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>315.98</v>
+        <v>385.99</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>309.98</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>359.97</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>385.97</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>379.97</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>319.98</v>
+        <v>239.99</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>389.97</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>169.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>239.98</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>359.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>559.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>458.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>309.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>559.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>458.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -3847,57 +3847,57 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>559.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>458.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>359.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>559.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>458.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -3907,137 +3907,137 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>559.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>458.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
+          <t>Donner DED-200 Max Batteries Electroniques</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>309.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>559.99</v>
+        <v>1099.99</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>458.99</v>
+        <v>1114.99</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Donner DED-200 Max Batteries Electroniques</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>499.99</v>
+        <v>899</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>1099.99</v>
+        <v>995.99</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>1114.99</v>
+        <v>998.99</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>899</v>
+        <v>125.99</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>995.99</v>
+        <v>166.99</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>998.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>125.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>166.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -4047,27 +4047,27 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>536.98</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>448.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -4077,27 +4077,27 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>536.98</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>448.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -4107,1611 +4107,1581 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>536.98</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>448.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>299.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>536.98</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>448.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>109.99</v>
+        <v>419.99</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>319.99</v>
+        <v>419.99</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>408.99</v>
+        <v>435.99</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>425.98</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>417.98</v>
+        <v>439.99</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>429.98</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>489.97</v>
+        <v>439.99</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>445.98</v>
+        <v>329.99</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>505.97</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>449.98</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>329.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>428.98</v>
+        <v>445.99</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>425.98</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>417.98</v>
+        <v>449.99</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>429.98</v>
+        <v>519.99</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>489.97</v>
+        <v>449.99</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>445.98</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>505.97</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>449.98</v>
+        <v>609.99</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>499.99</v>
+        <v>686.99</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>627.98</v>
+        <v>696.99</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>636.98</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>697.97</v>
+        <v>685.99</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>706.97</v>
+        <v>619.99</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>639.98</v>
+        <v>689.99</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>699.97</v>
+        <v>619.99</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>655.98</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>715.97</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>659.98</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>499.99</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc X-Style</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>579.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>579.98</v>
+        <v>675.99</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>639.97</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>615.98</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>675.97</v>
+        <v>619.99</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>599.98</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>659.97</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>619.98</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>459.99</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc X-Style</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>539.99</v>
+        <v>605.99</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano</t>
+          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>579.98</v>
+        <v>665.99</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>639.97</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>605.98</v>
+        <v>729.99</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>665.97</v>
+        <v>816.99</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>629.99</v>
+        <v>719.99</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>825.98</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>895.97</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>809.98</v>
+        <v>761.99</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>845.98</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>849.98</v>
+        <v>927.99</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>761.75</v>
+        <v>840.99</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>851.4299999999999</v>
+        <v>977.99</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>927.86</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>840.65</v>
+        <v>729.99</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>977.62</v>
+        <v>816.99</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>629.99</v>
+        <v>745.99</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>787.98</v>
+        <v>815.99</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>857.97</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>799.98</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>859.97</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>815.98</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>875.97</v>
+        <v>746.99</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>559.99</v>
+        <v>675.99</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>737.98</v>
+        <v>745.99</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>807.97</v>
+        <v>679.99</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>749.98</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>809.97</v>
+        <v>186.99</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>765.98</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>825.97</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
+          <t>Donner DMK-25 Pro Clavier MIDI</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>186.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>99.98999999999999</v>
+        <v>236.99</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>99.98999999999999</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Donner DMK-25 Pro Clavier MIDI</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>89.98999999999999</v>
+        <v>423.99</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>236.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>370.99</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>491.98</v>
+        <v>423.99</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>219.99</v>
+        <v>281.99</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>370.99</v>
+        <v>373.99</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>491.98</v>
+        <v>530.99</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
+          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>281.99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>373.37</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
+          <t>Pour la différence de prix</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>530.16</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>89</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>109.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Pour la différence de prix</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>7.69</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>152.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>352.99</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>152.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>352.99</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>152.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>352.99</v>
+        <v>86.98999999999999</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>152.99</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>352.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>86.98999999999999</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>69.98999999999999</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>389.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>479.98</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>479.98</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>495.98</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>519.98</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>399.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>479.98</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>479.98</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>495.98</v>
+        <v>79.47</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>519.98</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>89.98999999999999</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>79.47</v>
+        <v>518.99</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>89.98999999999999</v>
+        <v>566.99</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>469.99</v>
+        <v>557.99</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>518.99</v>
+        <v>636.99</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>566.98</v>
+        <v>627.99</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>557.98</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>636.97</v>
+        <v>569.99</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>627.97</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>549.98</v>
+        <v>585.99</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>569.98</v>
+        <v>645.99</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>629.97</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>585.98</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>645.97</v>
+        <v>536.99</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>589.98</v>
+        <v>527.99</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>429.99</v>
+        <v>606.99</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>489.99</v>
+        <v>597.99</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>536.98</v>
+        <v>519.99</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>527.98</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>606.97</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>597.97</v>
+        <v>555.99</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>519.98</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>539.98</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>599.97</v>
+        <v>559.98</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>555.98</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>615.97</v>
+        <v>518.99</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>559.98</v>
+        <v>566.99</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>469.99</v>
+        <v>557.99</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>529.99</v>
+        <v>636.99</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>566.98</v>
+        <v>627.99</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>557.98</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>636.97</v>
+        <v>569.99</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>627.97</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>549.98</v>
+        <v>585.99</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>569.98</v>
+        <v>645.99</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>629.97</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>585.98</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>645.97</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>589.98</v>
+        <v>536.99</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>429.99</v>
+        <v>527.99</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>499.99</v>
+        <v>606.99</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B519" t="n">
-        <v>536.98</v>
+        <v>597.99</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B520" t="n">
-        <v>527.98</v>
+        <v>519.99</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B521" t="n">
-        <v>606.97</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B522" t="n">
-        <v>597.97</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B523" t="n">
-        <v>519.98</v>
+        <v>555.99</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>539.98</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B525" t="n">
-        <v>599.97</v>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
-        </is>
-      </c>
-      <c r="B526" t="n">
-        <v>555.98</v>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
-        </is>
-      </c>
-      <c r="B527" t="n">
-        <v>615.97</v>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
-        </is>
-      </c>
-      <c r="B528" t="n">
-        <v>559.98</v>
+        <v>549.99</v>
       </c>
     </row>
   </sheetData>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -2297,101 +2297,101 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>279.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>418.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>419.98</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>369.98</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>369.98</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>299.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>398.99</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>399.98</v>
+        <v>419.98</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>352.98</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>352.98</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="197">

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B525"/>
+  <dimension ref="A1:B526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -447,107 +447,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DONNER DKA-50 50W Amplificateur de clavier</t>
+          <t>Donner VIVA Guitare sans cordes innovante</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>259.99</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Banquette de piano assortie</t>
+          <t>DONNER DKA-50 50W Amplificateur de clavier</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>119.99</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano</t>
+          <t>Donner OURA S200 Banquette de piano assortie</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>729.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>822.99</v>
+        <v>729.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>839.99</v>
+        <v>822.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>729.99</v>
+        <v>839.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>822.99</v>
+        <v>729.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>829.99</v>
+        <v>822.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>529.99</v>
+        <v>829.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>579.99</v>
+        <v>529.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano noir</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -557,57 +557,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>615.99</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano Blanc</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>599.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Donner MAMP8 Ampli AV 5.2 Canaux</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano Blanc</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>259.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano</t>
+          <t>Donner MAMP8 Ampli AV 5.2 Canaux</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>699.99</v>
+        <v>229.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + banc de piano</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>799.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc (match officiel)</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -617,37 +617,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc (match officiel)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>819.99</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc réglable X-Style</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>779.99</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier électronique - Blanc</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>79.98999999999999</v>
+        <v>779.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier électronique - Rosa</t>
+          <t>Donner DEK-32 à 32 touches Clavier électronique - Blanc</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -657,7 +657,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier électronique - Cyan</t>
+          <t>Donner DEK-32 à 32 touches Clavier électronique - Rosa</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -667,67 +667,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Donner SD-15 Clavier électronique 61 touches - Nur das Keyboard</t>
+          <t>Donner DEK-32 à 32 touches Clavier électronique - Cyan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>189.99</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Donner SD-15 Clavier électronique 61 touches - Bundle mit Zubehör</t>
+          <t>Donner SD-15 Clavier électronique 61 touches - Nur das Keyboard</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>259.99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Donner Starrypad Pro Contrôleur MIDI</t>
+          <t>Donner SD-15 Clavier électronique 61 touches - Bundle mit Zubehör</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>79.98999999999999</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Donner MH1 Casque de monitoring</t>
+          <t>Donner Starrypad Pro Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>59.99</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Donner Sac de Transport pour Clavier 88 Touches</t>
+          <t>Donner MH1 Casque de monitoring</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Blanc】</t>
+          <t>Donner Sac de Transport pour Clavier 88 Touches</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>439.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Noir】</t>
+          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Blanc】</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -737,187 +737,187 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Donner HUSH X LIVE Guitare de voyage - Version MIYAVI</t>
+          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Noir】</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>635.99</v>
+        <v>439.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - L1</t>
+          <t>Donner HUSH X LIVE Guitare de voyage - Version MIYAVI</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>199.99</v>
+        <v>635.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - L1</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>119.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - Pack</t>
+          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - KB-32M</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>319.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare</t>
+          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - Pack</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>259.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>459.99</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>358.99</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>259.99</v>
+        <v>358.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>459.99</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>358.99</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>259.99</v>
+        <v>358.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>459.99</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>358.99</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>259.99</v>
+        <v>358.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>459.99</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>358.99</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DED-200Max Batteries Electroniques</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>429.99</v>
+        <v>358.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>【Offre exclusive】Donner DED-200Max Batteries Electroniques</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>259.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -927,377 +927,377 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano</t>
+          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>749.99</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>852.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc</t>
+          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>839.99</v>
+        <v>852.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano</t>
+          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>369.99</v>
+        <v>839.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + noir</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>459.99</v>
+        <v>369.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>472.99</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>489.99</v>
+        <v>472.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>369.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + noir</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>469.99</v>
+        <v>369.99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>472.99</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>489.99</v>
+        <v>472.99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - DDP-80 PLUS Piano</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>499.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - DDP-80 PLUS Piano</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>599.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano</t>
+          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>609.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>309.99</v>
+        <v>609.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>309.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>309.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>309.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>309.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>309.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner BackBeat Batterie Electronique - BackBeat</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>899.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
+          <t>【Offre exclusive】Donner BackBeat Batterie Electronique - BackBeat</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>969.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Donner DED-100 Batterie électrique</t>
+          <t>【Offre exclusive】Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>399.99</v>
+        <v>969.99</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano</t>
+          <t>Donner DED-100 Batterie électrique</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>249.99</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>329.98</v>
+        <v>249.99</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1307,37 +1307,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>359.98</v>
+        <v>329.98</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Tourneur de Page</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>319.98</v>
+        <v>359.98</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>399.97</v>
+        <v>319.98</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir + Tourneur de Page</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1347,47 +1347,47 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir + Tourneur de Page</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>429.97</v>
+        <v>399.97</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>699.99</v>
+        <v>429.97</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano</t>
+          <t>【Boîte ouverte】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>769.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>849.98</v>
+        <v>769.99</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1397,167 +1397,167 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>875.98</v>
+        <v>849.98</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + DKB-100 Banc De Piano</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>869.98</v>
+        <v>875.98</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + DKB-100 Banc De Piano</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>885.98</v>
+        <v>869.98</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1099.99</v>
+        <v>885.98</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro + Tabouret de batterie DT-50</t>
+          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1169.99</v>
+        <v>1099.99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare</t>
+          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>219.99</v>
+        <v>1169.99</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>489.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>398.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>219.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>489.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>398.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>219.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>489.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + JW Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>398.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Donner Pupitre de batterie</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>39.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Acajou</t>
+          <t>Donner Pupitre de batterie</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>159.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Noir</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Acajou</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -1567,7 +1567,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Sunburst</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Noir</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -1577,37 +1577,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Sunburst</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>229.99</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>259.99</v>
+        <v>229.99</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst</t>
+          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>239.99</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -1617,7 +1617,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -1627,17 +1627,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>259.99</v>
+        <v>239.99</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -1647,7 +1647,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -1657,87 +1657,87 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Donner DAM1000 Audio Mixer</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>179.99</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro</t>
+          <t>Donner DAM1000 Audio Mixer</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>599.99</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro + Tabouret de batterie DT-50</t>
+          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>669.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston + Pied</t>
+          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>165.99</v>
+        <v>669.99</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston + Pied</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>72.98999999999999</v>
+        <v>165.99</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Pied</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>92.98999999999999</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go【Noir】</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Pied</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>89.98999999999999</v>
+        <v>92.98999999999999</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go II【Noir】</t>
+          <t>Donner Go ampli guitare - Donner Go【Noir】</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>129.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go II【Blanc】</t>
+          <t>Donner Go ampli guitare - Donner Go II【Noir】</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -1747,127 +1747,127 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
+          <t>Donner Go ampli guitare - Donner Go II【Blanc】</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>69.98999999999999</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>【Donner】Pour la différence de prix</t>
+          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>180</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>【Donner】Pour la différence de prix</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>469.99</v>
+        <v>180</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>539.99</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>559.99</v>
+        <v>529.99</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>579.99</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>399.99</v>
+        <v>569.99</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>485.99</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>489.99</v>
+        <v>485.99</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>509.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>159.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
+          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>209.99</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -1877,7 +1877,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -1887,7 +1887,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1897,57 +1897,57 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 4 Cymbales</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>499.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - Nouvelle 5 Tambours et 4 Cymbales</t>
+          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 4 Cymbales</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>599.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 3 Cymbales</t>
+          <t>Donner DED-200X Batterie Électronique - Nouvelle 5 Tambours et 4 Cymbales</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>589.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Donner Beat Go Kit de batterie électronique portable</t>
+          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 3 Cymbales</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>289.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
+          <t>Donner Beat Go Kit de batterie électronique portable</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>119.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1957,37 +1957,37 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Donner Table de percussion</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>39.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>Donner Table de percussion</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>599.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>699.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -1997,27 +1997,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>599.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>699.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -2027,17 +2027,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Bleu clair</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>69.98999999999999</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Rose clair</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Bleu clair</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -2047,17 +2047,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Bleu clair</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Rose clair</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>89.98999999999999</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Rose clair</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Bleu clair</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -2067,227 +2067,227 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Rose clair</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>269.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
+          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>149.99</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
+          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>129.99</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
+          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>339.99</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>429.99</v>
+        <v>329.99</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>429.99</v>
+        <v>419.99</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>442.99</v>
+        <v>419.99</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>499.99</v>
+        <v>432.99</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>499.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>512.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>459.99</v>
+        <v>502.99</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>829.99</v>
+        <v>449.99</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>909.99</v>
+        <v>829.99</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>925.99</v>
+        <v>909.99</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>899.99</v>
+        <v>925.99</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>979.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>999.99</v>
+        <v>979.99</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Eastar EDA-100 Digital Aerophone Noir</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>122.99</v>
+        <v>999.99</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
+          <t>Eastar EDA-100 Digital Aerophone Noir</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>299.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>418.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>419.98</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>369.98</v>
+        <v>419.98</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -2297,47 +2297,47 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>299.99</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>398.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>399.98</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>352.98</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -2347,47 +2347,47 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>279.99</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>418.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>419.98</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>369.98</v>
+        <v>419.98</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -2397,47 +2397,47 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>299.99</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>398.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>399.98</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>352.98</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -2447,17 +2447,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>99.98999999999999</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
+          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -2467,67 +2467,67 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
+          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>126.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
+          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>62.99</v>
+        <v>126.99</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
+          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>59.99</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>56.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>119.99</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>284.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -2537,47 +2537,47 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable Confort</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>115.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Donner M100 Casque de monitoring studio</t>
+          <t>Donner Banquette Piano Duo Réglable Confort</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>59.99</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano</t>
+          <t>Donner M100 Casque de monitoring studio</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>229.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-08 Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>319.99</v>
+        <v>229.99</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -2587,37 +2587,37 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>199.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>289.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>299.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -2627,47 +2627,47 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>367.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>392.99</v>
+        <v>367.99</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie Electronique</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>199.99</v>
+        <v>392.99</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Noir</t>
+          <t>Donner DED-70 Batterie Electronique</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>219.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Blanc</t>
+          <t>Donner DED-80 Batterie électrique - Noir</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -2677,47 +2677,47 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - L1</t>
+          <t>Donner DED-80 Batterie électrique - Blanc</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>279.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>Donner Essential L1 Synthétiseur - L1</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>119.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - Pack</t>
+          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>399.98</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>Donner Essential L1 Synthétiseur - Pack</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>799.99</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -2727,7 +2727,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -2737,147 +2737,147 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>102.99</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
+          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>409.99</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>498.99</v>
+        <v>409.99</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>499.98</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>409.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>498.99</v>
+        <v>409.99</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>499.98</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>399.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>498.99</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>499.98</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>399.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>474.99</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>499.98</v>
+        <v>474.99</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>899.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -2887,7 +2887,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -2897,7 +2897,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -2907,7 +2907,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -2917,7 +2917,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -2927,1247 +2927,1247 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>109.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>359.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>446.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>549.98</v>
+        <v>446.99</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>584.99</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>359.99</v>
+        <v>584.99</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>446.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>549.98</v>
+        <v>446.99</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>584.99</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Donner DED-300X Batterie Electronique</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>539.99</v>
+        <v>584.99</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
+          <t>Donner DED-300X Batterie Electronique</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>130.99</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>129.99</v>
+        <v>130.99</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>659.99</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>769.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>749.99</v>
+        <v>769.99</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>839.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>819.99</v>
+        <v>839.99</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>775.99</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>779.99</v>
+        <v>775.99</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>659.99</v>
+        <v>779.99</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>769.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>749.99</v>
+        <v>769.99</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>839.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>819.99</v>
+        <v>839.99</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>775.99</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>779.99</v>
+        <v>775.99</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>102.99</v>
+        <v>779.99</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
+          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>92.98999999999999</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>109.99</v>
+        <v>92.98999999999999</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Donner DT-50 Tabouret de Batterie</t>
+          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>72.98999999999999</v>
+        <v>99</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Bleu</t>
+          <t>Donner DT-50 Tabouret de Batterie</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>169.99</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
+          <t>Donner DST-550 Guitare Électrique - Bleu</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>199.99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Blanc</t>
+          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>169.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
+          <t>Donner DST-550 Guitare Électrique - Blanc</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>289.99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>379.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>279.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>379.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>389.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>489.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>509.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>389.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>479.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>509.99</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>209.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>284.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>315.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>309.99</v>
+        <v>315.99</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>359.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>385.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>379.99</v>
+        <v>385.99</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>319.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>389.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>179.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>269.99</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>279.99</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>289.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>339.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>349.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>359.99</v>
+        <v>349.99</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>295.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>365.99</v>
+        <v>295.99</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>189.99</v>
+        <v>365.99</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>269.99</v>
+        <v>189.99</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>279.99</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>282.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>335.99</v>
+        <v>282.99</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>343.99</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>352.99</v>
+        <v>343.99</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>285.99</v>
+        <v>352.99</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>355.99</v>
+        <v>285.99</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>209.99</v>
+        <v>355.99</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>284.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>315.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>309.99</v>
+        <v>315.99</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>359.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>385.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>379.99</v>
+        <v>385.99</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>319.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>389.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>169.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>239.99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>359.99</v>
+        <v>239.99</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>496.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>309.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>496.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>359.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>496.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>359.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>496.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>309.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>496.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>309.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>496.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Donner DED-200 Max Batteries Electroniques</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>499.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
+          <t>Donner DED-200 Max Batteries Electroniques</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>1099.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>1114.99</v>
+        <v>1099.99</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>899</v>
+        <v>1114.99</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>995.99</v>
+        <v>899</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>998.99</v>
+        <v>995.99</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>125.99</v>
+        <v>998.99</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>166.99</v>
+        <v>125.99</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>299.99</v>
+        <v>166.99</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>486.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>398.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>299.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>486.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>398.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>299.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>486.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>398.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>299.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>486.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>398.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>109.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>319.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>408.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>419.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -4177,87 +4177,87 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>435.99</v>
+        <v>419.99</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>489.99</v>
+        <v>435.99</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>439.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>509.99</v>
+        <v>439.99</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>439.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>329.99</v>
+        <v>439.99</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>418.99</v>
+        <v>329.99</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>429.99</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -4267,357 +4267,357 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>445.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>499.99</v>
+        <v>445.99</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>449.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>519.99</v>
+        <v>449.99</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>449.99</v>
+        <v>519.99</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>499.99</v>
+        <v>449.99</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>599.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>609.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>686.99</v>
+        <v>609.99</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>696.99</v>
+        <v>686.99</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>615.99</v>
+        <v>696.99</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>685.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>619.99</v>
+        <v>685.99</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>689.99</v>
+        <v>619.99</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>619.99</v>
+        <v>689.99</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>499.99</v>
+        <v>619.99</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc X-Style</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>579.99</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>579.99</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>639.99</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>615.99</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>675.99</v>
+        <v>605.99</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>599.99</v>
+        <v>665.99</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>659.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 Pro / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>619.99</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>459.99</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc X-Style</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>539.99</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>579.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>639.99</v>
+        <v>675.99</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>605.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 PRO Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>665.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>629.99</v>
+        <v>619.99</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>729.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>816.99</v>
+        <v>729.99</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>719.99</v>
+        <v>816.99</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>749.99</v>
+        <v>719.99</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -4627,217 +4627,217 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>761.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>851.99</v>
+        <v>761.99</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>927.99</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>840.99</v>
+        <v>927.99</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>977.99</v>
+        <v>840.99</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>629.99</v>
+        <v>977.99</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>729.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>816.99</v>
+        <v>729.99</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>745.99</v>
+        <v>816.99</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>815.99</v>
+        <v>745.99</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>749.99</v>
+        <v>815.99</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>819.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>559.99</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>659.99</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>746.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>675.99</v>
+        <v>746.99</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>745.99</v>
+        <v>675.99</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>679.99</v>
+        <v>745.99</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>749.99</v>
+        <v>679.99</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>186.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
+          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>99.98999999999999</v>
+        <v>186.99</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -4847,257 +4847,257 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Donner DMK-25 Pro Clavier MIDI</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>89.98999999999999</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
+          <t>Donner DMK-25 Pro Clavier MIDI</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>236.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>335.99</v>
+        <v>236.99</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>423.99</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>219.99</v>
+        <v>423.99</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>335.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>423.99</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>281.99</v>
+        <v>423.99</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>373.99</v>
+        <v>281.99</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>530.99</v>
+        <v>373.99</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>89</v>
+        <v>530.99</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>109.99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Pour la différence de prix</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>7.69</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
+          <t>Pour la différence de prix</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>152.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>339.99</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>152.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>339.99</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>152.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>339.99</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>152.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>339.99</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>86.98999999999999</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>69.98999999999999</v>
+        <v>86.98999999999999</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>389.99</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>479.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -5107,47 +5107,47 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>489.99</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>509.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>389.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>479.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -5157,530 +5157,540 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>489.99</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>509.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>89.98999999999999</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>79.47</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>89.98999999999999</v>
+        <v>79.47</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>469.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>518.99</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>566.99</v>
+        <v>518.99</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>557.99</v>
+        <v>566.99</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>636.99</v>
+        <v>557.99</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>627.99</v>
+        <v>636.99</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>549.99</v>
+        <v>627.99</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>569.99</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>629.99</v>
+        <v>569.99</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>585.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>645.99</v>
+        <v>585.99</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>589.99</v>
+        <v>645.99</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>429.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>536.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>527.99</v>
+        <v>536.99</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>606.99</v>
+        <v>527.99</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>597.99</v>
+        <v>606.99</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>519.99</v>
+        <v>597.99</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>539.99</v>
+        <v>519.99</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>599.99</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>555.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>615.99</v>
+        <v>555.99</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>549.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>559.98</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>469.99</v>
+        <v>559.98</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>518.99</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>566.99</v>
+        <v>518.99</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>557.99</v>
+        <v>566.99</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>636.99</v>
+        <v>557.99</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>627.99</v>
+        <v>636.99</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>549.99</v>
+        <v>627.99</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>569.99</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>629.99</v>
+        <v>569.99</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>585.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>645.99</v>
+        <v>585.99</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>589.99</v>
+        <v>645.99</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>429.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>499.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>536.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>527.99</v>
+        <v>536.99</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>606.99</v>
+        <v>527.99</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B519" t="n">
-        <v>597.99</v>
+        <v>606.99</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B520" t="n">
-        <v>519.99</v>
+        <v>597.99</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B521" t="n">
-        <v>539.99</v>
+        <v>519.99</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B522" t="n">
-        <v>599.99</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B523" t="n">
-        <v>555.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>615.99</v>
+        <v>555.99</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>615.99</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
           <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
-      <c r="B525" t="n">
+      <c r="B526" t="n">
         <v>549.99</v>
       </c>
     </row>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B526"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2267,37 +2267,37 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>418.99</v>
+        <v>341.99</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>419.98</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>369.98</v>
+        <v>419.98</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -2307,627 +2307,627 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>299.99</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>398.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>399.98</v>
+        <v>341.99</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>352.98</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>352.98</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>279.99</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>418.99</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>419.98</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>369.98</v>
+        <v>322.99</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>369.98</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>299.99</v>
+        <v>419.98</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>398.99</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>399.98</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>352.98</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>352.98</v>
+        <v>341.99</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>99.98999999999999</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>99.98999999999999</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>126.99</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>62.99</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
+          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>59.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
+          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>56.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
+          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>119.99</v>
+        <v>126.99</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>284.99</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>284.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable Confort</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>115.99</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Donner M100 Casque de monitoring studio</t>
+          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>59.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>229.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>319.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
+          <t>Donner Banquette Piano Duo Réglable Confort</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>319.99</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
+          <t>Donner M100 Casque de monitoring studio</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>199.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
+          <t>Donner DEP-08 Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>289.99</v>
+        <v>229.99</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>299.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>299.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>367.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>392.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie Electronique</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>199.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Noir</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>219.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Blanc</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>219.99</v>
+        <v>367.99</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - L1</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>279.99</v>
+        <v>392.99</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>Donner DED-70 Batterie Electronique - DED-70</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>119.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - Pack</t>
+          <t>Donner DED-70 Batterie Electronique - DED-70 + MH1 Casque + Plateau pour batterie</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>399.98</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>Donner DED-80 Batterie électrique - Noir</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>799.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
+          <t>Donner DED-80 Batterie électrique - Blanc</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>799.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>Donner Essential L1 Synthétiseur - L1</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>799.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
+          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>102.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
+          <t>Donner Essential L1 Synthétiseur - Pack</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>409.99</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>498.99</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>499.98</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>409.99</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
+          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>498.99</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>499.98</v>
+        <v>409.99</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>399.99</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>498.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>499.98</v>
+        <v>409.99</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>399.99</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>474.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>499.98</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>899.99</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>899.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>899.99</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>899.99</v>
+        <v>474.99</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>899.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -2937,1567 +2937,1567 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>109.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>359.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>446.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>549.98</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>584.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>359.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>446.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>549.98</v>
+        <v>446.99</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>584.99</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Donner DED-300X Batterie Electronique</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>539.99</v>
+        <v>584.99</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>130.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>129.99</v>
+        <v>446.99</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>659.99</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>769.99</v>
+        <v>584.99</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
+          <t>Donner DED-300X Batterie Electronique</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>749.99</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>839.99</v>
+        <v>130.99</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>819.99</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>775.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>779.99</v>
+        <v>769.99</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>659.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>769.99</v>
+        <v>839.99</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>749.99</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>839.99</v>
+        <v>775.99</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>819.99</v>
+        <v>779.99</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>775.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>779.99</v>
+        <v>769.99</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>102.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>92.98999999999999</v>
+        <v>839.99</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>109.99</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>99</v>
+        <v>775.99</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Donner DT-50 Tabouret de Batterie</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>72.98999999999999</v>
+        <v>779.99</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Bleu</t>
+          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>169.99</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>199.99</v>
+        <v>92.98999999999999</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Blanc</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>169.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
+          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>289.99</v>
+        <v>99</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
+          <t>Donner DT-50 Tabouret de Batterie</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>379.99</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
+          <t>Donner DST-550 Guitare Électrique - Bleu</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>279.99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
+          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>379.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
+          <t>Donner DST-550 Guitare Électrique - Blanc</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>389.99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>489.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>509.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>389.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>479.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>509.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>209.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>284.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>315.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>309.99</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>359.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>385.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>379.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>319.99</v>
+        <v>315.99</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>389.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>179.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>269.99</v>
+        <v>385.99</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>279.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>289.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>339.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>349.99</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>359.99</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>295.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>365.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>189.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>269.99</v>
+        <v>349.99</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>279.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>282.99</v>
+        <v>295.99</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>335.99</v>
+        <v>365.99</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>343.99</v>
+        <v>189.99</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>352.99</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>285.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>355.99</v>
+        <v>282.99</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>209.99</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>284.99</v>
+        <v>343.99</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>315.99</v>
+        <v>352.99</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>309.99</v>
+        <v>285.99</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>359.99</v>
+        <v>355.99</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>385.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>379.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>319.99</v>
+        <v>315.99</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>389.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>169.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>239.99</v>
+        <v>385.99</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>359.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>496.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>408.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>309.99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>496.99</v>
+        <v>239.99</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>408.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>359.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>496.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>359.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>496.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>408.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>309.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>496.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>408.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>309.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>496.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Donner DED-200 Max Batteries Electroniques</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>499.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>1099.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>1114.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>899</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>995.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>Donner DED-200 Max Batteries Electroniques</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>998.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>125.99</v>
+        <v>1099.99</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>166.99</v>
+        <v>1114.99</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>299.99</v>
+        <v>899</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>486.99</v>
+        <v>995.99</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>398.99</v>
+        <v>998.99</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>299.99</v>
+        <v>125.99</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>486.99</v>
+        <v>166.99</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>398.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>299.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>486.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>398.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>299.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>486.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>398.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>109.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>319.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>408.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>419.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>419.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>435.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>489.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>439.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>509.99</v>
+        <v>419.99</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>439.99</v>
+        <v>419.99</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>329.99</v>
+        <v>435.99</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>418.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>429.99</v>
+        <v>439.99</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>429.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>445.99</v>
+        <v>439.99</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>499.99</v>
+        <v>329.99</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>449.99</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>519.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>449.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>499.99</v>
+        <v>445.99</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>599.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>609.99</v>
+        <v>449.99</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>686.99</v>
+        <v>519.99</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>696.99</v>
+        <v>449.99</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>615.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>685.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>619.99</v>
+        <v>609.99</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>689.99</v>
+        <v>686.99</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>619.99</v>
+        <v>696.99</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>459.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc X-Style</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>539.99</v>
+        <v>685.99</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>579.99</v>
+        <v>619.99</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>639.99</v>
+        <v>689.99</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>605.99</v>
+        <v>619.99</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>665.99</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>499.99</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc X-Style</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -4507,637 +4507,637 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>579.99</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>639.99</v>
+        <v>605.99</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>615.99</v>
+        <v>665.99</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>675.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>599.99</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>659.99</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>619.99</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>629.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>729.99</v>
+        <v>675.99</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>816.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>719.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>749.99</v>
+        <v>619.99</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>749.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>761.99</v>
+        <v>729.99</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>851.99</v>
+        <v>816.99</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>927.99</v>
+        <v>719.99</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>840.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>977.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>629.99</v>
+        <v>761.99</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>729.99</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>816.99</v>
+        <v>927.99</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>745.99</v>
+        <v>840.99</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>815.99</v>
+        <v>977.99</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>749.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>819.99</v>
+        <v>729.99</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>559.99</v>
+        <v>816.99</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>659.99</v>
+        <v>745.99</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>746.99</v>
+        <v>815.99</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>675.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>745.99</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>679.99</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>749.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>186.99</v>
+        <v>746.99</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>99.98999999999999</v>
+        <v>675.99</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>99.98999999999999</v>
+        <v>745.99</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Donner DMK-25 Pro Clavier MIDI</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>89.98999999999999</v>
+        <v>679.99</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>236.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
+          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>335.99</v>
+        <v>186.99</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>423.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>219.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
+          <t>Donner DMK-25 Pro Clavier MIDI</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>335.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>423.99</v>
+        <v>236.99</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>281.99</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>373.99</v>
+        <v>423.99</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>530.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>89</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>109.99</v>
+        <v>423.99</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Pour la différence de prix</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>7.69</v>
+        <v>281.99</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>152.99</v>
+        <v>373.99</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>339.99</v>
+        <v>530.99</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
+          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>152.99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>339.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
+          <t>Pour la différence de prix</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>152.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>339.99</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>152.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>339.99</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>86.98999999999999</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>69.98999999999999</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>389.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>479.99</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>479.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>489.99</v>
+        <v>86.98999999999999</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>509.99</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -5147,7 +5147,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -5157,7 +5157,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -5167,7 +5167,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -5177,7 +5177,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -5187,510 +5187,560 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>89.98999999999999</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>79.47</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>89.98999999999999</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>469.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>518.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>566.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>557.99</v>
+        <v>79.47</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>636.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>627.99</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>549.99</v>
+        <v>518.99</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>569.99</v>
+        <v>566.99</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>629.99</v>
+        <v>557.99</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>585.99</v>
+        <v>636.99</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>645.99</v>
+        <v>627.99</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>589.99</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>429.99</v>
+        <v>569.99</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>536.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>527.99</v>
+        <v>585.99</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>606.99</v>
+        <v>645.99</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>597.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>519.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>539.99</v>
+        <v>536.99</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>599.99</v>
+        <v>527.99</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>555.99</v>
+        <v>606.99</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>615.99</v>
+        <v>597.99</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>549.99</v>
+        <v>519.99</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>559.98</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>469.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>518.99</v>
+        <v>555.99</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>566.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>557.99</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>636.99</v>
+        <v>559.98</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>627.99</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>549.99</v>
+        <v>518.99</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>569.99</v>
+        <v>566.99</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>629.99</v>
+        <v>557.99</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>585.99</v>
+        <v>636.99</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>645.99</v>
+        <v>627.99</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>589.99</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>429.99</v>
+        <v>569.99</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>499.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>536.99</v>
+        <v>585.99</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>527.99</v>
+        <v>645.99</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B519" t="n">
-        <v>606.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
         </is>
       </c>
       <c r="B520" t="n">
-        <v>597.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B521" t="n">
-        <v>519.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B522" t="n">
-        <v>539.99</v>
+        <v>536.99</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B523" t="n">
-        <v>599.99</v>
+        <v>527.99</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>555.99</v>
+        <v>606.99</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B525" t="n">
-        <v>615.99</v>
+        <v>597.99</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>519.99</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>539.99</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>599.99</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>555.99</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>615.99</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
           <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
-      <c r="B526" t="n">
+      <c r="B531" t="n">
         <v>549.99</v>
       </c>
     </row>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1257,307 +1257,307 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner BackBeat Batterie Electronique - BackBeat</t>
+          <t>Donner DED-100 Batterie électrique</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>899.99</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>969.99</v>
+        <v>249.99</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Donner DED-100 Batterie électrique</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>399.99</v>
+        <v>329.98</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>249.99</v>
+        <v>329.98</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>329.98</v>
+        <v>359.98</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>329.98</v>
+        <v>319.98</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>359.98</v>
+        <v>399.97</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Tourneur de Page</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir + Tourneur de Page</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>319.98</v>
+        <v>399.97</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>399.97</v>
+        <v>429.97</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir + Tourneur de Page</t>
+          <t>【Boîte ouverte】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>399.97</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>429.97</v>
+        <v>769.99</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>699.99</v>
+        <v>849.98</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>769.99</v>
+        <v>849.98</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>849.98</v>
+        <v>875.98</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + DKB-100 Banc De Piano</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>849.98</v>
+        <v>869.98</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>875.98</v>
+        <v>885.98</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + DKB-100 Banc De Piano</t>
+          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>869.98</v>
+        <v>1099.99</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>885.98</v>
+        <v>1169.99</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1099.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro + Tabouret de batterie DT-50</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1169.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>219.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>489.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>398.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>219.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>489.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>398.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>219.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner Pupitre de batterie</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>489.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + JW Pédale</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Acajou</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>398.99</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Donner Pupitre de batterie</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Noir</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>39.99</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Acajou</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Sunburst</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -1567,47 +1567,47 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Noir</t>
+          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>159.99</v>
+        <v>229.99</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Sunburst</t>
+          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>159.99</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>229.99</v>
+        <v>239.99</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>259.99</v>
+        <v>239.99</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -1617,27 +1617,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>239.99</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>239.99</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -1647,227 +1647,227 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard</t>
+          <t>Donner DAM1000 Audio Mixer</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>259.99</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly</t>
+          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>259.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Donner DAM1000 Audio Mixer</t>
+          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>179.99</v>
+        <v>669.99</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston + Pied</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>599.99</v>
+        <v>165.99</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro + Tabouret de batterie DT-50</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>669.99</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston + Pied</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Pied</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>165.99</v>
+        <v>92.98999999999999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston</t>
+          <t>Donner Go ampli guitare - Donner Go【Noir】</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>72.98999999999999</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Pied</t>
+          <t>Donner Go ampli guitare - Donner Go II【Noir】</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>92.98999999999999</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go【Noir】</t>
+          <t>Donner Go ampli guitare - Donner Go II【Blanc】</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>89.98999999999999</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go II【Noir】</t>
+          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>129.99</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go II【Blanc】</t>
+          <t>【Donner】Pour la différence de prix</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>129.99</v>
+        <v>180</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>69.98999999999999</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>【Donner】Pour la différence de prix</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>180</v>
+        <v>529.99</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>459.99</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>529.99</v>
+        <v>569.99</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>549.99</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>569.99</v>
+        <v>485.99</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>399.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>485.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>489.99</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>509.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>159.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -1877,7 +1877,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -1887,117 +1887,117 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
+          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 4 Cymbales</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>209.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
+          <t>Donner DED-200X Batterie Électronique - Nouvelle 5 Tambours et 4 Cymbales</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>209.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 4 Cymbales</t>
+          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 3 Cymbales</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>499.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - Nouvelle 5 Tambours et 4 Cymbales</t>
+          <t>Donner Beat Go Kit de batterie électronique portable</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>599.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 3 Cymbales</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>589.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Donner Beat Go Kit de batterie électronique portable</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>289.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
+          <t>Donner Table de percussion</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>119.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>119.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Donner Table de percussion</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>39.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>599.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>699.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -2007,767 +2007,767 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>599.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Bleu clair</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>699.99</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Rose clair</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>699.99</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Bleu clair</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Bleu clair</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>69.98999999999999</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Rose clair</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Rose clair</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>69.98999999999999</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Bleu clair</t>
+          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>89.98999999999999</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Rose clair</t>
+          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>89.98999999999999</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
+          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>269.99</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>149.99</v>
+        <v>329.99</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>129.99</v>
+        <v>419.99</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>329.99</v>
+        <v>419.99</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>419.99</v>
+        <v>432.99</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>419.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>432.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>489.99</v>
+        <v>502.99</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>489.99</v>
+        <v>449.99</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>502.99</v>
+        <v>829.99</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>449.99</v>
+        <v>909.99</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>829.99</v>
+        <v>925.99</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>909.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>925.99</v>
+        <v>979.99</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>899.99</v>
+        <v>999.99</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Eastar EDA-100 Digital Aerophone Noir</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>979.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>999.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Eastar EDA-100 Digital Aerophone Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>119.99</v>
+        <v>341.99</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>299.99</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + MH1 Casque</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>341.99</v>
+        <v>419.98</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>418.99</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>419.98</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>369.98</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>369.98</v>
+        <v>341.99</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>299.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + MH1 Casque</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>341.99</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>398.99</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>399.98</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>352.98</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>352.98</v>
+        <v>322.99</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>279.99</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + MH1 Casque</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>322.99</v>
+        <v>419.98</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>418.99</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>419.98</v>
+        <v>369.98</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>369.98</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>369.98</v>
+        <v>341.99</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>299.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + MH1 Casque</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>341.99</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>398.99</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>399.98</v>
+        <v>352.98</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>352.98</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>352.98</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
+          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>99.98999999999999</v>
+        <v>126.99</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
+          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>99.98999999999999</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>126.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>62.99</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
+          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>59.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>56.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>119.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>Donner Banquette Piano Duo Réglable Confort</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>284.99</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>Donner M100 Casque de monitoring studio</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>284.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable Confort</t>
+          <t>Donner DEP-08 Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>115.99</v>
+        <v>229.99</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Donner M100 Casque de monitoring studio</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>59.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>229.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>319.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>319.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>199.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>289.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>299.99</v>
+        <v>367.99</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>299.99</v>
+        <v>392.99</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
+          <t>Donner DED-70 Batterie Electronique - DED-70</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>367.99</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
+          <t>Donner DED-70 Batterie Electronique - DED-70 + MH1 Casque + Plateau pour batterie</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>392.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie Electronique - DED-70</t>
+          <t>Donner DED-80 Batterie électrique - Noir</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>199.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie Electronique - DED-70 + MH1 Casque + Plateau pour batterie</t>
+          <t>Donner DED-80 Batterie électrique - Blanc</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>284.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Noir</t>
+          <t>Donner Essential L1 Synthétiseur - L1</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>219.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Blanc</t>
+          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>219.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - L1</t>
+          <t>Donner Essential L1 Synthétiseur - Pack</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>279.99</v>
+        <v>399.98</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>119.99</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - Pack</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>399.98</v>
+        <v>799.99</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -2777,157 +2777,157 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
+          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>799.99</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>799.99</v>
+        <v>409.99</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>102.99</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>409.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>498.99</v>
+        <v>409.99</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>499.98</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>409.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>498.99</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>499.98</v>
+        <v>498.99</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>399.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>498.99</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>499.98</v>
+        <v>474.99</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>399.99</v>
+        <v>499.98</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>474.99</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>499.98</v>
+        <v>899.99</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -2937,7 +2937,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -2947,7 +2947,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -2957,7 +2957,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -2967,337 +2967,337 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>899.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>899.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>109.99</v>
+        <v>446.99</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>359.99</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>446.99</v>
+        <v>584.99</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>549.98</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>584.99</v>
+        <v>446.99</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>359.99</v>
+        <v>549.98</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>446.99</v>
+        <v>584.99</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>Donner DED-300X Batterie Electronique</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>549.98</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>584.99</v>
+        <v>130.99</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Donner DED-300X Batterie Electronique</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>539.99</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>130.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>129.99</v>
+        <v>769.99</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>659.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>769.99</v>
+        <v>839.99</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>749.99</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>839.99</v>
+        <v>775.99</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>819.99</v>
+        <v>779.99</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>775.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>779.99</v>
+        <v>769.99</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>659.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>769.99</v>
+        <v>839.99</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>749.99</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>839.99</v>
+        <v>775.99</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>819.99</v>
+        <v>779.99</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
+          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>775.99</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>779.99</v>
+        <v>92.98999999999999</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>102.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
+          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>92.98999999999999</v>
+        <v>99</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
+          <t>Donner DT-50 Tabouret de Batterie</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>109.99</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
+          <t>Donner DST-550 Guitare Électrique - Bleu</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Donner DT-50 Tabouret de Batterie</t>
+          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>72.98999999999999</v>
+        <v>199.99</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Bleu</t>
+          <t>Donner DST-550 Guitare Électrique - Blanc</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -3307,37 +3307,37 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>199.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Blanc</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>169.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>289.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -3347,917 +3347,917 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>279.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>379.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>389.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>489.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>509.99</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>389.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>479.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>509.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>209.99</v>
+        <v>315.99</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>284.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>315.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>309.99</v>
+        <v>385.99</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>359.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>385.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>379.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>319.99</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>389.99</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>179.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>269.99</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>279.99</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>289.99</v>
+        <v>349.99</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>339.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>349.99</v>
+        <v>295.99</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>359.99</v>
+        <v>365.99</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>295.99</v>
+        <v>189.99</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>365.99</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>189.99</v>
+        <v>279.99</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>269.99</v>
+        <v>282.99</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>279.99</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>282.99</v>
+        <v>343.99</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>335.99</v>
+        <v>352.99</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>343.99</v>
+        <v>285.99</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>352.99</v>
+        <v>355.99</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>285.99</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>355.99</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>209.99</v>
+        <v>315.99</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>284.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>315.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>309.99</v>
+        <v>385.99</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>359.99</v>
+        <v>379.99</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>385.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>379.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>319.99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>389.99</v>
+        <v>239.99</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>169.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>239.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>359.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>496.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>309.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>496.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>359.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>496.99</v>
+        <v>359.99</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>359.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>496.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>309.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>496.99</v>
+        <v>309.99</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>309.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DED-200 Max Batteries Electroniques</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>496.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>408.99</v>
+        <v>1099.99</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Donner DED-200 Max Batteries Electroniques</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>499.99</v>
+        <v>1114.99</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>1099.99</v>
+        <v>899</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>1114.99</v>
+        <v>995.99</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
+          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>899</v>
+        <v>998.99</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>995.99</v>
+        <v>125.99</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>998.99</v>
+        <v>166.99</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>125.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>166.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>299.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>486.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>398.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>299.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>486.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>398.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>299.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>486.99</v>
+        <v>299.99</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>398.99</v>
+        <v>486.99</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>299.99</v>
+        <v>398.99</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>486.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>398.99</v>
+        <v>319.99</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>109.99</v>
+        <v>408.99</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>319.99</v>
+        <v>419.99</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>408.99</v>
+        <v>419.99</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>419.99</v>
+        <v>435.99</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>419.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>435.99</v>
+        <v>439.99</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>489.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -4267,87 +4267,87 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>509.99</v>
+        <v>329.99</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>439.99</v>
+        <v>418.99</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>329.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>418.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>429.99</v>
+        <v>445.99</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>429.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>445.99</v>
+        <v>449.99</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>499.99</v>
+        <v>519.99</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -4357,97 +4357,97 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>519.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>449.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>499.99</v>
+        <v>609.99</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>599.99</v>
+        <v>686.99</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>609.99</v>
+        <v>696.99</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>686.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>696.99</v>
+        <v>685.99</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>615.99</v>
+        <v>619.99</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>685.99</v>
+        <v>689.99</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -4457,587 +4457,587 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>689.99</v>
+        <v>459.99</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>619.99</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>459.99</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc X-Style</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>539.99</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>579.99</v>
+        <v>605.99</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>639.99</v>
+        <v>665.99</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>605.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>665.99</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>499.99</v>
+        <v>579.99</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc X-Style</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>579.99</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>579.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>639.99</v>
+        <v>675.99</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>615.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>675.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc</t>
+          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>599.99</v>
+        <v>619.99</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>659.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>619.99</v>
+        <v>729.99</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>629.99</v>
+        <v>816.99</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>729.99</v>
+        <v>719.99</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>816.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>719.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>749.99</v>
+        <v>761.99</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>749.99</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>761.99</v>
+        <v>927.99</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>851.99</v>
+        <v>840.99</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>927.99</v>
+        <v>977.99</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>840.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>977.99</v>
+        <v>729.99</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>629.99</v>
+        <v>816.99</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>729.99</v>
+        <v>745.99</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>816.99</v>
+        <v>815.99</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>745.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>815.99</v>
+        <v>819.99</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>749.99</v>
+        <v>559.99</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>819.99</v>
+        <v>659.99</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>559.99</v>
+        <v>746.99</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>659.99</v>
+        <v>675.99</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>746.99</v>
+        <v>745.99</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>675.99</v>
+        <v>679.99</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>745.99</v>
+        <v>749.99</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>679.99</v>
+        <v>186.99</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>749.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>186.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
+          <t>Donner DMK-25 Pro Clavier MIDI</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>99.98999999999999</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>99.98999999999999</v>
+        <v>236.99</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Donner DMK-25 Pro Clavier MIDI</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>89.98999999999999</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>236.99</v>
+        <v>423.99</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>335.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>423.99</v>
+        <v>335.99</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>219.99</v>
+        <v>423.99</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>335.99</v>
+        <v>281.99</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>423.99</v>
+        <v>373.99</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>281.99</v>
+        <v>530.99</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
+          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>373.99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>530.99</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
+          <t>Pour la différence de prix</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>89</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>109.99</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Pour la différence de prix</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>7.69</v>
+        <v>339.99</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -5047,7 +5047,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -5057,7 +5057,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -5067,7 +5067,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -5077,7 +5077,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -5087,7 +5087,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -5097,147 +5097,147 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>152.99</v>
+        <v>86.98999999999999</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>339.99</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>86.98999999999999</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>69.98999999999999</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>389.99</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>479.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>479.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>489.99</v>
+        <v>389.99</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>509.99</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>389.99</v>
+        <v>479.99</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>479.99</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>479.99</v>
+        <v>509.99</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>489.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>509.99</v>
+        <v>79.47</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -5247,500 +5247,480 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>79.47</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>89.98999999999999</v>
+        <v>518.99</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>469.99</v>
+        <v>566.99</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>518.99</v>
+        <v>557.99</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>566.99</v>
+        <v>636.99</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>557.99</v>
+        <v>627.99</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>636.99</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>627.99</v>
+        <v>569.99</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>549.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>569.99</v>
+        <v>585.99</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>629.99</v>
+        <v>645.99</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>585.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>645.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>589.99</v>
+        <v>536.99</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>429.99</v>
+        <v>527.99</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>536.99</v>
+        <v>606.99</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>527.99</v>
+        <v>597.99</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>606.99</v>
+        <v>519.99</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>597.99</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>519.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>539.99</v>
+        <v>555.99</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>599.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>555.99</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>615.99</v>
+        <v>559.98</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>549.99</v>
+        <v>469.99</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>559.98</v>
+        <v>518.99</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>469.99</v>
+        <v>566.99</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>518.99</v>
+        <v>557.99</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>566.99</v>
+        <v>636.99</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>557.99</v>
+        <v>627.99</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>636.99</v>
+        <v>549.99</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>627.99</v>
+        <v>569.99</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>549.99</v>
+        <v>629.99</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>569.99</v>
+        <v>585.99</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>629.99</v>
+        <v>645.99</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>585.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>645.99</v>
+        <v>429.99</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B519" t="n">
-        <v>589.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B520" t="n">
-        <v>429.99</v>
+        <v>536.99</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B521" t="n">
-        <v>499.99</v>
+        <v>527.99</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B522" t="n">
-        <v>536.99</v>
+        <v>606.99</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B523" t="n">
-        <v>527.99</v>
+        <v>597.99</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>606.99</v>
+        <v>519.99</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B525" t="n">
-        <v>597.99</v>
+        <v>539.99</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B526" t="n">
-        <v>519.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B527" t="n">
-        <v>539.99</v>
+        <v>555.99</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B528" t="n">
-        <v>599.99</v>
+        <v>615.99</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B529" t="n">
-        <v>555.99</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
-        </is>
-      </c>
-      <c r="B530" t="n">
-        <v>615.99</v>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
-        </is>
-      </c>
-      <c r="B531" t="n">
         <v>549.99</v>
       </c>
     </row>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -677,21 +677,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Donner SD-15 Clavier électronique 61 touches - Nur das Keyboard</t>
+          <t>Donner SD-15 Clavier électronique 61 touches - Bundle mit Zubehör</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>169.99</v>
+        <v>219.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Donner SD-15 Clavier électronique 61 touches - Bundle mit Zubehör</t>
+          <t>Donner SD-15 Clavier électronique 61 touches - Nur das Keyboard</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>219.99</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="27">
@@ -2747,7 +2747,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -2757,7 +2757,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -2767,7 +2767,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -2907,7 +2907,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -2917,7 +2917,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -2927,7 +2927,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -2937,7 +2937,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -2947,7 +2947,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -2957,7 +2957,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>【Piano + banc gratuit】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -3997,7 +3997,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -4007,21 +4007,21 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>995.99</v>
+        <v>899</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>998.99</v>
+        <v>899</v>
       </c>
     </row>
     <row r="360">

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -2677,7 +2677,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie Electronique - DED-70</t>
+          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -2687,7 +2687,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie Electronique - DED-70 + MH1 Casque + Plateau pour batterie</t>
+          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70 + MH1 Casque + Plateau pour batterie</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -2697,7 +2697,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Noir</t>
+          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Noir</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -2707,7 +2707,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électrique - Blanc</t>
+          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Blanc</t>
         </is>
       </c>
       <c r="B228" t="n">

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -425,11 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:C529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -443,6 +444,11 @@
           <t>Prix TTC (€)</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>URL du produit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -453,6 +459,11 @@
       <c r="B2" t="n">
         <v>399.99</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-viva-stringless-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -463,6 +474,11 @@
       <c r="B3" t="n">
         <v>259.99</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dka-50-50w-keyboard-amplifier</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -473,6 +489,11 @@
       <c r="B4" t="n">
         <v>119.99</v>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura-piano-bench-s200</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -483,6 +504,11 @@
       <c r="B5" t="n">
         <v>729.99</v>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,6 +519,11 @@
       <c r="B6" t="n">
         <v>822.99</v>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -503,6 +534,11 @@
       <c r="B7" t="n">
         <v>839.99</v>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -513,6 +549,11 @@
       <c r="B8" t="n">
         <v>729.99</v>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -523,6 +564,11 @@
       <c r="B9" t="n">
         <v>822.99</v>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -533,6 +579,11 @@
       <c r="B10" t="n">
         <v>829.99</v>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -543,6 +594,11 @@
       <c r="B11" t="n">
         <v>529.99</v>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -553,6 +609,11 @@
       <c r="B12" t="n">
         <v>579.99</v>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -563,6 +624,11 @@
       <c r="B13" t="n">
         <v>579.99</v>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -573,6 +639,11 @@
       <c r="B14" t="n">
         <v>615.99</v>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -583,6 +654,11 @@
       <c r="B15" t="n">
         <v>599.99</v>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -593,6 +669,11 @@
       <c r="B16" t="n">
         <v>229.99</v>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-mamp8-5-2-channel-av-receiver</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -603,6 +684,11 @@
       <c r="B17" t="n">
         <v>699.99</v>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -613,6 +699,11 @@
       <c r="B18" t="n">
         <v>799.99</v>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -623,6 +714,11 @@
       <c r="B19" t="n">
         <v>799.99</v>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -633,6 +729,11 @@
       <c r="B20" t="n">
         <v>819.99</v>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,6 +744,11 @@
       <c r="B21" t="n">
         <v>779.99</v>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -653,6 +759,11 @@
       <c r="B22" t="n">
         <v>79.98999999999999</v>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -663,6 +774,11 @@
       <c r="B23" t="n">
         <v>79.98999999999999</v>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -673,6 +789,11 @@
       <c r="B24" t="n">
         <v>79.98999999999999</v>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -683,6 +804,11 @@
       <c r="B25" t="n">
         <v>219.99</v>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-sd-15-61-key-electronic-keyboard</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -693,6 +819,11 @@
       <c r="B26" t="n">
         <v>169.99</v>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-sd-15-61-key-electronic-keyboard</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -703,6 +834,11 @@
       <c r="B27" t="n">
         <v>79.98999999999999</v>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-starrypad-pro-midi-controller</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -713,6 +849,11 @@
       <c r="B28" t="n">
         <v>59.99</v>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-mh1-sound-monitor-headphones</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -723,6 +864,11 @@
       <c r="B29" t="n">
         <v>39.99</v>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-88-key-keyboard-gig-bag</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -733,6 +879,11 @@
       <c r="B30" t="n">
         <v>439.99</v>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -743,6 +894,11 @@
       <c r="B31" t="n">
         <v>439.99</v>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -753,6 +909,11 @@
       <c r="B32" t="n">
         <v>635.99</v>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -763,6 +924,11 @@
       <c r="B33" t="n">
         <v>199.99</v>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -773,6 +939,11 @@
       <c r="B34" t="n">
         <v>119.99</v>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -783,6 +954,11 @@
       <c r="B35" t="n">
         <v>319.99</v>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -793,6 +969,11 @@
       <c r="B36" t="n">
         <v>259.99</v>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -803,6 +984,11 @@
       <c r="B37" t="n">
         <v>459.99</v>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -813,6 +999,11 @@
       <c r="B38" t="n">
         <v>358.99</v>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -823,6 +1014,11 @@
       <c r="B39" t="n">
         <v>259.99</v>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -833,6 +1029,11 @@
       <c r="B40" t="n">
         <v>459.99</v>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -843,6 +1044,11 @@
       <c r="B41" t="n">
         <v>358.99</v>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -853,6 +1059,11 @@
       <c r="B42" t="n">
         <v>259.99</v>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -863,6 +1074,11 @@
       <c r="B43" t="n">
         <v>459.99</v>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -873,6 +1089,11 @@
       <c r="B44" t="n">
         <v>358.99</v>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -883,6 +1104,11 @@
       <c r="B45" t="n">
         <v>259.99</v>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -893,6 +1119,11 @@
       <c r="B46" t="n">
         <v>459.99</v>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -903,6 +1134,11 @@
       <c r="B47" t="n">
         <v>358.99</v>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -913,6 +1149,11 @@
       <c r="B48" t="n">
         <v>429.99</v>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ded-200max-batteries-electroniques</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -923,6 +1164,11 @@
       <c r="B49" t="n">
         <v>259.99</v>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -933,6 +1179,11 @@
       <c r="B50" t="n">
         <v>259.99</v>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -943,6 +1194,11 @@
       <c r="B51" t="n">
         <v>749.99</v>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -953,6 +1209,11 @@
       <c r="B52" t="n">
         <v>852.99</v>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -963,6 +1224,11 @@
       <c r="B53" t="n">
         <v>839.99</v>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -973,6 +1239,11 @@
       <c r="B54" t="n">
         <v>369.99</v>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -983,6 +1254,11 @@
       <c r="B55" t="n">
         <v>459.99</v>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -993,6 +1269,11 @@
       <c r="B56" t="n">
         <v>472.99</v>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1003,6 +1284,11 @@
       <c r="B57" t="n">
         <v>489.99</v>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1013,6 +1299,11 @@
       <c r="B58" t="n">
         <v>369.99</v>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1023,6 +1314,11 @@
       <c r="B59" t="n">
         <v>469.99</v>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1033,6 +1329,11 @@
       <c r="B60" t="n">
         <v>472.99</v>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1043,6 +1344,11 @@
       <c r="B61" t="n">
         <v>489.99</v>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1053,6 +1359,11 @@
       <c r="B62" t="n">
         <v>499.99</v>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1063,6 +1374,11 @@
       <c r="B63" t="n">
         <v>599.99</v>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1073,6 +1389,11 @@
       <c r="B64" t="n">
         <v>609.99</v>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1083,6 +1404,11 @@
       <c r="B65" t="n">
         <v>309.99</v>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1093,6 +1419,11 @@
       <c r="B66" t="n">
         <v>408.99</v>
       </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1103,6 +1434,11 @@
       <c r="B67" t="n">
         <v>509.99</v>
       </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1113,6 +1449,11 @@
       <c r="B68" t="n">
         <v>309.99</v>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1123,6 +1464,11 @@
       <c r="B69" t="n">
         <v>408.99</v>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1133,6 +1479,11 @@
       <c r="B70" t="n">
         <v>509.99</v>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1143,6 +1494,11 @@
       <c r="B71" t="n">
         <v>309.99</v>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1153,6 +1509,11 @@
       <c r="B72" t="n">
         <v>408.99</v>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1163,6 +1524,11 @@
       <c r="B73" t="n">
         <v>509.99</v>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1173,6 +1539,11 @@
       <c r="B74" t="n">
         <v>309.99</v>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1183,6 +1554,11 @@
       <c r="B75" t="n">
         <v>408.99</v>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1193,6 +1569,11 @@
       <c r="B76" t="n">
         <v>509.99</v>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1203,6 +1584,11 @@
       <c r="B77" t="n">
         <v>309.99</v>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1213,6 +1599,11 @@
       <c r="B78" t="n">
         <v>408.99</v>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1223,6 +1614,11 @@
       <c r="B79" t="n">
         <v>509.99</v>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1233,6 +1629,11 @@
       <c r="B80" t="n">
         <v>309.99</v>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1243,6 +1644,11 @@
       <c r="B81" t="n">
         <v>408.99</v>
       </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1253,6 +1659,11 @@
       <c r="B82" t="n">
         <v>509.99</v>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1263,6 +1674,11 @@
       <c r="B83" t="n">
         <v>399.99</v>
       </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ded-100-drum-set</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1273,6 +1689,11 @@
       <c r="B84" t="n">
         <v>249.99</v>
       </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1283,6 +1704,11 @@
       <c r="B85" t="n">
         <v>329.98</v>
       </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1293,6 +1719,11 @@
       <c r="B86" t="n">
         <v>329.98</v>
       </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1303,6 +1734,11 @@
       <c r="B87" t="n">
         <v>359.98</v>
       </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1313,6 +1749,11 @@
       <c r="B88" t="n">
         <v>319.98</v>
       </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1323,6 +1764,11 @@
       <c r="B89" t="n">
         <v>399.97</v>
       </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1333,6 +1779,11 @@
       <c r="B90" t="n">
         <v>399.97</v>
       </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1343,6 +1794,11 @@
       <c r="B91" t="n">
         <v>429.97</v>
       </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1353,6 +1809,11 @@
       <c r="B92" t="n">
         <v>699.99</v>
       </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s300-domestique-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1363,6 +1824,11 @@
       <c r="B93" t="n">
         <v>769.99</v>
       </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1373,6 +1839,11 @@
       <c r="B94" t="n">
         <v>849.98</v>
       </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1383,6 +1854,11 @@
       <c r="B95" t="n">
         <v>849.98</v>
       </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1393,6 +1869,11 @@
       <c r="B96" t="n">
         <v>875.98</v>
       </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1403,6 +1884,11 @@
       <c r="B97" t="n">
         <v>869.98</v>
       </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1413,6 +1899,11 @@
       <c r="B98" t="n">
         <v>885.98</v>
       </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1423,6 +1914,11 @@
       <c r="B99" t="n">
         <v>1099.99</v>
       </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1433,6 +1929,11 @@
       <c r="B100" t="n">
         <v>1169.99</v>
       </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1443,6 +1944,11 @@
       <c r="B101" t="n">
         <v>219.99</v>
       </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1453,6 +1959,11 @@
       <c r="B102" t="n">
         <v>489.99</v>
       </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1463,6 +1974,11 @@
       <c r="B103" t="n">
         <v>398.99</v>
       </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1473,6 +1989,11 @@
       <c r="B104" t="n">
         <v>219.99</v>
       </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1483,6 +2004,11 @@
       <c r="B105" t="n">
         <v>489.99</v>
       </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1493,6 +2019,11 @@
       <c r="B106" t="n">
         <v>398.99</v>
       </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1503,6 +2034,11 @@
       <c r="B107" t="n">
         <v>219.99</v>
       </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1513,6 +2049,11 @@
       <c r="B108" t="n">
         <v>489.99</v>
       </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1523,6 +2064,11 @@
       <c r="B109" t="n">
         <v>398.99</v>
       </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1533,6 +2079,11 @@
       <c r="B110" t="n">
         <v>39.99</v>
       </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-drum-music-stand</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1543,6 +2094,11 @@
       <c r="B111" t="n">
         <v>159.99</v>
       </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1553,6 +2109,11 @@
       <c r="B112" t="n">
         <v>159.99</v>
       </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1563,6 +2124,11 @@
       <c r="B113" t="n">
         <v>159.99</v>
       </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1573,6 +2139,11 @@
       <c r="B114" t="n">
         <v>229.99</v>
       </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1583,6 +2154,11 @@
       <c r="B115" t="n">
         <v>259.99</v>
       </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1593,6 +2169,11 @@
       <c r="B116" t="n">
         <v>239.99</v>
       </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1603,6 +2184,11 @@
       <c r="B117" t="n">
         <v>239.99</v>
       </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1613,6 +2199,11 @@
       <c r="B118" t="n">
         <v>239.99</v>
       </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1623,6 +2214,11 @@
       <c r="B119" t="n">
         <v>259.99</v>
       </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1633,6 +2229,11 @@
       <c r="B120" t="n">
         <v>259.99</v>
       </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1643,6 +2244,11 @@
       <c r="B121" t="n">
         <v>259.99</v>
       </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1653,6 +2259,11 @@
       <c r="B122" t="n">
         <v>179.99</v>
       </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dam1000-audio-mixer</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1663,6 +2274,11 @@
       <c r="B123" t="n">
         <v>599.99</v>
       </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1673,6 +2289,11 @@
       <c r="B124" t="n">
         <v>669.99</v>
       </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1683,6 +2304,11 @@
       <c r="B125" t="n">
         <v>165.99</v>
       </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1693,6 +2319,11 @@
       <c r="B126" t="n">
         <v>72.98999999999999</v>
       </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1703,6 +2334,11 @@
       <c r="B127" t="n">
         <v>92.98999999999999</v>
       </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1713,6 +2349,11 @@
       <c r="B128" t="n">
         <v>89.98999999999999</v>
       </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1723,6 +2364,11 @@
       <c r="B129" t="n">
         <v>129.99</v>
       </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1733,6 +2379,11 @@
       <c r="B130" t="n">
         <v>129.99</v>
       </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1743,6 +2394,11 @@
       <c r="B131" t="n">
         <v>69.98999999999999</v>
       </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/starrycrtl-midi-controller-black</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1753,6 +2409,11 @@
       <c r="B132" t="n">
         <v>180</v>
       </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-pour-la-difference-de-prix</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1763,6 +2424,11 @@
       <c r="B133" t="n">
         <v>459.99</v>
       </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1773,6 +2439,11 @@
       <c r="B134" t="n">
         <v>529.99</v>
       </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1783,6 +2454,11 @@
       <c r="B135" t="n">
         <v>549.99</v>
       </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1793,6 +2469,11 @@
       <c r="B136" t="n">
         <v>569.99</v>
       </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1803,6 +2484,11 @@
       <c r="B137" t="n">
         <v>399.99</v>
       </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1813,6 +2499,11 @@
       <c r="B138" t="n">
         <v>485.99</v>
       </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1823,6 +2514,11 @@
       <c r="B139" t="n">
         <v>489.99</v>
       </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1833,6 +2529,11 @@
       <c r="B140" t="n">
         <v>509.99</v>
       </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1843,6 +2544,11 @@
       <c r="B141" t="n">
         <v>159.99</v>
       </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-cv-3-wireless-in-ear-monitoring-system</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1853,6 +2559,11 @@
       <c r="B142" t="n">
         <v>209.99</v>
       </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1863,6 +2574,11 @@
       <c r="B143" t="n">
         <v>209.99</v>
       </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1873,6 +2589,11 @@
       <c r="B144" t="n">
         <v>209.99</v>
       </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1883,6 +2604,11 @@
       <c r="B145" t="n">
         <v>209.99</v>
       </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1893,6 +2619,11 @@
       <c r="B146" t="n">
         <v>499.99</v>
       </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1903,6 +2634,11 @@
       <c r="B147" t="n">
         <v>599.99</v>
       </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1913,6 +2649,11 @@
       <c r="B148" t="n">
         <v>589.99</v>
       </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1923,6 +2664,11 @@
       <c r="B149" t="n">
         <v>289.99</v>
       </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-beat-go-portable-electronic-drum-kit</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1933,6 +2679,11 @@
       <c r="B150" t="n">
         <v>119.99</v>
       </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1943,6 +2694,11 @@
       <c r="B151" t="n">
         <v>119.99</v>
       </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1953,6 +2709,11 @@
       <c r="B152" t="n">
         <v>39.99</v>
       </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-percussion-table</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -1963,6 +2724,11 @@
       <c r="B153" t="n">
         <v>599.99</v>
       </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -1973,6 +2739,11 @@
       <c r="B154" t="n">
         <v>699.99</v>
       </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -1983,6 +2754,11 @@
       <c r="B155" t="n">
         <v>699.99</v>
       </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -1993,6 +2769,11 @@
       <c r="B156" t="n">
         <v>599.99</v>
       </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2003,6 +2784,11 @@
       <c r="B157" t="n">
         <v>699.99</v>
       </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2013,6 +2799,11 @@
       <c r="B158" t="n">
         <v>699.99</v>
       </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2023,6 +2814,11 @@
       <c r="B159" t="n">
         <v>69.98999999999999</v>
       </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2033,6 +2829,11 @@
       <c r="B160" t="n">
         <v>69.98999999999999</v>
       </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2043,6 +2844,11 @@
       <c r="B161" t="n">
         <v>89.98999999999999</v>
       </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2053,6 +2859,11 @@
       <c r="B162" t="n">
         <v>89.98999999999999</v>
       </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2063,6 +2874,11 @@
       <c r="B163" t="n">
         <v>269.99</v>
       </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ded-70l-electronic-drum-kit-with-led-light</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2073,6 +2889,11 @@
       <c r="B164" t="n">
         <v>149.99</v>
       </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-starrykey-37-play-midi-controller</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2083,6 +2904,11 @@
       <c r="B165" t="n">
         <v>129.99</v>
       </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dda-20se-drum-monitor-speaker</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2093,6 +2919,11 @@
       <c r="B166" t="n">
         <v>329.99</v>
       </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2103,6 +2934,11 @@
       <c r="B167" t="n">
         <v>419.99</v>
       </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2113,6 +2949,11 @@
       <c r="B168" t="n">
         <v>419.99</v>
       </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2123,6 +2964,11 @@
       <c r="B169" t="n">
         <v>432.99</v>
       </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2133,6 +2979,11 @@
       <c r="B170" t="n">
         <v>489.99</v>
       </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2143,6 +2994,11 @@
       <c r="B171" t="n">
         <v>489.99</v>
       </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2153,6 +3009,11 @@
       <c r="B172" t="n">
         <v>502.99</v>
       </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2163,6 +3024,11 @@
       <c r="B173" t="n">
         <v>449.99</v>
       </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2173,6 +3039,11 @@
       <c r="B174" t="n">
         <v>829.99</v>
       </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2183,6 +3054,11 @@
       <c r="B175" t="n">
         <v>909.99</v>
       </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2193,6 +3069,11 @@
       <c r="B176" t="n">
         <v>925.99</v>
       </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2203,6 +3084,11 @@
       <c r="B177" t="n">
         <v>899.99</v>
       </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2213,6 +3099,11 @@
       <c r="B178" t="n">
         <v>979.99</v>
       </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2223,6 +3114,11 @@
       <c r="B179" t="n">
         <v>999.99</v>
       </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2233,6 +3129,11 @@
       <c r="B180" t="n">
         <v>119.99</v>
       </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/eastar-digital-aerophone-eda-100-noir</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2243,6 +3144,11 @@
       <c r="B181" t="n">
         <v>299.99</v>
       </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2253,6 +3159,11 @@
       <c r="B182" t="n">
         <v>341.99</v>
       </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2263,6 +3174,11 @@
       <c r="B183" t="n">
         <v>418.99</v>
       </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2273,6 +3189,11 @@
       <c r="B184" t="n">
         <v>419.98</v>
       </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2283,6 +3204,11 @@
       <c r="B185" t="n">
         <v>369.98</v>
       </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2293,6 +3219,11 @@
       <c r="B186" t="n">
         <v>369.98</v>
       </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2303,6 +3234,11 @@
       <c r="B187" t="n">
         <v>299.99</v>
       </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2313,6 +3249,11 @@
       <c r="B188" t="n">
         <v>341.99</v>
       </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2323,6 +3264,11 @@
       <c r="B189" t="n">
         <v>398.99</v>
       </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2333,6 +3279,11 @@
       <c r="B190" t="n">
         <v>399.98</v>
       </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2343,6 +3294,11 @@
       <c r="B191" t="n">
         <v>352.98</v>
       </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2353,6 +3309,11 @@
       <c r="B192" t="n">
         <v>352.98</v>
       </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2363,6 +3324,11 @@
       <c r="B193" t="n">
         <v>279.99</v>
       </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2373,6 +3339,11 @@
       <c r="B194" t="n">
         <v>322.99</v>
       </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2383,6 +3354,11 @@
       <c r="B195" t="n">
         <v>418.99</v>
       </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2393,6 +3369,11 @@
       <c r="B196" t="n">
         <v>419.98</v>
       </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2403,6 +3384,11 @@
       <c r="B197" t="n">
         <v>369.98</v>
       </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2413,6 +3399,11 @@
       <c r="B198" t="n">
         <v>369.98</v>
       </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2423,6 +3414,11 @@
       <c r="B199" t="n">
         <v>299.99</v>
       </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2433,6 +3429,11 @@
       <c r="B200" t="n">
         <v>341.99</v>
       </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2443,6 +3444,11 @@
       <c r="B201" t="n">
         <v>398.99</v>
       </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2453,6 +3459,11 @@
       <c r="B202" t="n">
         <v>399.98</v>
       </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2463,6 +3474,11 @@
       <c r="B203" t="n">
         <v>352.98</v>
       </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2473,6 +3489,11 @@
       <c r="B204" t="n">
         <v>352.98</v>
       </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2483,6 +3504,11 @@
       <c r="B205" t="n">
         <v>99.98999999999999</v>
       </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dks-200-heavy-duty-keyboard-stand-black</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2493,6 +3519,11 @@
       <c r="B206" t="n">
         <v>99.98999999999999</v>
       </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-pocket-go-portable-preset-pedal-multi-effects-processor-for-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2503,6 +3534,11 @@
       <c r="B207" t="n">
         <v>126.99</v>
       </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-mamp2-2-channel-amplifier</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2513,6 +3549,11 @@
       <c r="B208" t="n">
         <v>62.99</v>
       </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/starrypad-mini-midi-controller</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2523,6 +3564,11 @@
       <c r="B209" t="n">
         <v>59.99</v>
       </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2533,6 +3579,11 @@
       <c r="B210" t="n">
         <v>56.99</v>
       </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2543,6 +3594,11 @@
       <c r="B211" t="n">
         <v>119.99</v>
       </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-duet-adjustable-height-piano-bench-with-music-storage-black</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2553,6 +3609,11 @@
       <c r="B212" t="n">
         <v>284.99</v>
       </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2563,6 +3624,11 @@
       <c r="B213" t="n">
         <v>284.99</v>
       </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2573,6 +3639,11 @@
       <c r="B214" t="n">
         <v>115.99</v>
       </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench-brown-matt</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2583,6 +3654,11 @@
       <c r="B215" t="n">
         <v>59.99</v>
       </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-m100-studio-monitor-headphones</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2593,6 +3669,11 @@
       <c r="B216" t="n">
         <v>229.99</v>
       </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2603,6 +3684,11 @@
       <c r="B217" t="n">
         <v>319.99</v>
       </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2613,6 +3699,11 @@
       <c r="B218" t="n">
         <v>319.99</v>
       </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2623,6 +3714,11 @@
       <c r="B219" t="n">
         <v>199.99</v>
       </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2633,6 +3729,11 @@
       <c r="B220" t="n">
         <v>289.99</v>
       </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -2643,6 +3744,11 @@
       <c r="B221" t="n">
         <v>299.99</v>
       </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -2653,6 +3759,11 @@
       <c r="B222" t="n">
         <v>299.99</v>
       </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -2663,6 +3774,11 @@
       <c r="B223" t="n">
         <v>367.99</v>
       </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -2673,6 +3789,11 @@
       <c r="B224" t="n">
         <v>392.99</v>
       </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -2683,6 +3804,11 @@
       <c r="B225" t="n">
         <v>199.99</v>
       </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -2693,6 +3819,11 @@
       <c r="B226" t="n">
         <v>284.99</v>
       </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -2703,6 +3834,11 @@
       <c r="B227" t="n">
         <v>219.99</v>
       </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -2713,6 +3849,11 @@
       <c r="B228" t="n">
         <v>219.99</v>
       </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -2723,6 +3864,11 @@
       <c r="B229" t="n">
         <v>279.99</v>
       </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -2733,6 +3879,11 @@
       <c r="B230" t="n">
         <v>119.99</v>
       </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -2743,6 +3894,11 @@
       <c r="B231" t="n">
         <v>399.98</v>
       </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -2753,6 +3909,11 @@
       <c r="B232" t="n">
         <v>799.99</v>
       </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -2763,6 +3924,11 @@
       <c r="B233" t="n">
         <v>799.99</v>
       </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -2773,6 +3939,11 @@
       <c r="B234" t="n">
         <v>799.99</v>
       </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -2783,6 +3954,11 @@
       <c r="B235" t="n">
         <v>102.99</v>
       </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dkb-100-home-style-solid-wood-piano-bench</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -2793,6 +3969,11 @@
       <c r="B236" t="n">
         <v>409.99</v>
       </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -2803,6 +3984,11 @@
       <c r="B237" t="n">
         <v>498.99</v>
       </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -2813,6 +3999,11 @@
       <c r="B238" t="n">
         <v>499.98</v>
       </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -2823,6 +4014,11 @@
       <c r="B239" t="n">
         <v>409.99</v>
       </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -2833,6 +4029,11 @@
       <c r="B240" t="n">
         <v>498.99</v>
       </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -2843,6 +4044,11 @@
       <c r="B241" t="n">
         <v>499.98</v>
       </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -2853,6 +4059,11 @@
       <c r="B242" t="n">
         <v>399.99</v>
       </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -2863,6 +4074,11 @@
       <c r="B243" t="n">
         <v>498.99</v>
       </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -2873,6 +4089,11 @@
       <c r="B244" t="n">
         <v>499.98</v>
       </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -2883,6 +4104,11 @@
       <c r="B245" t="n">
         <v>399.99</v>
       </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -2893,6 +4119,11 @@
       <c r="B246" t="n">
         <v>474.99</v>
       </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -2903,6 +4134,11 @@
       <c r="B247" t="n">
         <v>499.98</v>
       </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -2913,6 +4149,11 @@
       <c r="B248" t="n">
         <v>899.99</v>
       </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -2923,6 +4164,11 @@
       <c r="B249" t="n">
         <v>899.99</v>
       </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -2933,6 +4179,11 @@
       <c r="B250" t="n">
         <v>899.99</v>
       </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -2943,6 +4194,11 @@
       <c r="B251" t="n">
         <v>899.99</v>
       </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -2953,6 +4209,11 @@
       <c r="B252" t="n">
         <v>899.99</v>
       </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -2963,6 +4224,11 @@
       <c r="B253" t="n">
         <v>899.99</v>
       </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -2973,6 +4239,11 @@
       <c r="B254" t="n">
         <v>109.99</v>
       </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/pedale-de-delay-et-de-reverberation-donner-yellow-fall-ii</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -2983,6 +4254,11 @@
       <c r="B255" t="n">
         <v>359.99</v>
       </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -2993,6 +4269,11 @@
       <c r="B256" t="n">
         <v>446.99</v>
       </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3003,6 +4284,11 @@
       <c r="B257" t="n">
         <v>549.98</v>
       </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3013,6 +4299,11 @@
       <c r="B258" t="n">
         <v>584.99</v>
       </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3023,6 +4314,11 @@
       <c r="B259" t="n">
         <v>359.99</v>
       </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3033,6 +4329,11 @@
       <c r="B260" t="n">
         <v>446.99</v>
       </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3043,6 +4344,11 @@
       <c r="B261" t="n">
         <v>549.98</v>
       </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3053,6 +4359,11 @@
       <c r="B262" t="n">
         <v>584.99</v>
       </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3063,6 +4374,11 @@
       <c r="B263" t="n">
         <v>539.99</v>
       </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/batterie-electronique-donner-ded-300x-5-tambours-4-cymbales</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3073,6 +4389,11 @@
       <c r="B264" t="n">
         <v>130.99</v>
       </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3083,6 +4404,11 @@
       <c r="B265" t="n">
         <v>129.99</v>
       </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3093,6 +4419,11 @@
       <c r="B266" t="n">
         <v>659.99</v>
       </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3103,6 +4434,11 @@
       <c r="B267" t="n">
         <v>769.99</v>
       </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3113,6 +4449,11 @@
       <c r="B268" t="n">
         <v>749.99</v>
       </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3123,6 +4464,11 @@
       <c r="B269" t="n">
         <v>839.99</v>
       </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3133,6 +4479,11 @@
       <c r="B270" t="n">
         <v>819.99</v>
       </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3143,6 +4494,11 @@
       <c r="B271" t="n">
         <v>775.99</v>
       </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3153,6 +4509,11 @@
       <c r="B272" t="n">
         <v>779.99</v>
       </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3163,6 +4524,11 @@
       <c r="B273" t="n">
         <v>659.99</v>
       </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3173,6 +4539,11 @@
       <c r="B274" t="n">
         <v>769.99</v>
       </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3183,6 +4554,11 @@
       <c r="B275" t="n">
         <v>749.99</v>
       </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3193,6 +4569,11 @@
       <c r="B276" t="n">
         <v>839.99</v>
       </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3203,6 +4584,11 @@
       <c r="B277" t="n">
         <v>819.99</v>
       </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3213,6 +4599,11 @@
       <c r="B278" t="n">
         <v>775.99</v>
       </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3223,6 +4614,11 @@
       <c r="B279" t="n">
         <v>779.99</v>
       </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3233,6 +4629,11 @@
       <c r="B280" t="n">
         <v>102.99</v>
       </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/dkb-200-home-style-corrosion-resistant-metal-piano-bench</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3243,6 +4644,11 @@
       <c r="B281" t="n">
         <v>92.98999999999999</v>
       </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -3253,6 +4659,11 @@
       <c r="B282" t="n">
         <v>109.99</v>
       </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -3263,6 +4674,11 @@
       <c r="B283" t="n">
         <v>99</v>
       </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/pedale-deffet-guitare-donner-triple-threat</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -3273,6 +4689,11 @@
       <c r="B284" t="n">
         <v>72.98999999999999</v>
       </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/siege-de-batterie-mince-donner-dt-50-marron</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -3283,6 +4704,11 @@
       <c r="B285" t="n">
         <v>169.99</v>
       </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -3293,6 +4719,11 @@
       <c r="B286" t="n">
         <v>199.99</v>
       </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -3303,6 +4734,11 @@
       <c r="B287" t="n">
         <v>169.99</v>
       </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -3313,6 +4749,11 @@
       <c r="B288" t="n">
         <v>289.99</v>
       </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -3323,6 +4764,11 @@
       <c r="B289" t="n">
         <v>379.99</v>
       </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -3333,6 +4779,11 @@
       <c r="B290" t="n">
         <v>279.99</v>
       </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -3343,6 +4794,11 @@
       <c r="B291" t="n">
         <v>379.99</v>
       </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -3353,6 +4809,11 @@
       <c r="B292" t="n">
         <v>389.99</v>
       </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -3363,6 +4824,11 @@
       <c r="B293" t="n">
         <v>489.99</v>
       </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -3373,6 +4839,11 @@
       <c r="B294" t="n">
         <v>509.99</v>
       </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -3383,6 +4854,11 @@
       <c r="B295" t="n">
         <v>389.99</v>
       </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -3393,6 +4869,11 @@
       <c r="B296" t="n">
         <v>479.99</v>
       </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -3403,6 +4884,11 @@
       <c r="B297" t="n">
         <v>509.99</v>
       </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -3413,6 +4899,11 @@
       <c r="B298" t="n">
         <v>209.99</v>
       </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -3423,6 +4914,11 @@
       <c r="B299" t="n">
         <v>284.99</v>
       </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -3433,6 +4929,11 @@
       <c r="B300" t="n">
         <v>315.99</v>
       </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -3443,6 +4944,11 @@
       <c r="B301" t="n">
         <v>309.99</v>
       </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -3453,6 +4959,11 @@
       <c r="B302" t="n">
         <v>359.99</v>
       </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -3463,6 +4974,11 @@
       <c r="B303" t="n">
         <v>385.99</v>
       </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -3473,6 +4989,11 @@
       <c r="B304" t="n">
         <v>379.99</v>
       </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -3483,6 +5004,11 @@
       <c r="B305" t="n">
         <v>319.99</v>
       </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -3493,6 +5019,11 @@
       <c r="B306" t="n">
         <v>389.99</v>
       </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -3503,6 +5034,11 @@
       <c r="B307" t="n">
         <v>179.99</v>
       </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -3513,6 +5049,11 @@
       <c r="B308" t="n">
         <v>269.99</v>
       </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -3523,6 +5064,11 @@
       <c r="B309" t="n">
         <v>279.99</v>
       </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -3533,6 +5079,11 @@
       <c r="B310" t="n">
         <v>289.99</v>
       </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -3543,6 +5094,11 @@
       <c r="B311" t="n">
         <v>339.99</v>
       </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -3553,6 +5109,11 @@
       <c r="B312" t="n">
         <v>349.99</v>
       </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -3563,6 +5124,11 @@
       <c r="B313" t="n">
         <v>359.99</v>
       </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -3573,6 +5139,11 @@
       <c r="B314" t="n">
         <v>295.99</v>
       </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -3583,6 +5154,11 @@
       <c r="B315" t="n">
         <v>365.99</v>
       </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -3593,6 +5169,11 @@
       <c r="B316" t="n">
         <v>189.99</v>
       </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -3603,6 +5184,11 @@
       <c r="B317" t="n">
         <v>269.99</v>
       </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -3613,6 +5199,11 @@
       <c r="B318" t="n">
         <v>279.99</v>
       </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -3623,6 +5214,11 @@
       <c r="B319" t="n">
         <v>282.99</v>
       </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -3633,6 +5229,11 @@
       <c r="B320" t="n">
         <v>335.99</v>
       </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -3643,6 +5244,11 @@
       <c r="B321" t="n">
         <v>343.99</v>
       </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -3653,6 +5259,11 @@
       <c r="B322" t="n">
         <v>352.99</v>
       </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -3663,6 +5274,11 @@
       <c r="B323" t="n">
         <v>285.99</v>
       </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -3673,6 +5289,11 @@
       <c r="B324" t="n">
         <v>355.99</v>
       </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -3683,6 +5304,11 @@
       <c r="B325" t="n">
         <v>209.99</v>
       </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -3693,6 +5319,11 @@
       <c r="B326" t="n">
         <v>284.99</v>
       </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -3703,6 +5334,11 @@
       <c r="B327" t="n">
         <v>315.99</v>
       </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -3713,6 +5349,11 @@
       <c r="B328" t="n">
         <v>309.99</v>
       </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -3723,6 +5364,11 @@
       <c r="B329" t="n">
         <v>359.99</v>
       </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -3733,6 +5379,11 @@
       <c r="B330" t="n">
         <v>385.99</v>
       </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -3743,6 +5394,11 @@
       <c r="B331" t="n">
         <v>379.99</v>
       </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -3753,6 +5409,11 @@
       <c r="B332" t="n">
         <v>319.99</v>
       </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -3763,6 +5424,11 @@
       <c r="B333" t="n">
         <v>389.99</v>
       </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -3773,6 +5439,11 @@
       <c r="B334" t="n">
         <v>169.99</v>
       </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -3783,6 +5454,11 @@
       <c r="B335" t="n">
         <v>239.99</v>
       </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -3793,6 +5469,11 @@
       <c r="B336" t="n">
         <v>359.99</v>
       </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -3803,6 +5484,11 @@
       <c r="B337" t="n">
         <v>496.99</v>
       </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -3813,6 +5499,11 @@
       <c r="B338" t="n">
         <v>408.99</v>
       </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -3823,6 +5514,11 @@
       <c r="B339" t="n">
         <v>309.99</v>
       </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -3833,6 +5529,11 @@
       <c r="B340" t="n">
         <v>496.99</v>
       </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -3843,6 +5544,11 @@
       <c r="B341" t="n">
         <v>408.99</v>
       </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -3853,6 +5559,11 @@
       <c r="B342" t="n">
         <v>359.99</v>
       </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -3863,6 +5574,11 @@
       <c r="B343" t="n">
         <v>496.99</v>
       </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -3873,6 +5589,11 @@
       <c r="B344" t="n">
         <v>408.99</v>
       </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -3883,6 +5604,11 @@
       <c r="B345" t="n">
         <v>359.99</v>
       </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -3893,6 +5619,11 @@
       <c r="B346" t="n">
         <v>496.99</v>
       </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -3903,6 +5634,11 @@
       <c r="B347" t="n">
         <v>408.99</v>
       </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -3913,6 +5649,11 @@
       <c r="B348" t="n">
         <v>309.99</v>
       </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -3923,6 +5664,11 @@
       <c r="B349" t="n">
         <v>496.99</v>
       </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -3933,6 +5679,11 @@
       <c r="B350" t="n">
         <v>408.99</v>
       </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -3943,6 +5694,11 @@
       <c r="B351" t="n">
         <v>309.99</v>
       </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -3953,6 +5709,11 @@
       <c r="B352" t="n">
         <v>496.99</v>
       </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -3963,6 +5724,11 @@
       <c r="B353" t="n">
         <v>408.99</v>
       </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -3973,6 +5739,11 @@
       <c r="B354" t="n">
         <v>499.99</v>
       </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-max-batteries-electroniques</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -3983,6 +5754,11 @@
       <c r="B355" t="n">
         <v>1099.99</v>
       </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -3993,6 +5769,11 @@
       <c r="B356" t="n">
         <v>1114.99</v>
       </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -4003,6 +5784,11 @@
       <c r="B357" t="n">
         <v>899</v>
       </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -4013,6 +5799,11 @@
       <c r="B358" t="n">
         <v>899</v>
       </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -4023,6 +5814,11 @@
       <c r="B359" t="n">
         <v>899</v>
       </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -4033,6 +5829,11 @@
       <c r="B360" t="n">
         <v>125.99</v>
       </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -4043,6 +5844,11 @@
       <c r="B361" t="n">
         <v>166.99</v>
       </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -4053,6 +5859,11 @@
       <c r="B362" t="n">
         <v>299.99</v>
       </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -4063,6 +5874,11 @@
       <c r="B363" t="n">
         <v>486.99</v>
       </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -4073,6 +5889,11 @@
       <c r="B364" t="n">
         <v>398.99</v>
       </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -4083,6 +5904,11 @@
       <c r="B365" t="n">
         <v>299.99</v>
       </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -4093,6 +5919,11 @@
       <c r="B366" t="n">
         <v>486.99</v>
       </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -4103,6 +5934,11 @@
       <c r="B367" t="n">
         <v>398.99</v>
       </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -4113,6 +5949,11 @@
       <c r="B368" t="n">
         <v>299.99</v>
       </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -4123,6 +5964,11 @@
       <c r="B369" t="n">
         <v>486.99</v>
       </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -4133,6 +5979,11 @@
       <c r="B370" t="n">
         <v>398.99</v>
       </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -4143,6 +5994,11 @@
       <c r="B371" t="n">
         <v>299.99</v>
       </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -4153,6 +6009,11 @@
       <c r="B372" t="n">
         <v>486.99</v>
       </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -4163,6 +6024,11 @@
       <c r="B373" t="n">
         <v>398.99</v>
       </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -4173,6 +6039,11 @@
       <c r="B374" t="n">
         <v>109.99</v>
       </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-banquette-de-piano-en-bois-massif-avec-espace-de-rangement</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -4183,6 +6054,11 @@
       <c r="B375" t="n">
         <v>319.99</v>
       </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -4193,6 +6069,11 @@
       <c r="B376" t="n">
         <v>408.99</v>
       </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -4203,6 +6084,11 @@
       <c r="B377" t="n">
         <v>419.99</v>
       </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -4213,6 +6099,11 @@
       <c r="B378" t="n">
         <v>419.99</v>
       </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -4223,6 +6114,11 @@
       <c r="B379" t="n">
         <v>435.99</v>
       </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -4233,6 +6129,11 @@
       <c r="B380" t="n">
         <v>489.99</v>
       </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -4243,6 +6144,11 @@
       <c r="B381" t="n">
         <v>439.99</v>
       </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -4253,6 +6159,11 @@
       <c r="B382" t="n">
         <v>509.99</v>
       </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -4263,6 +6174,11 @@
       <c r="B383" t="n">
         <v>439.99</v>
       </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -4273,6 +6189,11 @@
       <c r="B384" t="n">
         <v>329.99</v>
       </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -4283,6 +6204,11 @@
       <c r="B385" t="n">
         <v>418.99</v>
       </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -4293,6 +6219,11 @@
       <c r="B386" t="n">
         <v>429.99</v>
       </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -4303,6 +6234,11 @@
       <c r="B387" t="n">
         <v>429.99</v>
       </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -4313,6 +6249,11 @@
       <c r="B388" t="n">
         <v>445.99</v>
       </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -4323,6 +6264,11 @@
       <c r="B389" t="n">
         <v>499.99</v>
       </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -4333,6 +6279,11 @@
       <c r="B390" t="n">
         <v>449.99</v>
       </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -4343,6 +6294,11 @@
       <c r="B391" t="n">
         <v>519.99</v>
       </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -4353,6 +6309,11 @@
       <c r="B392" t="n">
         <v>449.99</v>
       </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -4363,6 +6324,11 @@
       <c r="B393" t="n">
         <v>499.99</v>
       </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -4373,6 +6339,11 @@
       <c r="B394" t="n">
         <v>599.99</v>
       </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -4383,6 +6354,11 @@
       <c r="B395" t="n">
         <v>609.99</v>
       </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -4393,6 +6369,11 @@
       <c r="B396" t="n">
         <v>686.99</v>
       </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -4403,6 +6384,11 @@
       <c r="B397" t="n">
         <v>696.99</v>
       </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -4413,6 +6399,11 @@
       <c r="B398" t="n">
         <v>615.99</v>
       </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -4423,6 +6414,11 @@
       <c r="B399" t="n">
         <v>685.99</v>
       </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -4433,6 +6429,11 @@
       <c r="B400" t="n">
         <v>619.99</v>
       </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -4443,6 +6444,11 @@
       <c r="B401" t="n">
         <v>689.99</v>
       </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -4453,6 +6459,11 @@
       <c r="B402" t="n">
         <v>619.99</v>
       </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -4463,6 +6474,11 @@
       <c r="B403" t="n">
         <v>459.99</v>
       </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -4473,6 +6489,11 @@
       <c r="B404" t="n">
         <v>539.99</v>
       </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -4483,6 +6504,11 @@
       <c r="B405" t="n">
         <v>579.99</v>
       </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -4493,6 +6519,11 @@
       <c r="B406" t="n">
         <v>639.99</v>
       </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -4503,6 +6534,11 @@
       <c r="B407" t="n">
         <v>605.99</v>
       </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -4513,6 +6549,11 @@
       <c r="B408" t="n">
         <v>665.99</v>
       </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -4523,6 +6564,11 @@
       <c r="B409" t="n">
         <v>499.99</v>
       </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -4533,6 +6579,11 @@
       <c r="B410" t="n">
         <v>579.99</v>
       </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -4543,6 +6594,11 @@
       <c r="B411" t="n">
         <v>579.99</v>
       </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -4553,6 +6609,11 @@
       <c r="B412" t="n">
         <v>639.99</v>
       </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -4563,6 +6624,11 @@
       <c r="B413" t="n">
         <v>615.99</v>
       </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -4573,6 +6639,11 @@
       <c r="B414" t="n">
         <v>675.99</v>
       </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -4583,6 +6654,11 @@
       <c r="B415" t="n">
         <v>599.99</v>
       </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -4593,6 +6669,11 @@
       <c r="B416" t="n">
         <v>659.99</v>
       </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -4603,6 +6684,11 @@
       <c r="B417" t="n">
         <v>619.99</v>
       </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -4613,6 +6699,11 @@
       <c r="B418" t="n">
         <v>629.99</v>
       </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -4623,6 +6714,11 @@
       <c r="B419" t="n">
         <v>729.99</v>
       </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -4633,6 +6729,11 @@
       <c r="B420" t="n">
         <v>816.99</v>
       </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -4643,6 +6744,11 @@
       <c r="B421" t="n">
         <v>719.99</v>
       </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -4653,6 +6759,11 @@
       <c r="B422" t="n">
         <v>749.99</v>
       </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -4663,6 +6774,11 @@
       <c r="B423" t="n">
         <v>749.99</v>
       </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -4673,6 +6789,11 @@
       <c r="B424" t="n">
         <v>761.99</v>
       </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -4683,6 +6804,11 @@
       <c r="B425" t="n">
         <v>851.99</v>
       </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -4693,6 +6819,11 @@
       <c r="B426" t="n">
         <v>927.99</v>
       </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -4703,6 +6834,11 @@
       <c r="B427" t="n">
         <v>840.99</v>
       </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -4713,6 +6849,11 @@
       <c r="B428" t="n">
         <v>977.99</v>
       </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -4723,6 +6864,11 @@
       <c r="B429" t="n">
         <v>629.99</v>
       </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -4733,6 +6879,11 @@
       <c r="B430" t="n">
         <v>729.99</v>
       </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -4743,6 +6894,11 @@
       <c r="B431" t="n">
         <v>816.99</v>
       </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -4753,6 +6909,11 @@
       <c r="B432" t="n">
         <v>745.99</v>
       </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -4763,6 +6924,11 @@
       <c r="B433" t="n">
         <v>815.99</v>
       </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -4773,6 +6939,11 @@
       <c r="B434" t="n">
         <v>749.99</v>
       </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -4783,6 +6954,11 @@
       <c r="B435" t="n">
         <v>819.99</v>
       </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -4793,6 +6969,11 @@
       <c r="B436" t="n">
         <v>559.99</v>
       </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -4803,6 +6984,11 @@
       <c r="B437" t="n">
         <v>659.99</v>
       </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -4813,6 +6999,11 @@
       <c r="B438" t="n">
         <v>746.99</v>
       </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -4823,6 +7014,11 @@
       <c r="B439" t="n">
         <v>675.99</v>
       </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -4833,6 +7029,11 @@
       <c r="B440" t="n">
         <v>745.99</v>
       </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -4843,6 +7044,11 @@
       <c r="B441" t="n">
         <v>679.99</v>
       </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -4853,6 +7059,11 @@
       <c r="B442" t="n">
         <v>749.99</v>
       </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -4863,6 +7074,11 @@
       <c r="B443" t="n">
         <v>186.99</v>
       </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-arena-2000</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -4873,6 +7089,11 @@
       <c r="B444" t="n">
         <v>99.98999999999999</v>
       </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -4883,6 +7104,11 @@
       <c r="B445" t="n">
         <v>99.98999999999999</v>
       </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -4893,6 +7119,11 @@
       <c r="B446" t="n">
         <v>89.98999999999999</v>
       </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dmk-25-pro-midi-keyboard</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -4903,6 +7134,11 @@
       <c r="B447" t="n">
         <v>236.99</v>
       </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -4913,6 +7149,11 @@
       <c r="B448" t="n">
         <v>335.99</v>
       </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -4923,6 +7164,11 @@
       <c r="B449" t="n">
         <v>423.99</v>
       </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -4933,6 +7179,11 @@
       <c r="B450" t="n">
         <v>219.99</v>
       </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -4943,6 +7194,11 @@
       <c r="B451" t="n">
         <v>335.99</v>
       </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -4953,6 +7209,11 @@
       <c r="B452" t="n">
         <v>423.99</v>
       </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -4963,6 +7224,11 @@
       <c r="B453" t="n">
         <v>281.99</v>
       </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -4973,6 +7239,11 @@
       <c r="B454" t="n">
         <v>373.99</v>
       </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -4983,6 +7254,11 @@
       <c r="B455" t="n">
         <v>530.99</v>
       </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -4993,6 +7269,11 @@
       <c r="B456" t="n">
         <v>89</v>
       </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-b1-syn-the-ti-seurs-sequencer</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -5003,6 +7284,11 @@
       <c r="B457" t="n">
         <v>109.99</v>
       </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/banc-de-piano-tabouret-en-bois-dur-et-solide</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -5013,6 +7299,11 @@
       <c r="B458" t="n">
         <v>7.69</v>
       </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/for-the-price-difference</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -5023,6 +7314,11 @@
       <c r="B459" t="n">
         <v>152.99</v>
       </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -5033,6 +7329,11 @@
       <c r="B460" t="n">
         <v>339.99</v>
       </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -5043,6 +7344,11 @@
       <c r="B461" t="n">
         <v>152.99</v>
       </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -5053,6 +7359,11 @@
       <c r="B462" t="n">
         <v>339.99</v>
       </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -5063,6 +7374,11 @@
       <c r="B463" t="n">
         <v>152.99</v>
       </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -5073,6 +7389,11 @@
       <c r="B464" t="n">
         <v>339.99</v>
       </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -5083,6 +7404,11 @@
       <c r="B465" t="n">
         <v>152.99</v>
       </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -5093,6 +7419,11 @@
       <c r="B466" t="n">
         <v>339.99</v>
       </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -5103,6 +7434,11 @@
       <c r="B467" t="n">
         <v>86.98999999999999</v>
       </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -5113,6 +7449,11 @@
       <c r="B468" t="n">
         <v>69.98999999999999</v>
       </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -5123,6 +7464,11 @@
       <c r="B469" t="n">
         <v>389.99</v>
       </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -5133,6 +7479,11 @@
       <c r="B470" t="n">
         <v>479.99</v>
       </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -5143,6 +7494,11 @@
       <c r="B471" t="n">
         <v>479.99</v>
       </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -5153,6 +7509,11 @@
       <c r="B472" t="n">
         <v>489.99</v>
       </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -5163,6 +7524,11 @@
       <c r="B473" t="n">
         <v>509.99</v>
       </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -5173,6 +7539,11 @@
       <c r="B474" t="n">
         <v>389.99</v>
       </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -5183,6 +7554,11 @@
       <c r="B475" t="n">
         <v>479.99</v>
       </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -5193,6 +7569,11 @@
       <c r="B476" t="n">
         <v>479.99</v>
       </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -5203,6 +7584,11 @@
       <c r="B477" t="n">
         <v>489.99</v>
       </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -5213,6 +7599,11 @@
       <c r="B478" t="n">
         <v>509.99</v>
       </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -5223,6 +7614,11 @@
       <c r="B479" t="n">
         <v>89.98999999999999</v>
       </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -5233,6 +7629,11 @@
       <c r="B480" t="n">
         <v>79.47</v>
       </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -5243,6 +7644,11 @@
       <c r="B481" t="n">
         <v>89.98999999999999</v>
       </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-piano-bench-keyboard-stool-solid-hard-wooden-digital-piano-stool-with-large-storage-black</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -5253,6 +7659,11 @@
       <c r="B482" t="n">
         <v>469.99</v>
       </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -5263,6 +7674,11 @@
       <c r="B483" t="n">
         <v>518.99</v>
       </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -5273,6 +7689,11 @@
       <c r="B484" t="n">
         <v>566.99</v>
       </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -5283,6 +7704,11 @@
       <c r="B485" t="n">
         <v>557.99</v>
       </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -5293,6 +7719,11 @@
       <c r="B486" t="n">
         <v>636.99</v>
       </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -5303,6 +7734,11 @@
       <c r="B487" t="n">
         <v>627.99</v>
       </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -5313,6 +7749,11 @@
       <c r="B488" t="n">
         <v>549.99</v>
       </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -5323,6 +7764,11 @@
       <c r="B489" t="n">
         <v>569.99</v>
       </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -5333,6 +7779,11 @@
       <c r="B490" t="n">
         <v>629.99</v>
       </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -5343,6 +7794,11 @@
       <c r="B491" t="n">
         <v>585.99</v>
       </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -5353,6 +7809,11 @@
       <c r="B492" t="n">
         <v>645.99</v>
       </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -5363,6 +7824,11 @@
       <c r="B493" t="n">
         <v>589.99</v>
       </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -5373,6 +7839,11 @@
       <c r="B494" t="n">
         <v>429.99</v>
       </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -5383,6 +7854,11 @@
       <c r="B495" t="n">
         <v>536.99</v>
       </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -5393,6 +7869,11 @@
       <c r="B496" t="n">
         <v>527.99</v>
       </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -5403,6 +7884,11 @@
       <c r="B497" t="n">
         <v>606.99</v>
       </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -5413,6 +7899,11 @@
       <c r="B498" t="n">
         <v>597.99</v>
       </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -5423,6 +7914,11 @@
       <c r="B499" t="n">
         <v>519.99</v>
       </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -5433,6 +7929,11 @@
       <c r="B500" t="n">
         <v>539.99</v>
       </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -5443,6 +7944,11 @@
       <c r="B501" t="n">
         <v>599.99</v>
       </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -5453,6 +7959,11 @@
       <c r="B502" t="n">
         <v>555.99</v>
       </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -5463,6 +7974,11 @@
       <c r="B503" t="n">
         <v>615.99</v>
       </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -5473,6 +7989,11 @@
       <c r="B504" t="n">
         <v>549.99</v>
       </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -5483,6 +8004,11 @@
       <c r="B505" t="n">
         <v>559.98</v>
       </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -5493,6 +8019,11 @@
       <c r="B506" t="n">
         <v>469.99</v>
       </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -5503,6 +8034,11 @@
       <c r="B507" t="n">
         <v>518.99</v>
       </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -5513,6 +8049,11 @@
       <c r="B508" t="n">
         <v>566.99</v>
       </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -5523,6 +8064,11 @@
       <c r="B509" t="n">
         <v>557.99</v>
       </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -5533,6 +8079,11 @@
       <c r="B510" t="n">
         <v>636.99</v>
       </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -5543,6 +8094,11 @@
       <c r="B511" t="n">
         <v>627.99</v>
       </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -5553,6 +8109,11 @@
       <c r="B512" t="n">
         <v>549.99</v>
       </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -5563,6 +8124,11 @@
       <c r="B513" t="n">
         <v>569.99</v>
       </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -5573,6 +8139,11 @@
       <c r="B514" t="n">
         <v>629.99</v>
       </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -5583,6 +8154,11 @@
       <c r="B515" t="n">
         <v>585.99</v>
       </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -5593,6 +8169,11 @@
       <c r="B516" t="n">
         <v>645.99</v>
       </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -5603,6 +8184,11 @@
       <c r="B517" t="n">
         <v>589.99</v>
       </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -5613,6 +8199,11 @@
       <c r="B518" t="n">
         <v>429.99</v>
       </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -5623,6 +8214,11 @@
       <c r="B519" t="n">
         <v>499.99</v>
       </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -5633,6 +8229,11 @@
       <c r="B520" t="n">
         <v>536.99</v>
       </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -5643,6 +8244,11 @@
       <c r="B521" t="n">
         <v>527.99</v>
       </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -5653,6 +8259,11 @@
       <c r="B522" t="n">
         <v>606.99</v>
       </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -5663,6 +8274,11 @@
       <c r="B523" t="n">
         <v>597.99</v>
       </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -5673,6 +8289,11 @@
       <c r="B524" t="n">
         <v>519.99</v>
       </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -5683,6 +8304,11 @@
       <c r="B525" t="n">
         <v>539.99</v>
       </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -5693,6 +8319,11 @@
       <c r="B526" t="n">
         <v>599.99</v>
       </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -5703,6 +8334,11 @@
       <c r="B527" t="n">
         <v>555.99</v>
       </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -5713,6 +8349,11 @@
       <c r="B528" t="n">
         <v>615.99</v>
       </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -5722,6 +8363,11 @@
       </c>
       <c r="B529" t="n">
         <v>549.99</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -498,7 +498,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -513,11 +513,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>822.99</v>
+        <v>829.99</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,11 +528,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>839.99</v>
+        <v>822.99</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -558,11 +558,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>822.99</v>
+        <v>839.99</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -573,11 +573,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>829.99</v>
+        <v>822.99</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -2718,7 +2718,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -2733,7 +2733,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -2748,7 +2748,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -2763,7 +2763,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -2778,7 +2778,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -2793,7 +2793,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4143,7 +4143,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -4158,7 +4158,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -4173,7 +4173,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -4188,7 +4188,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -4203,7 +4203,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -4218,7 +4218,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B253" t="n">

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C529"/>
+  <dimension ref="A1:C514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2613,11 +2613,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 4 Cymbales</t>
+          <t>Donner DED-200X Batterie Électronique - Nouvelle 5 Tambours et 4 Cymbales</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>499.99</v>
+        <v>599.99</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -2628,11 +2628,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - Nouvelle 5 Tambours et 4 Cymbales</t>
+          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 4 Cymbales</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>599.99</v>
+        <v>499.99</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -6468,1196 +6468,1196 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>459.99</v>
+        <v>629.99</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc X-Style</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>539.99</v>
+        <v>729.99</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>579.99</v>
+        <v>816.99</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>639.99</v>
+        <v>719.99</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>605.99</v>
+        <v>749.99</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>665.99</v>
+        <v>749.99</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>499.99</v>
+        <v>761.99</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc X-Style</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>579.99</v>
+        <v>851.99</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>579.99</v>
+        <v>927.99</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>639.99</v>
+        <v>840.99</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>615.99</v>
+        <v>977.99</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>675.99</v>
+        <v>629.99</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>599.99</v>
+        <v>729.99</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>659.99</v>
+        <v>816.99</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>【Déstockage】Donner DDP-90 Domestique Piano Numérique - DDP-90 Pro / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>619.99</v>
+        <v>745.99</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-90-home-digital-piano-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>629.99</v>
+        <v>815.99</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>729.99</v>
+        <v>749.99</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>816.99</v>
+        <v>819.99</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>719.99</v>
+        <v>559.99</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>749.99</v>
+        <v>659.99</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>749.99</v>
+        <v>746.99</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>761.99</v>
+        <v>675.99</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>851.99</v>
+        <v>745.99</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>927.99</v>
+        <v>679.99</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>840.99</v>
+        <v>749.99</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>977.99</v>
+        <v>186.99</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-arena-2000</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>629.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>729.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DMK-25 Pro Clavier MIDI</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>816.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dmk-25-pro-midi-keyboard</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>745.99</v>
+        <v>236.99</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>815.99</v>
+        <v>335.99</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>749.99</v>
+        <v>423.99</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>819.99</v>
+        <v>219.99</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>559.99</v>
+        <v>335.99</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>659.99</v>
+        <v>423.99</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>746.99</v>
+        <v>281.99</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>675.99</v>
+        <v>373.99</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>745.99</v>
+        <v>530.99</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>679.99</v>
+        <v>89</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-b1-syn-the-ti-seurs-sequencer</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>749.99</v>
+        <v>109.99</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/banc-de-piano-tabouret-en-bois-dur-et-solide</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
+          <t>Pour la différence de prix</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>186.99</v>
+        <v>7.69</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-arena-2000</t>
+          <t>https://fr.donnermusic.com/products/for-the-price-difference</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>99.98999999999999</v>
+        <v>152.99</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>99.98999999999999</v>
+        <v>339.99</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Donner DMK-25 Pro Clavier MIDI</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>89.98999999999999</v>
+        <v>152.99</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dmk-25-pro-midi-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>236.99</v>
+        <v>339.99</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>335.99</v>
+        <v>152.99</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>423.99</v>
+        <v>339.99</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>219.99</v>
+        <v>152.99</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>335.99</v>
+        <v>339.99</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>423.99</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>281.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>373.99</v>
+        <v>389.99</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>530.99</v>
+        <v>479.99</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>89</v>
+        <v>479.99</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-b1-syn-the-ti-seurs-sequencer</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>109.99</v>
+        <v>489.99</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/banc-de-piano-tabouret-en-bois-dur-et-solide</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Pour la différence de prix</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>7.69</v>
+        <v>509.99</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/for-the-price-difference</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>152.99</v>
+        <v>389.99</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>339.99</v>
+        <v>479.99</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>152.99</v>
+        <v>479.99</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>339.99</v>
+        <v>489.99</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>152.99</v>
+        <v>509.99</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>339.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>152.99</v>
+        <v>79.47</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>339.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-piano-bench-keyboard-stool-solid-hard-wooden-digital-piano-stool-with-large-storage-black</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>86.98999999999999</v>
+        <v>469.99</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>69.98999999999999</v>
+        <v>518.99</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>389.99</v>
+        <v>566.99</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>479.99</v>
+        <v>557.99</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>479.99</v>
+        <v>636.99</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>489.99</v>
+        <v>627.99</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>509.99</v>
+        <v>549.99</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>389.99</v>
+        <v>569.99</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>479.99</v>
+        <v>629.99</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>479.99</v>
+        <v>585.99</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>489.99</v>
+        <v>645.99</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>509.99</v>
+        <v>589.99</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>89.98999999999999</v>
+        <v>429.99</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>79.47</v>
+        <v>536.99</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>89.98999999999999</v>
+        <v>527.99</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-piano-bench-keyboard-stool-solid-hard-wooden-digital-piano-stool-with-large-storage-black</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>469.99</v>
+        <v>606.99</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
@@ -7668,11 +7668,11 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>518.99</v>
+        <v>597.99</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
@@ -7683,11 +7683,11 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>566.99</v>
+        <v>519.99</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
@@ -7698,11 +7698,11 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>557.99</v>
+        <v>539.99</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
@@ -7713,11 +7713,11 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>636.99</v>
+        <v>599.99</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
@@ -7728,11 +7728,11 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>627.99</v>
+        <v>555.99</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
@@ -7743,11 +7743,11 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>549.99</v>
+        <v>615.99</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
@@ -7758,11 +7758,11 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>569.99</v>
+        <v>549.99</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
@@ -7773,11 +7773,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>629.99</v>
+        <v>559.98</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
@@ -7788,11 +7788,11 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>585.99</v>
+        <v>469.99</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
@@ -7803,11 +7803,11 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>645.99</v>
+        <v>518.99</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
@@ -7818,11 +7818,11 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>589.99</v>
+        <v>566.99</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
@@ -7833,11 +7833,11 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>429.99</v>
+        <v>557.99</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
@@ -7848,11 +7848,11 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>536.99</v>
+        <v>636.99</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
@@ -7863,11 +7863,11 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>527.99</v>
+        <v>627.99</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
@@ -7878,11 +7878,11 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>606.99</v>
+        <v>549.99</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
@@ -7893,11 +7893,11 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>597.99</v>
+        <v>569.99</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
@@ -7908,11 +7908,11 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>519.99</v>
+        <v>629.99</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
@@ -7923,11 +7923,11 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>539.99</v>
+        <v>585.99</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
@@ -7938,11 +7938,11 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>599.99</v>
+        <v>645.99</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
@@ -7953,11 +7953,11 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>555.99</v>
+        <v>589.99</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
@@ -7968,11 +7968,11 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>615.99</v>
+        <v>429.99</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
@@ -7983,11 +7983,11 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>549.99</v>
+        <v>499.99</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
@@ -7998,11 +7998,11 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>559.98</v>
+        <v>536.99</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
@@ -8013,11 +8013,11 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>469.99</v>
+        <v>527.99</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
@@ -8028,11 +8028,11 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>518.99</v>
+        <v>606.99</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
@@ -8043,11 +8043,11 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>566.99</v>
+        <v>597.99</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
@@ -8058,11 +8058,11 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>557.99</v>
+        <v>519.99</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
@@ -8073,11 +8073,11 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>636.99</v>
+        <v>539.99</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
@@ -8088,11 +8088,11 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>627.99</v>
+        <v>599.99</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
@@ -8103,11 +8103,11 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>549.99</v>
+        <v>555.99</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
@@ -8118,11 +8118,11 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>569.99</v>
+        <v>615.99</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
@@ -8133,238 +8133,13 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>629.99</v>
+        <v>549.99</v>
       </c>
       <c r="C514" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
-        </is>
-      </c>
-      <c r="B515" t="n">
-        <v>585.99</v>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
-        </is>
-      </c>
-      <c r="B516" t="n">
-        <v>645.99</v>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
-        </is>
-      </c>
-      <c r="B517" t="n">
-        <v>589.99</v>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
-        </is>
-      </c>
-      <c r="B518" t="n">
-        <v>429.99</v>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
-        </is>
-      </c>
-      <c r="B519" t="n">
-        <v>499.99</v>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
-        </is>
-      </c>
-      <c r="B520" t="n">
-        <v>536.99</v>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
-        </is>
-      </c>
-      <c r="B521" t="n">
-        <v>527.99</v>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
-        </is>
-      </c>
-      <c r="B522" t="n">
-        <v>606.99</v>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
-        </is>
-      </c>
-      <c r="B523" t="n">
-        <v>597.99</v>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
-        </is>
-      </c>
-      <c r="B524" t="n">
-        <v>519.99</v>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
-        </is>
-      </c>
-      <c r="B525" t="n">
-        <v>539.99</v>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
-        </is>
-      </c>
-      <c r="B526" t="n">
-        <v>599.99</v>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
-        </is>
-      </c>
-      <c r="B527" t="n">
-        <v>555.99</v>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
-        </is>
-      </c>
-      <c r="B528" t="n">
-        <v>615.99</v>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
-        </is>
-      </c>
-      <c r="B529" t="n">
-        <v>549.99</v>
-      </c>
-      <c r="C529" t="inlineStr">
         <is>
           <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>399.99</v>
+        <v>329.99</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>249.99</v>
+        <v>219.99</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>219.99</v>
+        <v>209.99</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>489.99</v>
+        <v>479.99</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>398.99</v>
+        <v>388.99</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>219.99</v>
+        <v>209.99</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>489.99</v>
+        <v>479.99</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>398.99</v>
+        <v>388.99</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>219.99</v>
+        <v>209.99</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>489.99</v>
+        <v>479.99</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>398.99</v>
+        <v>388.99</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>299.99</v>
+        <v>279.99</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>341.99</v>
+        <v>322.99</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>130.99</v>
+        <v>129.99</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -4218,7 +4218,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -4233,11 +4233,11 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>498.99</v>
+        <v>474.99</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -4263,7 +4263,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -4278,11 +4278,11 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>474.99</v>
+        <v>498.99</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -5058,11 +5058,11 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>209.99</v>
+        <v>179.99</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -5073,11 +5073,11 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>284.99</v>
+        <v>269.99</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -5088,11 +5088,11 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>315.99</v>
+        <v>279.99</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -5103,11 +5103,11 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>309.99</v>
+        <v>289.99</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -5118,11 +5118,11 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>359.99</v>
+        <v>339.99</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -5133,11 +5133,11 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>385.99</v>
+        <v>349.99</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -5148,11 +5148,11 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>379.99</v>
+        <v>359.99</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -5163,11 +5163,11 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>319.99</v>
+        <v>295.99</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -5178,11 +5178,11 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>389.99</v>
+        <v>365.99</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -5193,11 +5193,11 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>179.99</v>
+        <v>209.99</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -5208,11 +5208,11 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>269.99</v>
+        <v>284.99</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -5223,11 +5223,11 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>279.99</v>
+        <v>315.99</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -5238,11 +5238,11 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>289.99</v>
+        <v>309.99</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -5253,11 +5253,11 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>339.99</v>
+        <v>359.99</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -5268,11 +5268,11 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>349.99</v>
+        <v>385.99</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -5283,11 +5283,11 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>359.99</v>
+        <v>379.99</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -5298,11 +5298,11 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>295.99</v>
+        <v>319.99</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -5313,11 +5313,11 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>365.99</v>
+        <v>389.99</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -918,7 +918,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier électronique - Blanc</t>
+          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Blanc</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -933,7 +933,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier électronique - Rosa</t>
+          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Rosa</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -948,7 +948,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier électronique - Cyan</t>
+          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Cyan</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2973,7 +2973,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Bleu clair</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Bleu clair</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -2988,7 +2988,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 32 Touches Rose clair</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Rose clair</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -3003,7 +3003,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Bleu clair</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Bleu clair</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -3018,7 +3018,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier Numérique - 44 Touches avec Support Rose clair</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Rose clair</t>
         </is>
       </c>
       <c r="B173" t="n">

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C525"/>
+  <dimension ref="A1:C519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -663,472 +663,472 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>729.99</v>
+        <v>529.99</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>829.99</v>
+        <v>579.99</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>822.99</v>
+        <v>579.99</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>729.99</v>
+        <v>615.99</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano Blanc</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>839.99</v>
+        <v>599.99</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA R300 Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>Donner MAMP8 Ampli AV 5.2 Canaux</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>822.99</v>
+        <v>229.99</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-r300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-mamp8-5-2-channel-av-receiver</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>529.99</v>
+        <v>699.99</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc réglable X-Style</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>579.99</v>
+        <v>799.99</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano noir</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc (match officiel)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>579.99</v>
+        <v>799.99</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>615.99</v>
+        <v>819.99</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano Blanc</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>599.99</v>
+        <v>779.99</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Donner MAMP8 Ampli AV 5.2 Canaux</t>
+          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Blanc</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>229.99</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-mamp8-5-2-channel-av-receiver</t>
+          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano</t>
+          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Rosa</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>699.99</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + banc de piano</t>
+          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Cyan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>799.99</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc (match officiel)</t>
+          <t>Donner SD-15 Clavier électronique 61 touches - Bundle mit Zubehör</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>799.99</v>
+        <v>219.99</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-sd-15-61-key-electronic-keyboard</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner SD-15 Clavier électronique 61 touches - Nur das Keyboard</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>819.99</v>
+        <v>169.99</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-sd-15-61-key-electronic-keyboard</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc réglable X-Style</t>
+          <t>Donner Starrypad Pro Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>779.99</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-starrypad-pro-midi-controller</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Blanc</t>
+          <t>Donner MH1 Casque de monitoring</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>79.98999999999999</v>
+        <v>59.99</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-mh1-sound-monitor-headphones</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Rosa</t>
+          <t>Donner Sac de Transport pour Clavier 88 Touches</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>79.98999999999999</v>
+        <v>39.99</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-88-key-keyboard-gig-bag</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Cyan</t>
+          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Blanc】</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>79.98999999999999</v>
+        <v>439.99</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Donner SD-15 Clavier électronique 61 touches - Bundle mit Zubehör</t>
+          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Noir】</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>219.99</v>
+        <v>439.99</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-sd-15-61-key-electronic-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Donner SD-15 Clavier électronique 61 touches - Nur das Keyboard</t>
+          <t>Donner HUSH X LIVE Guitare de voyage - Version MIYAVI</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>169.99</v>
+        <v>635.99</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-sd-15-61-key-electronic-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Donner Starrypad Pro Contrôleur MIDI</t>
+          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - L1</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>79.98999999999999</v>
+        <v>199.99</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-starrypad-pro-midi-controller</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Donner MH1 Casque de monitoring</t>
+          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - KB-32M</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>59.99</v>
+        <v>119.99</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-mh1-sound-monitor-headphones</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Donner Sac de Transport pour Clavier 88 Touches</t>
+          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - Pack</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>39.99</v>
+        <v>319.99</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-88-key-keyboard-gig-bag</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Blanc】</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>439.99</v>
+        <v>259.99</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Noir】</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>439.99</v>
+        <v>459.99</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Donner HUSH X LIVE Guitare de voyage - Version MIYAVI</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>635.99</v>
+        <v>358.99</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - L1</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>199.99</v>
+        <v>259.99</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>119.99</v>
+        <v>459.99</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - Pack</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>319.99</v>
+        <v>358.99</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1143,7 +1143,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1158,7 +1158,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1173,7 +1173,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1188,7 +1188,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1203,7 +1203,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1218,191 +1218,191 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare</t>
+          <t>【Offre exclusive】Donner DED-200Max Batteries Electroniques</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>259.99</v>
+        <v>429.99</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ded-200max-batteries-electroniques</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>459.99</v>
+        <v>259.99</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>358.99</v>
+        <v>259.99</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare</t>
+          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>259.99</v>
+        <v>749.99</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>459.99</v>
+        <v>852.99</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>358.99</v>
+        <v>839.99</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DED-200Max Batteries Electroniques</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>429.99</v>
+        <v>369.99</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ded-200max-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>259.99</v>
+        <v>459.99</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>259.99</v>
+        <v>472.99</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>749.99</v>
+        <v>489.99</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>852.99</v>
+        <v>369.99</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>839.99</v>
+        <v>469.99</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>369.99</v>
+        <v>472.99</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + noir</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>459.99</v>
+        <v>489.99</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1428,142 +1428,142 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - DDP-80 PLUS Piano</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>472.99</v>
+        <v>499.99</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>489.99</v>
+        <v>599.99</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano</t>
+          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>369.99</v>
+        <v>609.99</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + noir</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>469.99</v>
+        <v>309.99</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>472.99</v>
+        <v>408.99</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>489.99</v>
+        <v>509.99</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - DDP-80 PLUS Piano</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>499.99</v>
+        <v>309.99</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>599.99</v>
+        <v>408.99</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>609.99</v>
+        <v>509.99</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1578,7 +1578,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1593,7 +1593,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1608,7 +1608,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1623,7 +1623,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1638,7 +1638,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1653,7 +1653,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1668,7 +1668,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1683,7 +1683,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1698,7 +1698,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1713,7 +1713,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1728,7 +1728,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1743,116 +1743,116 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare</t>
+          <t>Donner DED-100 Batterie électrique</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>309.99</v>
+        <v>399.99</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-100-drum-set</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>408.99</v>
+        <v>219.99</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>509.99</v>
+        <v>329.98</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>309.99</v>
+        <v>329.98</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>408.99</v>
+        <v>359.98</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>509.99</v>
+        <v>319.98</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Donner DED-100 Batterie électrique</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>399.99</v>
+        <v>399.97</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-100-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir + Tourneur de Page</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>219.99</v>
+        <v>399.97</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1863,11 +1863,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>329.98</v>
+        <v>429.97</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1878,232 +1878,232 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir</t>
+          <t>【Boîte ouverte】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>329.98</v>
+        <v>699.99</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s300-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>359.98</v>
+        <v>769.99</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Tourneur de Page</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>319.98</v>
+        <v>849.98</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>399.97</v>
+        <v>849.98</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir + Tourneur de Page</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>399.97</v>
+        <v>875.98</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + DKB-100 Banc De Piano</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>429.97</v>
+        <v>869.98</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>699.99</v>
+        <v>885.98</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s300-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano</t>
+          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>769.99</v>
+        <v>1099.99</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Noir</t>
+          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>849.98</v>
+        <v>1169.99</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc réglable X-Style</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>849.98</v>
+        <v>209.99</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Marron</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>875.98</v>
+        <v>479.99</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + DKB-100 Banc De Piano</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>869.98</v>
+        <v>388.99</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>885.98</v>
+        <v>209.99</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1099.99</v>
+        <v>479.99</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro + Tabouret de batterie DT-50</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1169.99</v>
+        <v>388.99</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2118,7 +2118,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2133,7 +2133,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2148,172 +2148,172 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare</t>
+          <t>Donner Pupitre de batterie</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>209.99</v>
+        <v>39.99</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/donner-drum-music-stand</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Acajou</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>479.99</v>
+        <v>159.99</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + JW Pédale</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Noir</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>388.99</v>
+        <v>159.99</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Sunburst</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>209.99</v>
+        <v>159.99</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + Arena 2000 Pédale</t>
+          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>479.99</v>
+        <v>229.99</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + JW Pédale</t>
+          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>388.99</v>
+        <v>259.99</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Donner Pupitre de batterie</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>39.99</v>
+        <v>239.99</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-drum-music-stand</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Acajou</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>159.99</v>
+        <v>239.99</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Noir</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>159.99</v>
+        <v>239.99</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Sunburst</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>159.99</v>
+        <v>259.99</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>229.99</v>
+        <v>259.99</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2321,273 +2321,273 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst</t>
+          <t>Donner DAM1000 Audio Mixer</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>239.99</v>
+        <v>179.99</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-dam1000-audio-mixer</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel</t>
+          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>239.99</v>
+        <v>599.99</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc</t>
+          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>239.99</v>
+        <v>669.99</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston + Pied</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>259.99</v>
+        <v>165.99</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>259.99</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Pied</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>259.99</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Donner DAM1000 Audio Mixer</t>
+          <t>Donner Go ampli guitare - Donner Go【Noir】</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>179.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dam1000-audio-mixer</t>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro</t>
+          <t>Donner Go ampli guitare - Donner Go II【Noir】</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>599.99</v>
+        <v>129.99</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro + Tabouret de batterie DT-50</t>
+          <t>Donner Go ampli guitare - Donner Go II【Blanc】</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>669.99</v>
+        <v>129.99</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston + Pied</t>
+          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>165.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+          <t>https://fr.donnermusic.com/products/starrycrtl-midi-controller-black</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston</t>
+          <t>【Donner】Pour la différence de prix</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>72.98999999999999</v>
+        <v>180</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+          <t>https://fr.donnermusic.com/products/donner-pour-la-difference-de-prix</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Pied</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>92.98999999999999</v>
+        <v>459.99</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go【Noir】</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>89.98999999999999</v>
+        <v>529.99</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go II【Noir】</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>129.99</v>
+        <v>549.99</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go II【Blanc】</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>129.99</v>
+        <v>569.99</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>69.98999999999999</v>
+        <v>399.99</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/starrycrtl-midi-controller-black</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>【Donner】Pour la différence de prix</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>180</v>
+        <v>485.99</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-pour-la-difference-de-prix</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>459.99</v>
+        <v>489.99</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -2598,11 +2598,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>529.99</v>
+        <v>509.99</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -2613,476 +2613,476 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>549.99</v>
+        <v>159.99</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-cv-3-wireless-in-ear-monitoring-system</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>569.99</v>
+        <v>209.99</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>399.99</v>
+        <v>209.99</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>485.99</v>
+        <v>209.99</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>489.99</v>
+        <v>209.99</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DED-200X Batterie Électronique - Nouvelle 5 Tambours et 4 Cymbales</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>509.99</v>
+        <v>599.99</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
+          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 4 Cymbales</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>159.99</v>
+        <v>499.99</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-cv-3-wireless-in-ear-monitoring-system</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
+          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 3 Cymbales</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>209.99</v>
+        <v>589.99</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
+          <t>Donner Beat Go Kit de batterie électronique portable</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>209.99</v>
+        <v>289.99</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-beat-go-portable-electronic-drum-kit</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>209.99</v>
+        <v>119.99</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>209.99</v>
+        <v>119.99</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - Nouvelle 5 Tambours et 4 Cymbales</t>
+          <t>Donner Table de percussion</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>599.99</v>
+        <v>39.99</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
+          <t>https://fr.donnermusic.com/products/donner-percussion-table</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 4 Cymbales</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>499.99</v>
+        <v>599.99</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 3 Cymbales</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>589.99</v>
+        <v>699.99</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Donner Beat Go Kit de batterie électronique portable</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>289.99</v>
+        <v>699.99</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-beat-go-portable-electronic-drum-kit</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>119.99</v>
+        <v>599.99</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>119.99</v>
+        <v>699.99</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Donner Table de percussion</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>39.99</v>
+        <v>699.99</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-percussion-table</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Bleu clair</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>599.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Rose clair</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>699.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Bleu clair</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>699.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Rose clair</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>599.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>699.99</v>
+        <v>269.99</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-70l-electronic-drum-kit-with-led-light</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>699.99</v>
+        <v>149.99</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-starrykey-37-play-midi-controller</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Bleu clair</t>
+          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>69.98999999999999</v>
+        <v>129.99</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/donner-dda-20se-drum-monitor-speaker</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Rose clair</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>69.98999999999999</v>
+        <v>329.99</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Bleu clair</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>89.98999999999999</v>
+        <v>419.99</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Rose clair</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>89.98999999999999</v>
+        <v>419.99</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>269.99</v>
+        <v>432.99</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-70l-electronic-drum-kit-with-led-light</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>149.99</v>
+        <v>489.99</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-starrykey-37-play-midi-controller</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>129.99</v>
+        <v>489.99</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dda-20se-drum-monitor-speaker</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>329.99</v>
+        <v>502.99</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -3093,11 +3093,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>419.99</v>
+        <v>449.99</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -3108,206 +3108,206 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>419.99</v>
+        <v>829.99</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>432.99</v>
+        <v>909.99</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>489.99</v>
+        <v>925.99</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>489.99</v>
+        <v>899.99</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>502.99</v>
+        <v>979.99</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>449.99</v>
+        <v>999.99</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
+          <t>Eastar EDA-100 Digital Aerophone Noir</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>829.99</v>
+        <v>119.99</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/eastar-digital-aerophone-eda-100-noir</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>909.99</v>
+        <v>279.99</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>925.99</v>
+        <v>322.99</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>899.99</v>
+        <v>418.99</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>979.99</v>
+        <v>419.98</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>999.99</v>
+        <v>369.98</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Eastar EDA-100 Digital Aerophone Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>119.99</v>
+        <v>369.98</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-digital-aerophone-eda-100-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>279.99</v>
+        <v>299.99</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -3318,11 +3318,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + MH1 Casque</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>322.99</v>
+        <v>341.99</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -3333,11 +3333,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>418.99</v>
+        <v>398.99</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -3348,11 +3348,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>419.98</v>
+        <v>399.98</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -3363,11 +3363,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>369.98</v>
+        <v>352.98</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -3378,11 +3378,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>369.98</v>
+        <v>352.98</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -3393,11 +3393,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>299.99</v>
+        <v>279.99</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -3408,11 +3408,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + MH1 Casque</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>341.99</v>
+        <v>322.99</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -3423,11 +3423,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>398.99</v>
+        <v>418.99</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -3438,11 +3438,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>399.98</v>
+        <v>419.98</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -3453,11 +3453,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>352.98</v>
+        <v>369.98</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -3468,11 +3468,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>352.98</v>
+        <v>369.98</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -3483,11 +3483,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>279.99</v>
+        <v>299.99</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -3498,11 +3498,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + MH1 Casque</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>322.99</v>
+        <v>341.99</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -3513,11 +3513,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>418.99</v>
+        <v>398.99</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -3528,11 +3528,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>419.98</v>
+        <v>399.98</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -3543,11 +3543,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>369.98</v>
+        <v>352.98</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -3558,11 +3558,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>369.98</v>
+        <v>352.98</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -3573,157 +3573,157 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
+          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>299.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-dks-200-heavy-duty-keyboard-stand-black</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + MH1 Casque</t>
+          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>341.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-pocket-go-portable-preset-pedal-multi-effects-processor-for-guitar</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
+          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>398.99</v>
+        <v>126.99</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-mamp2-2-channel-amplifier</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
+          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>399.98</v>
+        <v>62.99</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/starrypad-mini-midi-controller</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>352.98</v>
+        <v>59.99</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>352.98</v>
+        <v>56.99</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
+          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>99.98999999999999</v>
+        <v>119.99</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dks-200-heavy-duty-keyboard-stand-black</t>
+          <t>https://fr.donnermusic.com/products/donner-duet-adjustable-height-piano-bench-with-music-storage-black</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>99.98999999999999</v>
+        <v>303.99</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-pocket-go-portable-preset-pedal-multi-effects-processor-for-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>126.99</v>
+        <v>303.99</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-mamp2-2-channel-amplifier</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
+          <t>Donner Banquette Piano Duo Réglable Confort</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>62.99</v>
+        <v>115.99</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/starrypad-mini-midi-controller</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench-brown-matt</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
+          <t>Donner M100 Casque de monitoring studio</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -3731,149 +3731,149 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
+          <t>https://fr.donnermusic.com/products/donner-m100-studio-monitor-headphones</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
+          <t>Donner DEP-08 Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>56.99</v>
+        <v>229.99</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>119.99</v>
+        <v>319.99</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-duet-adjustable-height-piano-bench-with-music-storage-black</t>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>303.99</v>
+        <v>319.99</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>303.99</v>
+        <v>169.99</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable Confort</t>
+          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>115.99</v>
+        <v>259.99</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench-brown-matt</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Donner M100 Casque de monitoring studio</t>
+          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>59.99</v>
+        <v>269.99</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-m100-studio-monitor-headphones</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano</t>
+          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>229.99</v>
+        <v>367.99</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
+          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>319.99</v>
+        <v>299.99</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
+          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>319.99</v>
+        <v>392.99</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
+          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -3881,258 +3881,258 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
+          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70 + MH1 Casque + Plateau pour batterie</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>289.99</v>
+        <v>284.99</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
+          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Noir</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>299.99</v>
+        <v>219.99</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
+          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Blanc</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>299.99</v>
+        <v>219.99</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
+          <t>Donner Essential L1 Synthétiseur - L1</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>367.99</v>
+        <v>279.99</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
+          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>392.99</v>
+        <v>119.99</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70</t>
+          <t>Donner Essential L1 Synthétiseur - Pack</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>199.99</v>
+        <v>399.98</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70 + MH1 Casque + Plateau pour batterie</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>284.99</v>
+        <v>899.99</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Noir</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>219.99</v>
+        <v>899.99</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Blanc</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>219.99</v>
+        <v>899.99</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - L1</t>
+          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>279.99</v>
+        <v>102.99</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+          <t>https://fr.donnermusic.com/products/donner-dkb-100-home-style-solid-wood-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>119.99</v>
+        <v>409.99</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - Pack</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>399.98</v>
+        <v>498.99</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>899.99</v>
+        <v>499.98</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>899.99</v>
+        <v>409.99</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>899.99</v>
+        <v>498.99</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>102.99</v>
+        <v>499.98</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dkb-100-home-style-solid-wood-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>409.99</v>
+        <v>399.99</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -4143,11 +4143,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>498.99</v>
+        <v>474.99</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -4173,11 +4173,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>409.99</v>
+        <v>399.99</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -4203,7 +4203,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -4218,206 +4218,206 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>399.99</v>
+        <v>899.99</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>474.99</v>
+        <v>899.99</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>499.98</v>
+        <v>899.99</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>399.99</v>
+        <v>899.99</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>498.99</v>
+        <v>899.99</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>499.98</v>
+        <v>899.99</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>899.99</v>
+        <v>109.99</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/pedale-de-delay-et-de-reverberation-donner-yellow-fall-ii</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>899.99</v>
+        <v>359.99</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>899.99</v>
+        <v>446.99</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>899.99</v>
+        <v>549.98</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>899.99</v>
+        <v>584.99</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>899.99</v>
+        <v>359.99</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>109.99</v>
+        <v>446.99</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/pedale-de-delay-et-de-reverberation-donner-yellow-fall-ii</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>359.99</v>
+        <v>549.98</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -4428,11 +4428,11 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>446.99</v>
+        <v>584.99</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -4443,146 +4443,146 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>Donner DED-300X Batterie Electronique</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>549.98</v>
+        <v>539.99</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/batterie-electronique-donner-ded-300x-5-tambours-4-cymbales</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>584.99</v>
+        <v>129.99</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>359.99</v>
+        <v>129.99</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>446.99</v>
+        <v>685.99</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>549.98</v>
+        <v>769.99</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>584.99</v>
+        <v>749.99</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Donner DED-300X Batterie Electronique</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>539.99</v>
+        <v>839.99</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/batterie-electronique-donner-ded-300x-5-tambours-4-cymbales</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>129.99</v>
+        <v>819.99</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>129.99</v>
+        <v>775.99</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>685.99</v>
+        <v>779.99</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -4593,11 +4593,11 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>769.99</v>
+        <v>685.99</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -4608,11 +4608,11 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>749.99</v>
+        <v>769.99</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -4623,11 +4623,11 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>839.99</v>
+        <v>749.99</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -4638,11 +4638,11 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>819.99</v>
+        <v>839.99</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -4653,11 +4653,11 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>775.99</v>
+        <v>819.99</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -4668,11 +4668,11 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>779.99</v>
+        <v>775.99</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -4683,11 +4683,11 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>685.99</v>
+        <v>779.99</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -4698,371 +4698,371 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
+          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>769.99</v>
+        <v>102.99</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/dkb-200-home-style-corrosion-resistant-metal-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>749.99</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>839.99</v>
+        <v>109.99</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>819.99</v>
+        <v>99</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/pedale-deffet-guitare-donner-triple-threat</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DT-50 Tabouret de Batterie</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>775.99</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/siege-de-batterie-mince-donner-dt-50-marron</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DST-550 Guitare Électrique - Bleu</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>779.99</v>
+        <v>169.99</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
+          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>102.99</v>
+        <v>199.99</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dkb-200-home-style-corrosion-resistant-metal-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
+          <t>Donner DST-550 Guitare Électrique - Blanc</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>92.98999999999999</v>
+        <v>169.99</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>109.99</v>
+        <v>289.99</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>99</v>
+        <v>379.99</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/pedale-deffet-guitare-donner-triple-threat</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Donner DT-50 Tabouret de Batterie</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>72.98999999999999</v>
+        <v>279.99</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/siege-de-batterie-mince-donner-dt-50-marron</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Bleu</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>169.99</v>
+        <v>379.99</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>199.99</v>
+        <v>389.99</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Blanc</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>169.99</v>
+        <v>489.99</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>289.99</v>
+        <v>509.99</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>379.99</v>
+        <v>389.99</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>279.99</v>
+        <v>479.99</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>379.99</v>
+        <v>509.99</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>389.99</v>
+        <v>179.99</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>489.99</v>
+        <v>269.99</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>509.99</v>
+        <v>279.99</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>389.99</v>
+        <v>289.99</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>479.99</v>
+        <v>339.99</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>509.99</v>
+        <v>349.99</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>179.99</v>
+        <v>359.99</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -5073,11 +5073,11 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>269.99</v>
+        <v>295.99</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -5088,11 +5088,11 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>279.99</v>
+        <v>365.99</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -5103,11 +5103,11 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>289.99</v>
+        <v>209.99</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -5118,11 +5118,11 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>339.99</v>
+        <v>284.99</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -5133,11 +5133,11 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>349.99</v>
+        <v>315.99</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -5148,11 +5148,11 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>359.99</v>
+        <v>309.99</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -5163,11 +5163,11 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>295.99</v>
+        <v>359.99</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -5178,11 +5178,11 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>365.99</v>
+        <v>385.99</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -5193,11 +5193,11 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>209.99</v>
+        <v>379.99</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -5208,11 +5208,11 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>284.99</v>
+        <v>319.99</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -5223,11 +5223,11 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>315.99</v>
+        <v>389.99</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -5238,11 +5238,11 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>309.99</v>
+        <v>189.99</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -5253,11 +5253,11 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>359.99</v>
+        <v>269.99</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -5268,11 +5268,11 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>385.99</v>
+        <v>279.99</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -5283,11 +5283,11 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>379.99</v>
+        <v>282.99</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -5298,11 +5298,11 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>319.99</v>
+        <v>335.99</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -5313,11 +5313,11 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>389.99</v>
+        <v>343.99</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -5328,11 +5328,11 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>189.99</v>
+        <v>352.99</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -5343,11 +5343,11 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>269.99</v>
+        <v>285.99</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -5358,11 +5358,11 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>279.99</v>
+        <v>355.99</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -5373,11 +5373,11 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>282.99</v>
+        <v>209.99</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -5388,11 +5388,11 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>335.99</v>
+        <v>284.99</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -5403,11 +5403,11 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>343.99</v>
+        <v>315.99</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -5418,11 +5418,11 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>352.99</v>
+        <v>309.99</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -5433,11 +5433,11 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>285.99</v>
+        <v>359.99</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -5448,11 +5448,11 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>355.99</v>
+        <v>385.99</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -5463,11 +5463,11 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>209.99</v>
+        <v>379.99</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -5478,11 +5478,11 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>284.99</v>
+        <v>319.99</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -5493,11 +5493,11 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>315.99</v>
+        <v>389.99</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -5508,127 +5508,127 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>309.99</v>
+        <v>169.99</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>359.99</v>
+        <v>239.99</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>385.99</v>
+        <v>359.99</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>379.99</v>
+        <v>496.99</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>319.99</v>
+        <v>408.99</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>389.99</v>
+        <v>359.99</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>169.99</v>
+        <v>496.99</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>239.99</v>
+        <v>408.99</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -5643,7 +5643,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -5658,7 +5658,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -5673,7 +5673,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -5688,7 +5688,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -5703,7 +5703,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -5718,7 +5718,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -5733,7 +5733,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -5748,7 +5748,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -5763,7 +5763,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -5778,7 +5778,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -5793,7 +5793,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -5808,217 +5808,217 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>Donner DED-200 Max Batteries Electroniques</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>359.99</v>
+        <v>499.99</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-max-batteries-electroniques</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>496.99</v>
+        <v>1099.99</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>408.99</v>
+        <v>1114.99</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>359.99</v>
+        <v>899</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>496.99</v>
+        <v>899</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>408.99</v>
+        <v>899</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Donner DED-200 Max Batteries Electroniques</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>499.99</v>
+        <v>125.99</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-200-max-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>1099.99</v>
+        <v>166.99</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>1114.99</v>
+        <v>299.99</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>899</v>
+        <v>486.99</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>899</v>
+        <v>398.99</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>899</v>
+        <v>299.99</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>125.99</v>
+        <v>486.99</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>166.99</v>
+        <v>398.99</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -6033,7 +6033,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -6048,7 +6048,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -6063,7 +6063,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -6078,7 +6078,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -6093,7 +6093,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -6108,116 +6108,116 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>299.99</v>
+        <v>109.99</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-banquette-de-piano-en-bois-massif-avec-espace-de-rangement</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>486.99</v>
+        <v>319.99</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>398.99</v>
+        <v>408.99</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>299.99</v>
+        <v>419.99</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>486.99</v>
+        <v>419.99</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>398.99</v>
+        <v>435.99</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>109.99</v>
+        <v>489.99</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-banquette-de-piano-en-bois-massif-avec-espace-de-rangement</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>319.99</v>
+        <v>439.99</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -6228,11 +6228,11 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>408.99</v>
+        <v>509.99</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -6243,11 +6243,11 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>419.99</v>
+        <v>439.99</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -6258,11 +6258,11 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>419.99</v>
+        <v>329.99</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -6273,11 +6273,11 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>435.99</v>
+        <v>418.99</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -6288,11 +6288,11 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>489.99</v>
+        <v>429.99</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
@@ -6303,11 +6303,11 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>439.99</v>
+        <v>429.99</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -6318,11 +6318,11 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>509.99</v>
+        <v>445.99</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -6333,11 +6333,11 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>439.99</v>
+        <v>499.99</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
@@ -6348,11 +6348,11 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>329.99</v>
+        <v>449.99</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -6363,11 +6363,11 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>418.99</v>
+        <v>519.99</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -6378,11 +6378,11 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>429.99</v>
+        <v>449.99</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -6393,101 +6393,101 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>429.99</v>
+        <v>499.99</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>445.99</v>
+        <v>599.99</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>499.99</v>
+        <v>609.99</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>449.99</v>
+        <v>686.99</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>519.99</v>
+        <v>696.99</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>449.99</v>
+        <v>615.99</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>499.99</v>
+        <v>685.99</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -6498,11 +6498,11 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>599.99</v>
+        <v>619.99</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -6513,11 +6513,11 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>609.99</v>
+        <v>689.99</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
@@ -6528,11 +6528,11 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>686.99</v>
+        <v>619.99</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
@@ -6543,101 +6543,101 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>696.99</v>
+        <v>629.99</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>615.99</v>
+        <v>729.99</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>685.99</v>
+        <v>816.99</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>619.99</v>
+        <v>719.99</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>689.99</v>
+        <v>749.99</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>619.99</v>
+        <v>749.99</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>629.99</v>
+        <v>761.99</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
@@ -6648,11 +6648,11 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>729.99</v>
+        <v>851.99</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -6663,11 +6663,11 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>816.99</v>
+        <v>927.99</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -6678,11 +6678,11 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>719.99</v>
+        <v>840.99</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -6693,11 +6693,11 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>749.99</v>
+        <v>977.99</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
@@ -6708,101 +6708,101 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>749.99</v>
+        <v>629.99</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>761.99</v>
+        <v>729.99</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>851.99</v>
+        <v>816.99</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>927.99</v>
+        <v>745.99</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>840.99</v>
+        <v>815.99</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>977.99</v>
+        <v>749.99</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>629.99</v>
+        <v>819.99</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -6813,11 +6813,11 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>729.99</v>
+        <v>559.99</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -6828,11 +6828,11 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>816.99</v>
+        <v>659.99</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -6843,11 +6843,11 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>745.99</v>
+        <v>746.99</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -6858,11 +6858,11 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>815.99</v>
+        <v>675.99</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -6873,11 +6873,11 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>749.99</v>
+        <v>745.99</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -6888,11 +6888,11 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>819.99</v>
+        <v>679.99</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -6903,11 +6903,11 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>559.99</v>
+        <v>749.99</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -6918,161 +6918,161 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
+          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>659.99</v>
+        <v>186.99</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-arena-2000</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>746.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>675.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DMK-25 Pro Clavier MIDI</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>745.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dmk-25-pro-midi-keyboard</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>679.99</v>
+        <v>236.99</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>749.99</v>
+        <v>335.99</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>186.99</v>
+        <v>423.99</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-arena-2000</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>99.98999999999999</v>
+        <v>219.99</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>99.98999999999999</v>
+        <v>335.99</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Donner DMK-25 Pro Clavier MIDI</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>89.98999999999999</v>
+        <v>423.99</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dmk-25-pro-midi-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>236.99</v>
+        <v>281.99</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -7083,11 +7083,11 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>335.99</v>
+        <v>373.99</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
@@ -7098,11 +7098,11 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>423.99</v>
+        <v>530.99</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -7113,142 +7113,142 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
+          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>219.99</v>
+        <v>89</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-b1-syn-the-ti-seurs-sequencer</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>335.99</v>
+        <v>109.99</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/banc-de-piano-tabouret-en-bois-dur-et-solide</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Pour la différence de prix</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>423.99</v>
+        <v>30</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/for-the-price-difference</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>281.99</v>
+        <v>152.99</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>373.99</v>
+        <v>339.99</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>530.99</v>
+        <v>152.99</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>89</v>
+        <v>339.99</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-b1-syn-the-ti-seurs-sequencer</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>109.99</v>
+        <v>152.99</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/banc-de-piano-tabouret-en-bois-dur-et-solide</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Pour la différence de prix</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>30</v>
+        <v>339.99</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/for-the-price-difference</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -7263,7 +7263,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -7278,131 +7278,131 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>152.99</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>339.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>152.99</v>
+        <v>389.99</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>339.99</v>
+        <v>479.99</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>152.99</v>
+        <v>479.99</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>339.99</v>
+        <v>489.99</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>86.98999999999999</v>
+        <v>509.99</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>69.98999999999999</v>
+        <v>389.99</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>389.99</v>
+        <v>479.99</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -7428,11 +7428,11 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>479.99</v>
+        <v>489.99</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
@@ -7443,11 +7443,11 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>489.99</v>
+        <v>509.99</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
@@ -7458,146 +7458,146 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>509.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>389.99</v>
+        <v>79.47</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>479.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-piano-bench-keyboard-stool-solid-hard-wooden-digital-piano-stool-with-large-storage-black</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>479.99</v>
+        <v>469.99</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>489.99</v>
+        <v>518.99</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>509.99</v>
+        <v>566.99</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>89.98999999999999</v>
+        <v>557.99</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>79.47</v>
+        <v>636.99</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>89.98999999999999</v>
+        <v>627.99</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-piano-bench-keyboard-stool-solid-hard-wooden-digital-piano-stool-with-large-storage-black</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>469.99</v>
+        <v>549.99</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
@@ -7608,11 +7608,11 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>518.99</v>
+        <v>569.99</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
@@ -7623,11 +7623,11 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>566.99</v>
+        <v>629.99</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
@@ -7638,11 +7638,11 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>557.99</v>
+        <v>585.99</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
@@ -7653,11 +7653,11 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>636.99</v>
+        <v>645.99</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
@@ -7668,11 +7668,11 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>627.99</v>
+        <v>589.99</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
@@ -7683,11 +7683,11 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>549.99</v>
+        <v>429.99</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
@@ -7698,11 +7698,11 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>569.99</v>
+        <v>536.99</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
@@ -7713,11 +7713,11 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>629.99</v>
+        <v>527.99</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
@@ -7728,11 +7728,11 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>585.99</v>
+        <v>606.99</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
@@ -7743,11 +7743,11 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>645.99</v>
+        <v>597.99</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
@@ -7758,11 +7758,11 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>589.99</v>
+        <v>519.99</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
@@ -7773,11 +7773,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>429.99</v>
+        <v>539.99</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
@@ -7788,11 +7788,11 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>536.99</v>
+        <v>599.99</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
@@ -7803,11 +7803,11 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>527.99</v>
+        <v>555.99</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
@@ -7818,11 +7818,11 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>606.99</v>
+        <v>615.99</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
@@ -7833,11 +7833,11 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>597.99</v>
+        <v>549.99</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
@@ -7848,11 +7848,11 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>519.99</v>
+        <v>559.98</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
@@ -7863,11 +7863,11 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>539.99</v>
+        <v>469.99</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
@@ -7878,11 +7878,11 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>599.99</v>
+        <v>518.99</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
@@ -7893,11 +7893,11 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>555.99</v>
+        <v>566.99</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
@@ -7908,11 +7908,11 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>615.99</v>
+        <v>557.99</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
@@ -7923,11 +7923,11 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>549.99</v>
+        <v>636.99</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
@@ -7938,11 +7938,11 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>559.98</v>
+        <v>627.99</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
@@ -7953,11 +7953,11 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>469.99</v>
+        <v>549.99</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
@@ -7968,11 +7968,11 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>518.99</v>
+        <v>569.99</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
@@ -7983,11 +7983,11 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>566.99</v>
+        <v>629.99</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
@@ -7998,11 +7998,11 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>557.99</v>
+        <v>585.99</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
@@ -8013,11 +8013,11 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>636.99</v>
+        <v>645.99</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
@@ -8028,11 +8028,11 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>627.99</v>
+        <v>589.99</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
@@ -8043,11 +8043,11 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>549.99</v>
+        <v>429.99</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
@@ -8058,11 +8058,11 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>569.99</v>
+        <v>499.99</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
@@ -8073,11 +8073,11 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>629.99</v>
+        <v>536.99</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
@@ -8088,11 +8088,11 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>585.99</v>
+        <v>527.99</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
@@ -8103,11 +8103,11 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>645.99</v>
+        <v>606.99</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
@@ -8118,11 +8118,11 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>589.99</v>
+        <v>597.99</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
@@ -8133,11 +8133,11 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>429.99</v>
+        <v>519.99</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
@@ -8148,11 +8148,11 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>499.99</v>
+        <v>539.99</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
@@ -8163,11 +8163,11 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>536.99</v>
+        <v>599.99</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
@@ -8178,11 +8178,11 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>527.99</v>
+        <v>555.99</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
@@ -8193,11 +8193,11 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>606.99</v>
+        <v>615.99</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
@@ -8208,103 +8208,13 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B519" t="n">
-        <v>597.99</v>
+        <v>549.99</v>
       </c>
       <c r="C519" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
-        </is>
-      </c>
-      <c r="B520" t="n">
-        <v>519.99</v>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
-        </is>
-      </c>
-      <c r="B521" t="n">
-        <v>539.99</v>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
-        </is>
-      </c>
-      <c r="B522" t="n">
-        <v>599.99</v>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
-        </is>
-      </c>
-      <c r="B523" t="n">
-        <v>555.99</v>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
-        </is>
-      </c>
-      <c r="B524" t="n">
-        <v>615.99</v>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
-        </is>
-      </c>
-      <c r="B525" t="n">
-        <v>549.99</v>
-      </c>
-      <c r="C525" t="inlineStr">
         <is>
           <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C519"/>
+  <dimension ref="A1:C523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -453,71 +453,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano</t>
+          <t>Donner Set Mini-Maestros : Clavier Portable KIDO &amp; Clavier DEK-32 pour Débutants - KIDO 32 Touches Bleu + DEK-32 Blanc</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>679.99</v>
+        <v>132.99</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dgp-100-lightweight-grand-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-set-mini-maestros-clavier-portable-kido-clavier-dek-32-pour-debutants</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + Banc réglable X-Style</t>
+          <t>Donner Set Mini-Maestros : Clavier Portable KIDO &amp; Clavier DEK-32 pour Débutants - KIDO 32 Touches Rose + DEK-32 Rose</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>739.99</v>
+        <v>132.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dgp-100-lightweight-grand-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-set-mini-maestros-clavier-portable-kido-clavier-dek-32-pour-debutants</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + DKB-100 Tabouret Bois Massif</t>
+          <t>Donner DEP-1S Ensemble Joyeux de Famille : Style Bois Piano Numérique + Clavier Enfant KIDO 44 Touches - DEP-1S couleur bois naturel【Nouvelle version】 + KIDO 44 Bleu</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>759.99</v>
+        <v>284.99</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dgp-100-lightweight-grand-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-ensemble-joyeux-de-famille-style-bois-piano-numerique-clavier-enfant-kido-44-touches</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + Banc de piano noir</t>
+          <t>Donner DEP-1S Ensemble Joyeux de Famille : Style Bois Piano Numérique + Clavier Enfant KIDO 44 Touches - DEP-1S couleur bois naturel【Nouvelle version】 + KIDO 44 Rose</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>739.99</v>
+        <v>284.99</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dgp-100-lightweight-grand-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-ensemble-joyeux-de-famille-style-bois-piano-numerique-clavier-enfant-kido-44-touches</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + Banc réglable en hauteur</t>
+          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>775.99</v>
+        <v>679.99</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,11 +528,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + Tabouret de piano blanc</t>
+          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>759.99</v>
+        <v>739.99</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -543,11 +543,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + DKB-100 Tabouret Bois Massif</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>779.99</v>
+        <v>759.99</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -558,176 +558,176 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Donner OURA J100 Piano numérique de salon 88 touches - OURA J100</t>
+          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + Banc de piano noir</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>599.99</v>
+        <v>739.99</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura-j100-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dgp-100-lightweight-grand-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Donner OURA J100 Piano numérique de salon 88 touches - OURA J100 + Banc de piano Beige</t>
+          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>709.99</v>
+        <v>775.99</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura-j100-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dgp-100-lightweight-grand-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Donner OURA J100 Piano numérique de salon 88 touches - OURA J100 + Banc de piano réglable en hauteur Beige</t>
+          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>719.99</v>
+        <v>759.99</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura-j100-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dgp-100-lightweight-grand-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Donner OURA J100 Piano numérique de salon 88 touches - OURA J100 + Banc de piano réglable en hauteur Blanc</t>
+          <t>Donner DGP‑100 Piano Numérique Grand Format Léger - Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>719.99</v>
+        <v>779.99</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura-j100-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dgp-100-lightweight-grand-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Donner VIVA Guitare sans cordes innovante</t>
+          <t>Donner OURA J100 Piano numérique de salon 88 touches - OURA J100</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>329.99</v>
+        <v>599.99</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-viva-stringless-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-oura-j100-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DONNER DKA-50 50W Amplificateur de clavier</t>
+          <t>Donner OURA J100 Piano numérique de salon 88 touches - OURA J100 + Banc de piano Beige</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>259.99</v>
+        <v>709.99</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dka-50-50w-keyboard-amplifier</t>
+          <t>https://fr.donnermusic.com/products/donner-oura-j100-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Banquette de piano assortie</t>
+          <t>Donner OURA J100 Piano numérique de salon 88 touches - OURA J100 + Banc de piano réglable en hauteur Beige</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>119.99</v>
+        <v>719.99</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura-piano-bench-s200</t>
+          <t>https://fr.donnermusic.com/products/donner-oura-j100-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano</t>
+          <t>Donner OURA J100 Piano numérique de salon 88 touches - OURA J100 + Banc de piano réglable en hauteur Blanc</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>529.99</v>
+        <v>719.99</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+          <t>https://fr.donnermusic.com/products/donner-oura-j100-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc réglable X-Style</t>
+          <t>Donner VIVA Guitare sans cordes innovante</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>579.99</v>
+        <v>329.99</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+          <t>https://fr.donnermusic.com/products/donner-viva-stringless-guitar</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano noir</t>
+          <t>DONNER DKA-50 50W Amplificateur de clavier</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>579.99</v>
+        <v>259.99</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+          <t>https://fr.donnermusic.com/products/donner-dka-50-50w-keyboard-amplifier</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner OURA S200 Banquette de piano assortie</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>615.99</v>
+        <v>119.99</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
+          <t>https://fr.donnermusic.com/products/donner-oura-piano-bench-s200</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano Blanc</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>599.99</v>
+        <v>529.99</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -738,86 +738,86 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Donner MAMP8 Ampli AV 5.2 Canaux</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>229.99</v>
+        <v>579.99</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-mamp8-5-2-channel-av-receiver</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>699.99</v>
+        <v>579.99</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + banc de piano</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>799.99</v>
+        <v>615.99</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc (match officiel)</t>
+          <t>Donner DDP-75 Piano Numérique Droit Noir Laqué, 88 Touches à Action de Marteau - Piano + Tabouret de piano Blanc</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>799.99</v>
+        <v>599.99</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-75-flip-top-upright-digital-piano-with-hammer-action</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner MAMP8 Ampli AV 5.2 Canaux</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>819.99</v>
+        <v>229.99</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-mamp8-5-2-channel-av-receiver</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc réglable X-Style</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>779.99</v>
+        <v>699.99</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -828,82 +828,82 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Blanc</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>79.98999999999999</v>
+        <v>799.99</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Rosa</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc (match officiel)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>79.98999999999999</v>
+        <v>799.99</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Cyan</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>79.98999999999999</v>
+        <v>819.99</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Donner SD-15 Clavier électronique 61 touches - Bundle mit Zubehör</t>
+          <t>Donner OURA S200 Piano numérique 88 touches pour la maison - Bleu / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>219.99</v>
+        <v>779.99</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-sd-15-61-key-electronic-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-s200-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Donner SD-15 Clavier électronique 61 touches - Nur das Keyboard</t>
+          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Blanc</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>169.99</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-sd-15-61-key-electronic-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Donner Starrypad Pro Contrôleur MIDI</t>
+          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Rosa</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -911,198 +911,198 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-starrypad-pro-midi-controller</t>
+          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Donner MH1 Casque de monitoring</t>
+          <t>Donner DEK-32 à 32 touches Clavier pour enfant - Cyan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>59.99</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-mh1-sound-monitor-headphones</t>
+          <t>https://fr.donnermusic.com/products/donner-dek-32-32-keys-electronic-keyboard</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Donner Sac de Transport pour Clavier 88 Touches</t>
+          <t>Donner SD-15 Clavier électronique 61 touches - Bundle mit Zubehör</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>39.99</v>
+        <v>219.99</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-88-key-keyboard-gig-bag</t>
+          <t>https://fr.donnermusic.com/products/donner-sd-15-61-key-electronic-keyboard</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Blanc】</t>
+          <t>Donner SD-15 Clavier électronique 61 touches - Nur das Keyboard</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>439.99</v>
+        <v>169.99</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-sd-15-61-key-electronic-keyboard</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Noir】</t>
+          <t>Donner Starrypad Pro Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>439.99</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-starrypad-pro-midi-controller</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Donner HUSH X LIVE Guitare de voyage - Version MIYAVI</t>
+          <t>Donner MH1 Casque de monitoring</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>635.99</v>
+        <v>59.99</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-mh1-sound-monitor-headphones</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - L1</t>
+          <t>Donner Sac de Transport pour Clavier 88 Touches</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>199.99</v>
+        <v>39.99</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+          <t>https://fr.donnermusic.com/products/donner-88-key-keyboard-gig-bag</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Blanc】</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>119.99</v>
+        <v>439.99</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - Pack</t>
+          <t>Donner HUSH X LIVE Guitare de voyage - Version Standard【Noir】</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>319.99</v>
+        <v>439.99</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare</t>
+          <t>Donner HUSH X LIVE Guitare de voyage - Version MIYAVI</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>259.99</v>
+        <v>635.99</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-live-guitar</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - L1</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>459.99</v>
+        <v>199.99</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - KB-32M</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>358.99</v>
+        <v>119.99</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare</t>
+          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - Pack</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>259.99</v>
+        <v>319.99</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>459.99</v>
+        <v>259.99</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1113,11 +1113,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>358.99</v>
+        <v>459.99</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1128,11 +1128,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>259.99</v>
+        <v>358.99</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1143,11 +1143,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>459.99</v>
+        <v>259.99</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1158,11 +1158,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>358.99</v>
+        <v>459.99</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1173,11 +1173,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>259.99</v>
+        <v>358.99</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1188,11 +1188,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>459.99</v>
+        <v>259.99</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1203,11 +1203,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>358.99</v>
+        <v>459.99</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1218,22 +1218,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DED-200Max Batteries Electroniques</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>429.99</v>
+        <v>358.99</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ded-200max-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1241,134 +1241,134 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>259.99</v>
+        <v>459.99</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano</t>
+          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>749.99</v>
+        <v>358.99</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>【Offre exclusive】Donner DED-200Max Batteries Electroniques</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>852.99</v>
+        <v>429.99</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ded-200max-batteries-electroniques</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc</t>
+          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>839.99</v>
+        <v>259.99</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano</t>
+          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>369.99</v>
+        <v>259.99</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + noir</t>
+          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>459.99</v>
+        <v>749.99</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>472.99</v>
+        <v>852.99</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>489.99</v>
+        <v>839.99</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1383,11 +1383,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + noir</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>469.99</v>
+        <v>459.99</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1413,7 +1413,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1428,116 +1428,116 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - DDP-80 PLUS Piano</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>499.99</v>
+        <v>369.99</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>599.99</v>
+        <v>469.99</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>609.99</v>
+        <v>472.99</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>309.99</v>
+        <v>489.99</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - DDP-80 PLUS Piano</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>408.99</v>
+        <v>499.99</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>509.99</v>
+        <v>599.99</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>309.99</v>
+        <v>609.99</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1548,11 +1548,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1563,11 +1563,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>309.99</v>
+        <v>509.99</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1578,11 +1578,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1593,11 +1593,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1608,11 +1608,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>309.99</v>
+        <v>509.99</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1623,11 +1623,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1638,11 +1638,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1653,11 +1653,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>309.99</v>
+        <v>509.99</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1668,11 +1668,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1698,11 +1698,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>309.99</v>
+        <v>509.99</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1713,11 +1713,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>408.99</v>
+        <v>309.99</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1728,11 +1728,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1743,86 +1743,86 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Donner DED-100 Batterie électrique</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>399.99</v>
+        <v>509.99</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-100-drum-set</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>219.99</v>
+        <v>309.99</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>329.98</v>
+        <v>408.99</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir</t>
+          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>329.98</v>
+        <v>509.99</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DED-100 Batterie électrique</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>359.98</v>
+        <v>399.99</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-100-drum-set</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Tourneur de Page</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>319.98</v>
+        <v>219.99</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1833,11 +1833,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>399.97</v>
+        <v>329.98</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir + Tourneur de Page</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>399.97</v>
+        <v>329.98</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1863,11 +1863,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>429.97</v>
+        <v>359.98</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1878,86 +1878,86 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>699.99</v>
+        <v>319.98</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s300-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>769.99</v>
+        <v>399.97</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Noir</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir + Tourneur de Page</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>849.98</v>
+        <v>399.97</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>849.98</v>
+        <v>429.97</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Marron</t>
+          <t>【Boîte ouverte】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>875.98</v>
+        <v>699.99</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s300-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + DKB-100 Banc De Piano</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>869.98</v>
+        <v>769.99</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -1968,11 +1968,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>885.98</v>
+        <v>849.98</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -1983,101 +1983,101 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1099.99</v>
+        <v>849.98</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro + Tabouret de batterie DT-50</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1169.99</v>
+        <v>875.98</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + DKB-100 Banc De Piano</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>209.99</v>
+        <v>869.98</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>479.99</v>
+        <v>885.98</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>388.99</v>
+        <v>1099.99</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare</t>
+          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>209.99</v>
+        <v>1169.99</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>479.99</v>
+        <v>209.99</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2088,11 +2088,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>388.99</v>
+        <v>479.99</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2103,11 +2103,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>209.99</v>
+        <v>388.99</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2118,11 +2118,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>479.99</v>
+        <v>209.99</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2133,11 +2133,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + JW Pédale</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>388.99</v>
+        <v>479.99</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2148,142 +2148,142 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Donner Pupitre de batterie</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>39.99</v>
+        <v>388.99</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-drum-music-stand</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Acajou</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>159.99</v>
+        <v>209.99</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Noir</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>159.99</v>
+        <v>479.99</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Sunburst</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>159.99</v>
+        <v>388.99</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>Donner Pupitre de batterie</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>229.99</v>
+        <v>39.99</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/donner-drum-music-stand</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Acajou</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>259.99</v>
+        <v>159.99</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Noir</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>239.99</v>
+        <v>159.99</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Sunburst</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>239.99</v>
+        <v>159.99</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc</t>
+          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>239.99</v>
+        <v>229.99</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï</t>
+          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2291,18 +2291,18 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>259.99</v>
+        <v>239.99</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2313,11 +2313,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>259.99</v>
+        <v>239.99</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2328,251 +2328,251 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Donner DAM1000 Audio Mixer</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>179.99</v>
+        <v>239.99</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dam1000-audio-mixer</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>599.99</v>
+        <v>259.99</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro + Tabouret de batterie DT-50</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>669.99</v>
+        <v>259.99</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston + Pied</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>165.99</v>
+        <v>259.99</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston</t>
+          <t>Donner DAM1000 Audio Mixer</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>72.98999999999999</v>
+        <v>179.99</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+          <t>https://fr.donnermusic.com/products/donner-dam1000-audio-mixer</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Pied</t>
+          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>92.98999999999999</v>
+        <v>599.99</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go【Noir】</t>
+          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>89.98999999999999</v>
+        <v>669.99</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go II【Noir】</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston + Pied</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>129.99</v>
+        <v>165.99</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Donner Go ampli guitare - Donner Go II【Blanc】</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>129.99</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Pied</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>69.98999999999999</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/starrycrtl-midi-controller-black</t>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>【Donner】Pour la différence de prix</t>
+          <t>Donner Go Ampli Guitare - Donner Go【Noir】</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>180</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-pour-la-difference-de-prix</t>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>Donner Go Ampli Guitare - Donner Go【Jaune】</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>459.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>Donner Go Ampli Guitare - Donner Go II【Noir】</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>529.99</v>
+        <v>129.99</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>Donner Go Ampli Guitare - Donner Go II【Blanc】</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>549.99</v>
+        <v>129.99</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>569.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/starrycrtl-midi-controller-black</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>【Donner】Pour la différence de prix</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>399.99</v>
+        <v>180</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-pour-la-difference-de-prix</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>485.99</v>
+        <v>459.99</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -2583,11 +2583,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>489.99</v>
+        <v>529.99</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -2598,11 +2598,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>509.99</v>
+        <v>549.99</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -2613,251 +2613,251 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>159.99</v>
+        <v>569.99</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-cv-3-wireless-in-ear-monitoring-system</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>209.99</v>
+        <v>399.99</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>209.99</v>
+        <v>485.99</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>209.99</v>
+        <v>489.99</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>209.99</v>
+        <v>509.99</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - Nouvelle 5 Tambours et 4 Cymbales</t>
+          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>599.99</v>
+        <v>159.99</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
+          <t>https://fr.donnermusic.com/products/donner-cv-3-wireless-in-ear-monitoring-system</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 4 Cymbales</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>499.99</v>
+        <v>209.99</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique - 5 Tambours et 3 Cymbales</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>589.99</v>
+        <v>209.99</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Donner Beat Go Kit de batterie électronique portable</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>289.99</v>
+        <v>209.99</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-beat-go-portable-electronic-drum-kit</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>119.99</v>
+        <v>209.99</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
+          <t>Donner DED-200X Batterie Électronique【Version mise à niveau disponible】 - DED-200X Mise à niveau</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>119.99</v>
+        <v>599.99</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Donner Table de percussion</t>
+          <t>Donner DED-200X Batterie Électronique【Version mise à niveau disponible】 - DED-200X</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>39.99</v>
+        <v>499.99</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-percussion-table</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner Beat Go Kit de batterie électronique portable</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>599.99</v>
+        <v>289.99</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-beat-go-portable-electronic-drum-kit</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>699.99</v>
+        <v>119.99</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>699.99</v>
+        <v>119.99</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>Donner Table de percussion</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>599.99</v>
+        <v>39.99</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-percussion-table</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>699.99</v>
+        <v>599.99</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -2883,176 +2883,176 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Bleu clair</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>69.98999999999999</v>
+        <v>699.99</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Rose clair</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>69.98999999999999</v>
+        <v>599.99</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Bleu clair</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>89.98999999999999</v>
+        <v>699.99</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Rose clair</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>89.98999999999999</v>
+        <v>699.99</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Bleu clair</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>269.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-70l-electronic-drum-kit-with-led-light</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Rose clair</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>149.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-starrykey-37-play-midi-controller</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Bleu clair</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>129.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dda-20se-drum-monitor-speaker</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Rose clair</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>329.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
+          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>419.99</v>
+        <v>269.99</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-70l-electronic-drum-kit-with-led-light</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>419.99</v>
+        <v>149.99</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/donner-starrykey-37-play-midi-controller</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
+          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>432.99</v>
+        <v>129.99</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/donner-dda-20se-drum-monitor-speaker</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>489.99</v>
+        <v>329.99</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -3063,11 +3063,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>489.99</v>
+        <v>419.99</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -3078,11 +3078,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>502.99</v>
+        <v>419.99</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -3093,11 +3093,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>449.99</v>
+        <v>432.99</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -3108,71 +3108,71 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>829.99</v>
+        <v>489.99</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>909.99</v>
+        <v>489.99</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>925.99</v>
+        <v>502.99</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>899.99</v>
+        <v>449.99</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>979.99</v>
+        <v>829.99</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -3183,11 +3183,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>999.99</v>
+        <v>909.99</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -3198,86 +3198,86 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Eastar EDA-100 Digital Aerophone Noir</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>119.99</v>
+        <v>925.99</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-digital-aerophone-eda-100-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>279.99</v>
+        <v>899.99</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + MH1 Casque</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>322.99</v>
+        <v>979.99</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>418.99</v>
+        <v>999.99</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
+          <t>Eastar EDA-100 Digital Aerophone Noir</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>419.98</v>
+        <v>119.99</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/eastar-digital-aerophone-eda-100-noir</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>369.98</v>
+        <v>279.99</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -3288,11 +3288,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>369.98</v>
+        <v>322.99</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -3303,11 +3303,11 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>299.99</v>
+        <v>418.99</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -3318,11 +3318,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + MH1 Casque</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>341.99</v>
+        <v>419.98</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -3333,11 +3333,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>398.99</v>
+        <v>369.98</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -3348,11 +3348,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>399.98</v>
+        <v>369.98</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -3363,11 +3363,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>352.98</v>
+        <v>299.99</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -3378,11 +3378,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>352.98</v>
+        <v>341.99</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -3393,11 +3393,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>279.99</v>
+        <v>398.99</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -3408,11 +3408,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + MH1 Casque</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>322.99</v>
+        <v>399.98</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -3423,11 +3423,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>418.99</v>
+        <v>352.98</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -3438,11 +3438,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>419.98</v>
+        <v>352.98</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -3453,11 +3453,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>369.98</v>
+        <v>279.99</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -3468,11 +3468,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>369.98</v>
+        <v>322.99</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -3483,11 +3483,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>299.99</v>
+        <v>418.99</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -3498,11 +3498,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + MH1 Casque</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>341.99</v>
+        <v>419.98</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -3513,11 +3513,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>398.99</v>
+        <v>369.98</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -3528,11 +3528,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>399.98</v>
+        <v>369.98</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -3543,11 +3543,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>352.98</v>
+        <v>299.99</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -3558,11 +3558,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>352.98</v>
+        <v>341.99</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -3573,281 +3573,281 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>99.98999999999999</v>
+        <v>398.99</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dks-200-heavy-duty-keyboard-stand-black</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>99.98999999999999</v>
+        <v>399.98</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-pocket-go-portable-preset-pedal-multi-effects-processor-for-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>126.99</v>
+        <v>352.98</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-mamp2-2-channel-amplifier</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>62.99</v>
+        <v>352.98</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/starrypad-mini-midi-controller</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
+          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>59.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
+          <t>https://fr.donnermusic.com/products/donner-dks-200-heavy-duty-keyboard-stand-black</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
+          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>56.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
+          <t>https://fr.donnermusic.com/products/donner-pocket-go-portable-preset-pedal-multi-effects-processor-for-guitar</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
+          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>119.99</v>
+        <v>126.99</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-duet-adjustable-height-piano-bench-with-music-storage-black</t>
+          <t>https://fr.donnermusic.com/products/donner-mamp2-2-channel-amplifier</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>303.99</v>
+        <v>62.99</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
+          <t>https://fr.donnermusic.com/products/starrypad-mini-midi-controller</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>303.99</v>
+        <v>59.99</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
+          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable Confort</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>115.99</v>
+        <v>56.99</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench-brown-matt</t>
+          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Donner M100 Casque de monitoring studio</t>
+          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>59.99</v>
+        <v>119.99</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-m100-studio-monitor-headphones</t>
+          <t>https://fr.donnermusic.com/products/donner-duet-adjustable-height-piano-bench-with-music-storage-black</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>229.99</v>
+        <v>303.99</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>319.99</v>
+        <v>303.99</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
+          <t>Donner Banquette Piano Duo Réglable Confort</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>319.99</v>
+        <v>115.99</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench-brown-matt</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano</t>
+          <t>Donner M100 Casque de monitoring studio</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>169.99</v>
+        <v>59.99</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/donner-m100-studio-monitor-headphones</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
+          <t>Donner DEP-08 Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>259.99</v>
+        <v>229.99</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>269.99</v>
+        <v>319.99</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>367.99</v>
+        <v>319.99</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>299.99</v>
+        <v>169.99</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -3858,11 +3858,11 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>【Offre spéciale mi-mois】Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>392.99</v>
+        <v>259.99</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -3873,236 +3873,236 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>199.99</v>
+        <v>269.99</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70 + MH1 Casque + Plateau pour batterie</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>284.99</v>
+        <v>367.99</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Noir</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>219.99</v>
+        <v>299.99</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Blanc</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>219.99</v>
+        <v>392.99</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - L1</t>
+          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>279.99</v>
+        <v>199.99</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70 + MH1 Casque + Plateau pour batterie</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>119.99</v>
+        <v>284.99</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - Pack</t>
+          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Noir</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>399.98</v>
+        <v>219.99</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Blanc</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>899.99</v>
+        <v>219.99</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
+          <t>Donner Essential L1 Synthétiseur - L1</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>899.99</v>
+        <v>279.99</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>899.99</v>
+        <v>119.99</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
+          <t>Donner Essential L1 Synthétiseur - Pack</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>102.99</v>
+        <v>399.98</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dkb-100-home-style-solid-wood-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>409.99</v>
+        <v>899.99</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>498.99</v>
+        <v>899.99</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>499.98</v>
+        <v>899.99</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
+          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>409.99</v>
+        <v>102.99</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/donner-dkb-100-home-style-solid-wood-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>498.99</v>
+        <v>409.99</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -4113,11 +4113,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>499.98</v>
+        <v>498.99</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -4128,11 +4128,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>399.99</v>
+        <v>499.98</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -4143,11 +4143,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>474.99</v>
+        <v>409.99</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -4158,11 +4158,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>499.98</v>
+        <v>498.99</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -4173,11 +4173,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>399.99</v>
+        <v>499.98</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -4188,11 +4188,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>498.99</v>
+        <v>399.99</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -4203,11 +4203,11 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>499.98</v>
+        <v>474.99</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -4218,67 +4218,67 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>899.99</v>
+        <v>499.98</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>899.99</v>
+        <v>399.99</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>899.99</v>
+        <v>498.99</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>899.99</v>
+        <v>499.98</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -4293,7 +4293,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -4308,82 +4308,82 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>109.99</v>
+        <v>899.99</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/pedale-de-delay-et-de-reverberation-donner-yellow-fall-ii</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>359.99</v>
+        <v>899.99</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>446.99</v>
+        <v>899.99</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>549.98</v>
+        <v>899.99</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>584.99</v>
+        <v>109.99</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/pedale-de-delay-et-de-reverberation-donner-yellow-fall-ii</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -4398,7 +4398,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -4413,7 +4413,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -4428,7 +4428,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -4443,116 +4443,116 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Donner DED-300X Batterie Electronique</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>539.99</v>
+        <v>359.99</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/batterie-electronique-donner-ded-300x-5-tambours-4-cymbales</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>129.99</v>
+        <v>446.99</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>129.99</v>
+        <v>549.98</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>685.99</v>
+        <v>584.99</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
+          <t>Donner DED-300X Batterie Electronique</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>769.99</v>
+        <v>539.99</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/batterie-electronique-donner-ded-300x-5-tambours-4-cymbales</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>749.99</v>
+        <v>129.99</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>839.99</v>
+        <v>129.99</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>819.99</v>
+        <v>685.99</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -4563,11 +4563,11 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>775.99</v>
+        <v>769.99</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -4578,11 +4578,11 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>779.99</v>
+        <v>749.99</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -4593,11 +4593,11 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>685.99</v>
+        <v>839.99</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -4608,11 +4608,11 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>769.99</v>
+        <v>819.99</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -4623,11 +4623,11 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>749.99</v>
+        <v>775.99</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -4638,11 +4638,11 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>839.99</v>
+        <v>779.99</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -4653,11 +4653,11 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>819.99</v>
+        <v>685.99</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -4668,11 +4668,11 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>775.99</v>
+        <v>769.99</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -4683,11 +4683,11 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>779.99</v>
+        <v>749.99</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -4698,251 +4698,251 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>102.99</v>
+        <v>839.99</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dkb-200-home-style-corrosion-resistant-metal-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>92.98999999999999</v>
+        <v>819.99</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>109.99</v>
+        <v>775.99</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>99</v>
+        <v>779.99</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/pedale-deffet-guitare-donner-triple-threat</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Donner DT-50 Tabouret de Batterie</t>
+          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>72.98999999999999</v>
+        <v>102.99</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/siege-de-batterie-mince-donner-dt-50-marron</t>
+          <t>https://fr.donnermusic.com/products/dkb-200-home-style-corrosion-resistant-metal-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Bleu</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>169.99</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>199.99</v>
+        <v>109.99</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Blanc</t>
+          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>169.99</v>
+        <v>99</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+          <t>https://fr.donnermusic.com/products/pedale-deffet-guitare-donner-triple-threat</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
+          <t>Donner DT-50 Tabouret de Batterie</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>289.99</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/siege-de-batterie-mince-donner-dt-50-marron</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
+          <t>Donner DST-550 Guitare Électrique - Bleu</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>379.99</v>
+        <v>169.99</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
+          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>279.99</v>
+        <v>199.99</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
+          <t>Donner DST-550 Guitare Électrique - Blanc</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>379.99</v>
+        <v>169.99</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>389.99</v>
+        <v>289.99</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>489.99</v>
+        <v>379.99</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>509.99</v>
+        <v>279.99</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>389.99</v>
+        <v>379.99</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>479.99</v>
+        <v>389.99</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -4953,11 +4953,11 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>509.99</v>
+        <v>489.99</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -4968,71 +4968,71 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>179.99</v>
+        <v>509.99</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>269.99</v>
+        <v>389.99</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>279.99</v>
+        <v>479.99</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>289.99</v>
+        <v>509.99</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>339.99</v>
+        <v>179.99</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -5043,11 +5043,11 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>349.99</v>
+        <v>269.99</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -5058,11 +5058,11 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>359.99</v>
+        <v>279.99</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -5073,11 +5073,11 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>295.99</v>
+        <v>289.99</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -5088,11 +5088,11 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>365.99</v>
+        <v>339.99</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -5103,11 +5103,11 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>209.99</v>
+        <v>349.99</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -5118,11 +5118,11 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>284.99</v>
+        <v>359.99</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -5133,11 +5133,11 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>315.99</v>
+        <v>295.99</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -5148,11 +5148,11 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>309.99</v>
+        <v>365.99</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -5163,11 +5163,11 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>359.99</v>
+        <v>209.99</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -5178,11 +5178,11 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>385.99</v>
+        <v>284.99</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -5193,11 +5193,11 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>379.99</v>
+        <v>315.99</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -5208,11 +5208,11 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>319.99</v>
+        <v>309.99</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -5223,11 +5223,11 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>389.99</v>
+        <v>359.99</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -5238,11 +5238,11 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>189.99</v>
+        <v>385.99</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -5253,11 +5253,11 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>269.99</v>
+        <v>379.99</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -5268,11 +5268,11 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>279.99</v>
+        <v>319.99</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -5283,11 +5283,11 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>282.99</v>
+        <v>389.99</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -5298,11 +5298,11 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>335.99</v>
+        <v>189.99</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -5313,11 +5313,11 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>343.99</v>
+        <v>269.99</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -5328,11 +5328,11 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>352.99</v>
+        <v>279.99</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -5343,11 +5343,11 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>285.99</v>
+        <v>282.99</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -5358,11 +5358,11 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>355.99</v>
+        <v>335.99</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -5373,11 +5373,11 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>209.99</v>
+        <v>343.99</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -5388,11 +5388,11 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>284.99</v>
+        <v>352.99</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -5403,11 +5403,11 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>315.99</v>
+        <v>285.99</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -5418,11 +5418,11 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>309.99</v>
+        <v>355.99</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -5433,11 +5433,11 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>359.99</v>
+        <v>209.99</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -5448,11 +5448,11 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>385.99</v>
+        <v>284.99</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -5463,11 +5463,11 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>379.99</v>
+        <v>315.99</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -5478,11 +5478,11 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>319.99</v>
+        <v>309.99</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -5493,11 +5493,11 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>389.99</v>
+        <v>359.99</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -5508,101 +5508,101 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>169.99</v>
+        <v>385.99</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>239.99</v>
+        <v>379.99</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>359.99</v>
+        <v>319.99</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>496.99</v>
+        <v>389.99</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>408.99</v>
+        <v>169.99</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>359.99</v>
+        <v>239.99</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>496.99</v>
+        <v>359.99</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -5613,11 +5613,11 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -5628,11 +5628,11 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>359.99</v>
+        <v>408.99</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -5643,11 +5643,11 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>496.99</v>
+        <v>359.99</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -5658,11 +5658,11 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -5673,11 +5673,11 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>359.99</v>
+        <v>408.99</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -5688,11 +5688,11 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>496.99</v>
+        <v>359.99</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -5703,11 +5703,11 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -5718,11 +5718,11 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>359.99</v>
+        <v>408.99</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -5733,11 +5733,11 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>496.99</v>
+        <v>359.99</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -5748,11 +5748,11 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -5763,11 +5763,11 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>359.99</v>
+        <v>408.99</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -5778,11 +5778,11 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>496.99</v>
+        <v>359.99</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -5793,11 +5793,11 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>408.99</v>
+        <v>496.99</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -5808,191 +5808,191 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Donner DED-200 Max Batteries Electroniques</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>499.99</v>
+        <v>408.99</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-200-max-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>1099.99</v>
+        <v>359.99</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>1114.99</v>
+        <v>496.99</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>899</v>
+        <v>408.99</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
+          <t>Donner DED-200 Max Batteries Electroniques</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>899</v>
+        <v>499.99</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-max-batteries-electroniques</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>899</v>
+        <v>1099.99</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>125.99</v>
+        <v>1114.99</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>166.99</v>
+        <v>899</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>299.99</v>
+        <v>899</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>486.99</v>
+        <v>899</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>398.99</v>
+        <v>125.99</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>299.99</v>
+        <v>166.99</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>486.99</v>
+        <v>299.99</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -6003,11 +6003,11 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>398.99</v>
+        <v>486.99</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -6018,11 +6018,11 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>299.99</v>
+        <v>398.99</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -6033,11 +6033,11 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>486.99</v>
+        <v>299.99</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -6048,11 +6048,11 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>398.99</v>
+        <v>486.99</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -6063,11 +6063,11 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>299.99</v>
+        <v>398.99</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -6078,11 +6078,11 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>486.99</v>
+        <v>299.99</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -6093,11 +6093,11 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>398.99</v>
+        <v>486.99</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -6108,86 +6108,86 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>109.99</v>
+        <v>398.99</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-banquette-de-piano-en-bois-massif-avec-espace-de-rangement</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>319.99</v>
+        <v>299.99</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>408.99</v>
+        <v>486.99</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>419.99</v>
+        <v>398.99</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>419.99</v>
+        <v>109.99</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-banquette-de-piano-en-bois-massif-avec-espace-de-rangement</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>435.99</v>
+        <v>319.99</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -6198,11 +6198,11 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>489.99</v>
+        <v>408.99</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -6213,11 +6213,11 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>439.99</v>
+        <v>419.99</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -6228,11 +6228,11 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>509.99</v>
+        <v>419.99</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -6243,11 +6243,11 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>439.99</v>
+        <v>435.99</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -6258,11 +6258,11 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>329.99</v>
+        <v>489.99</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -6273,11 +6273,11 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>418.99</v>
+        <v>439.99</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -6288,11 +6288,11 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>429.99</v>
+        <v>509.99</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
@@ -6303,11 +6303,11 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>429.99</v>
+        <v>439.99</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -6318,11 +6318,11 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>445.99</v>
+        <v>329.99</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -6333,11 +6333,11 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>499.99</v>
+        <v>418.99</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
@@ -6348,11 +6348,11 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>449.99</v>
+        <v>429.99</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -6363,11 +6363,11 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>519.99</v>
+        <v>429.99</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -6378,11 +6378,11 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>449.99</v>
+        <v>445.99</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -6401,63 +6401,63 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>599.99</v>
+        <v>449.99</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>609.99</v>
+        <v>519.99</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>686.99</v>
+        <v>449.99</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>696.99</v>
+        <v>499.99</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -6468,11 +6468,11 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>615.99</v>
+        <v>599.99</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
@@ -6483,11 +6483,11 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>685.99</v>
+        <v>609.99</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -6498,11 +6498,11 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>619.99</v>
+        <v>686.99</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -6513,11 +6513,11 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>689.99</v>
+        <v>696.99</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
@@ -6528,11 +6528,11 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>619.99</v>
+        <v>615.99</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
@@ -6543,71 +6543,71 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>629.99</v>
+        <v>685.99</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>729.99</v>
+        <v>619.99</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>816.99</v>
+        <v>689.99</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>719.99</v>
+        <v>619.99</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>749.99</v>
+        <v>629.99</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
@@ -6618,11 +6618,11 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>749.99</v>
+        <v>729.99</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
@@ -6633,11 +6633,11 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>761.99</v>
+        <v>816.99</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
@@ -6648,11 +6648,11 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>851.99</v>
+        <v>719.99</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -6663,11 +6663,11 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>927.99</v>
+        <v>749.99</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -6678,11 +6678,11 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>840.99</v>
+        <v>749.99</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -6693,11 +6693,11 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>977.99</v>
+        <v>761.99</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
@@ -6708,71 +6708,71 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>629.99</v>
+        <v>851.99</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>729.99</v>
+        <v>927.99</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>816.99</v>
+        <v>840.99</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>745.99</v>
+        <v>977.99</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>815.99</v>
+        <v>629.99</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
@@ -6783,11 +6783,11 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>749.99</v>
+        <v>729.99</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
@@ -6798,11 +6798,11 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>819.99</v>
+        <v>816.99</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -6813,11 +6813,11 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>559.99</v>
+        <v>745.99</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -6828,11 +6828,11 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>659.99</v>
+        <v>815.99</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -6843,11 +6843,11 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>746.99</v>
+        <v>749.99</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -6858,11 +6858,11 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>675.99</v>
+        <v>819.99</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -6873,11 +6873,11 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>745.99</v>
+        <v>559.99</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -6888,11 +6888,11 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>679.99</v>
+        <v>659.99</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -6903,11 +6903,11 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>749.99</v>
+        <v>746.99</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -6918,131 +6918,131 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>186.99</v>
+        <v>675.99</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-arena-2000</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>99.98999999999999</v>
+        <v>745.99</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>99.98999999999999</v>
+        <v>679.99</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Donner DMK-25 Pro Clavier MIDI</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>89.98999999999999</v>
+        <v>749.99</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dmk-25-pro-midi-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
+          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>236.99</v>
+        <v>186.99</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-arena-2000</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>335.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>423.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
+          <t>Donner DMK-25 Pro Clavier MIDI</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>219.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-dmk-25-pro-midi-keyboard</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>335.99</v>
+        <v>236.99</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -7053,11 +7053,11 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>423.99</v>
+        <v>335.99</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -7068,11 +7068,11 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>281.99</v>
+        <v>423.99</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -7083,11 +7083,11 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>373.99</v>
+        <v>219.99</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
@@ -7098,11 +7098,11 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>530.99</v>
+        <v>335.99</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -7113,112 +7113,112 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>89</v>
+        <v>423.99</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-b1-syn-the-ti-seurs-sequencer</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>109.99</v>
+        <v>281.99</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/banc-de-piano-tabouret-en-bois-dur-et-solide</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Pour la différence de prix</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>30</v>
+        <v>373.99</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/for-the-price-difference</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>152.99</v>
+        <v>530.99</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
+          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>339.99</v>
+        <v>89</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-b1-syn-the-ti-seurs-sequencer</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>152.99</v>
+        <v>109.99</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/banc-de-piano-tabouret-en-bois-dur-et-solide</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Pour la différence de prix</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>339.99</v>
+        <v>30</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/for-the-price-difference</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -7233,7 +7233,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -7248,7 +7248,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -7263,7 +7263,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -7278,101 +7278,101 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>86.98999999999999</v>
+        <v>152.99</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>69.98999999999999</v>
+        <v>339.99</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>389.99</v>
+        <v>152.99</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>479.99</v>
+        <v>339.99</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>479.99</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>489.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
+          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>509.99</v>
+        <v>389.99</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
@@ -7383,11 +7383,11 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>389.99</v>
+        <v>479.99</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -7413,11 +7413,11 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>479.99</v>
+        <v>489.99</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
@@ -7428,11 +7428,11 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>489.99</v>
+        <v>509.99</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
@@ -7443,11 +7443,11 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>509.99</v>
+        <v>389.99</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
@@ -7458,116 +7458,116 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>89.98999999999999</v>
+        <v>479.99</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>79.47</v>
+        <v>479.99</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>89.98999999999999</v>
+        <v>489.99</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-piano-bench-keyboard-stool-solid-hard-wooden-digital-piano-stool-with-large-storage-black</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>469.99</v>
+        <v>509.99</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>518.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>566.99</v>
+        <v>79.47</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>557.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+          <t>https://fr.donnermusic.com/products/donner-piano-bench-keyboard-stool-solid-hard-wooden-digital-piano-stool-with-large-storage-black</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>636.99</v>
+        <v>469.99</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
@@ -7578,11 +7578,11 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>627.99</v>
+        <v>518.99</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
@@ -7593,11 +7593,11 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>549.99</v>
+        <v>566.99</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
@@ -7608,11 +7608,11 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>569.99</v>
+        <v>557.99</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
@@ -7623,11 +7623,11 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>629.99</v>
+        <v>636.99</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
@@ -7638,11 +7638,11 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>585.99</v>
+        <v>627.99</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
@@ -7653,11 +7653,11 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>645.99</v>
+        <v>549.99</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
@@ -7668,11 +7668,11 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>589.99</v>
+        <v>569.99</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
@@ -7683,11 +7683,11 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>429.99</v>
+        <v>629.99</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
@@ -7698,11 +7698,11 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>536.99</v>
+        <v>585.99</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
@@ -7713,11 +7713,11 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>527.99</v>
+        <v>645.99</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
@@ -7728,11 +7728,11 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>606.99</v>
+        <v>589.99</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
@@ -7743,11 +7743,11 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>597.99</v>
+        <v>429.99</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
@@ -7758,11 +7758,11 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>519.99</v>
+        <v>536.99</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
@@ -7773,11 +7773,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>539.99</v>
+        <v>527.99</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
@@ -7788,11 +7788,11 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>599.99</v>
+        <v>606.99</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
@@ -7803,11 +7803,11 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>555.99</v>
+        <v>597.99</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
@@ -7818,11 +7818,11 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>615.99</v>
+        <v>519.99</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
@@ -7833,11 +7833,11 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>549.99</v>
+        <v>539.99</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
@@ -7848,11 +7848,11 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>559.98</v>
+        <v>599.99</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
@@ -7863,11 +7863,11 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>469.99</v>
+        <v>555.99</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
@@ -7878,11 +7878,11 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>518.99</v>
+        <v>615.99</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
@@ -7893,11 +7893,11 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>566.99</v>
+        <v>549.99</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
@@ -7908,11 +7908,11 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>557.99</v>
+        <v>559.98</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
@@ -7923,11 +7923,11 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>636.99</v>
+        <v>469.99</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
@@ -7938,11 +7938,11 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>627.99</v>
+        <v>518.99</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
@@ -7953,11 +7953,11 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>549.99</v>
+        <v>566.99</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
@@ -7968,11 +7968,11 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>569.99</v>
+        <v>557.99</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
@@ -7983,11 +7983,11 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>629.99</v>
+        <v>636.99</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
@@ -7998,11 +7998,11 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>585.99</v>
+        <v>627.99</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
@@ -8013,11 +8013,11 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>645.99</v>
+        <v>549.99</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
@@ -8028,11 +8028,11 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>589.99</v>
+        <v>569.99</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
@@ -8043,11 +8043,11 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>429.99</v>
+        <v>629.99</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
@@ -8058,11 +8058,11 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>499.99</v>
+        <v>585.99</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
@@ -8073,11 +8073,11 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>536.99</v>
+        <v>645.99</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
@@ -8088,11 +8088,11 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>527.99</v>
+        <v>589.99</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
@@ -8103,11 +8103,11 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / DDP-80</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>606.99</v>
+        <v>429.99</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
@@ -8118,11 +8118,11 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>597.99</v>
+        <v>499.99</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
@@ -8133,11 +8133,11 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>519.99</v>
+        <v>536.99</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
@@ -8148,11 +8148,11 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>539.99</v>
+        <v>527.99</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
@@ -8163,11 +8163,11 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>599.99</v>
+        <v>606.99</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
@@ -8178,11 +8178,11 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>555.99</v>
+        <v>597.99</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
@@ -8193,11 +8193,11 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>615.99</v>
+        <v>519.99</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
@@ -8208,13 +8208,73 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>539.99</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>599.99</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>555.99</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>615.99</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
           <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
-      <c r="B519" t="n">
+      <c r="B523" t="n">
         <v>549.99</v>
       </c>
-      <c r="C519" t="inlineStr">
+      <c r="C523" t="inlineStr">
         <is>
           <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>

--- a/Prix_Donner_TTC.xlsx
+++ b/Prix_Donner_TTC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C523"/>
+  <dimension ref="A1:C473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1053,2212 +1053,2212 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - L1</t>
+          <t>Donner DED-100 Batterie électrique</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>199.99</v>
+        <v>399.99</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-100-drum-set</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>119.99</v>
+        <v>219.99</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner Essential L1 Synthétiseur - Pack</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>319.99</v>
+        <v>329.98</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-essential-l1-synthetiseur</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>259.99</v>
+        <v>329.98</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>459.99</v>
+        <v>359.98</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - naturel / Guitare + JW Pédale</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>358.99</v>
+        <v>319.98</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>259.99</v>
+        <v>399.97</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir + Tourneur de Page</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>459.99</v>
+        <v>399.97</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>358.99</v>
+        <v>429.97</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare</t>
+          <t>【Boîte ouverte】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>259.99</v>
+        <v>699.99</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s300-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>459.99</v>
+        <v>769.99</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>358.99</v>
+        <v>849.98</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>259.99</v>
+        <v>849.98</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>459.99</v>
+        <v>875.98</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH X Guitare Électrique - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + DKB-100 Banc De Piano</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>358.99</v>
+        <v>869.98</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-x-guitare-electrique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DED-200Max Batteries Electroniques</t>
+          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>429.99</v>
+        <v>885.98</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ded-200max-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>259.99</v>
+        <v>1099.99</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>259.99</v>
+        <v>1169.99</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>749.99</v>
+        <v>209.99</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>852.99</v>
+        <v>479.99</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S300 Piano Numérique - Piano+Banc</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>839.99</v>
+        <v>388.99</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s300-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>369.99</v>
+        <v>209.99</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + noir</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>459.99</v>
+        <v>479.99</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>472.99</v>
+        <v>388.99</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>489.99</v>
+        <v>209.99</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>369.99</v>
+        <v>479.99</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + noir</t>
+          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>469.99</v>
+        <v>388.99</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>Donner Pupitre de batterie</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>472.99</v>
+        <v>39.99</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-drum-music-stand</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner OURA S100 Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Acajou</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>489.99</v>
+        <v>159.99</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-oura™-s100-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - DDP-80 PLUS Piano</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Noir</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>499.99</v>
+        <v>159.99</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Sunburst</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>599.99</v>
+        <v>159.99</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner DDP-80 PLUS Piano Numérique - Piano + Banc de Piano</t>
+          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>609.99</v>
+        <v>229.99</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>309.99</v>
+        <v>259.99</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>408.99</v>
+        <v>239.99</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>509.99</v>
+        <v>239.99</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>309.99</v>
+        <v>239.99</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>408.99</v>
+        <v>259.99</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>509.99</v>
+        <v>259.99</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>309.99</v>
+        <v>259.99</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DAM1000 Audio Mixer</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>408.99</v>
+        <v>179.99</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-dam1000-audio-mixer</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>509.99</v>
+        <v>599.99</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>309.99</v>
+        <v>669.99</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston + Pied</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>408.99</v>
+        <v>165.99</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>509.99</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare</t>
+          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Pied</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>309.99</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner Go Ampli Guitare - Donner Go【Noir】</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>408.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>Donner Go Ampli Guitare - Donner Go【Jaune】</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>509.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare</t>
+          <t>Donner Go Ampli Guitare - Donner Go II【Noir】</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>309.99</v>
+        <v>129.99</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner Go Ampli Guitare - Donner Go II【Blanc】</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>408.99</v>
+        <v>129.99</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>【Offre exclusive】Donner HUSH I PRO Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>509.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/offre-exclusive-donner-hush-i-pro-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/starrycrtl-midi-controller-black</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Donner DED-100 Batterie électrique</t>
+          <t>【Donner】Pour la différence de prix</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>399.99</v>
+        <v>180</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-100-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-pour-la-difference-de-prix</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>219.99</v>
+        <v>459.99</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>329.98</v>
+        <v>529.99</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>329.98</v>
+        <v>549.99</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>359.98</v>
+        <v>569.99</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Tourneur de Page</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>319.98</v>
+        <v>399.99</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>399.97</v>
+        <v>485.99</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Banc de Piano Noir + Tourneur de Page</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>399.97</v>
+        <v>489.99</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Donner DEP-07  Piano numérique portable semi-lesté à 88 touches - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>429.97</v>
+        <v>509.99</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-07-88-key-semi-weighted-portable-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>699.99</v>
+        <v>159.99</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s300-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-cv-3-wireless-in-ear-monitoring-system</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>769.99</v>
+        <v>209.99</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Noir</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>849.98</v>
+        <v>209.99</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc réglable X-Style</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>849.98</v>
+        <v>209.99</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Banc de Piano Marron</t>
+          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>875.98</v>
+        <v>209.99</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + DKB-100 Banc De Piano</t>
+          <t>Donner DED-200X Batterie Électronique【Version mise à niveau disponible】 - DED-200X Mise à niveau</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>869.98</v>
+        <v>599.99</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Donner DDP-300 Piano numérique à clavier lesté (version améliorée) - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DED-200X Batterie Électronique【Version mise à niveau disponible】 - DED-200X</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>885.98</v>
+        <v>499.99</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-300-fully-weighted-home-digital-piano-upgraded-version</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro</t>
+          <t>Donner Beat Go Kit de batterie électronique portable</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1099.99</v>
+        <v>289.99</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-beat-go-portable-electronic-drum-kit</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Donner BackBeat Pro Batterie électronique - BackBeat Pro + Tabouret de batterie DT-50</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1169.99</v>
+        <v>119.99</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-pro-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare</t>
+          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>209.99</v>
+        <v>119.99</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner Table de percussion</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>479.99</v>
+        <v>39.99</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/donner-percussion-table</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Sunburst / Guitare + JW Pédale</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>388.99</v>
+        <v>599.99</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>209.99</v>
+        <v>699.99</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>479.99</v>
+        <v>699.99</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - Noir / Guitare + JW Pédale</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>388.99</v>
+        <v>599.99</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>209.99</v>
+        <v>699.99</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + Arena 2000 Pédale</t>
+          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>479.99</v>
+        <v>699.99</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Donner HUSH I EVO2 Guitare de Voyage Ultra-Légère - couleur bois naturel / Guitare + JW Pédale</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Bleu clair</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>388.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-silent-guitar-mahogany</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Donner Pupitre de batterie</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Rose clair</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>39.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-drum-music-stand</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Acajou</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Bleu clair</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>159.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Noir</t>
+          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Rose clair</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>159.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I Guitare de Voyage Ultra-Légère - Sunburst</t>
+          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>159.99</v>
+        <v>269.99</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush-i-guitare</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-70l-electronic-drum-kit-with-led-light</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>229.99</v>
+        <v>149.99</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/donner-starrykey-37-play-midi-controller</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>259.99</v>
+        <v>129.99</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-c-guitare-nylon-voyage-electro-acoustique</t>
+          <t>https://fr.donnermusic.com/products/donner-dda-20se-drum-monitor-speaker</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>239.99</v>
+        <v>329.99</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>239.99</v>
+        <v>419.99</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>239.99</v>
+        <v>419.99</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>259.99</v>
+        <v>432.99</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>259.99</v>
+        <v>489.99</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>259.99</v>
+        <v>489.99</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-i-pro-electro-acoustique-guitare-voyageuse</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Donner DAM1000 Audio Mixer</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>179.99</v>
+        <v>502.99</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dam1000-audio-mixer</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro</t>
+          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>599.99</v>
+        <v>449.99</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Donner DED-200 Pro Batterie électronique - DED-200Pro + Tabouret de batterie DT-50</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>669.99</v>
+        <v>829.99</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ded-200pro-new-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston + Pied</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>165.99</v>
+        <v>909.99</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Contrôleur de cymbale Charleston</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>72.98999999999999</v>
+        <v>925.99</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Donner HHCB-12 Contrôleur de cymbale Charleston 12'' + Pied - Pied</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>92.98999999999999</v>
+        <v>899.99</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hhcb-12-separater-hi-hat</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Donner Go Ampli Guitare - Donner Go【Noir】</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>89.98999999999999</v>
+        <v>979.99</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Donner Go Ampli Guitare - Donner Go【Jaune】</t>
+          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>89.98999999999999</v>
+        <v>999.99</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Donner Go Ampli Guitare - Donner Go II【Noir】</t>
+          <t>Eastar EDA-100 Digital Aerophone Noir</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>129.99</v>
+        <v>119.99</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+          <t>https://fr.donnermusic.com/products/eastar-digital-aerophone-eda-100-noir</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Donner Go Ampli Guitare - Donner Go II【Blanc】</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>129.99</v>
+        <v>279.99</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-go-electric-guitar-amplifier-black</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Donner Starryctrl Contrôleur MIDI, Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>69.98999999999999</v>
+        <v>322.99</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/starrycrtl-midi-controller-black</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>【Donner】Pour la différence de prix</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>180</v>
+        <v>418.99</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-pour-la-difference-de-prix</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>459.99</v>
+        <v>419.98</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>529.99</v>
+        <v>369.98</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>549.99</v>
+        <v>369.98</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>569.99</v>
+        <v>299.99</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>399.99</v>
+        <v>341.99</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>485.99</v>
+        <v>398.99</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>489.99</v>
+        <v>399.98</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>509.99</v>
+        <v>352.98</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-s100-domestique-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Donner CV-3 Système de monitoring intra-auriculaire sans fil</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>159.99</v>
+        <v>352.98</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-cv-3-wireless-in-ear-monitoring-system</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Sunburst</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>209.99</v>
+        <v>279.99</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - naturel</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>209.99</v>
+        <v>322.99</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Noir</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>209.99</v>
+        <v>418.99</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner HUSH X Guitare Électrique Sans Tête - Blanc</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>209.99</v>
+        <v>419.98</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-hush™-x-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique【Version mise à niveau disponible】 - DED-200X Mise à niveau</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>599.99</v>
+        <v>369.98</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Donner DED-200X Batterie Électronique【Version mise à niveau disponible】 - DED-200X</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>499.99</v>
+        <v>369.98</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-200-set-de-batterie-electronique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Donner Beat Go Kit de batterie électronique portable</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>289.99</v>
+        <v>299.99</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-beat-go-portable-electronic-drum-kit</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Blanc mat</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + MH1 Casque</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>119.99</v>
+        <v>341.99</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Donner Tabouret De Piano À Hauteur Réglable - Beige mat</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>119.99</v>
+        <v>398.99</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Donner Table de percussion</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>39.99</v>
+        <v>399.98</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-percussion-table</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>599.99</v>
+        <v>352.98</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>699.99</v>
+        <v>352.98</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>699.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dks-200-heavy-duty-keyboard-stand-black</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>599.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-pocket-go-portable-preset-pedal-multi-effects-processor-for-guitar</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>699.99</v>
+        <v>126.99</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-mamp2-2-channel-amplifier</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>699.99</v>
+        <v>62.99</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/boite-ouverte-donner-oura™-r300-professionnel-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/starrypad-mini-midi-controller</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Bleu clair</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>69.98999999999999</v>
+        <v>59.99</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 32 Touches Rose clair</t>
+          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>69.98999999999999</v>
+        <v>56.99</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Bleu clair</t>
+          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>89.98999999999999</v>
+        <v>119.99</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/donner-duet-adjustable-height-piano-bench-with-music-storage-black</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>【Déstockage】Eastar KIDO Miniature Clavier pour enfant - 44 Touches avec Support Rose clair</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>89.98999999999999</v>
+        <v>303.99</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-kido-v-10-mini-digital-keyboard-32-keys</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Donner DED-70L Batterie électronique Avec Lumière LED</t>
+          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>269.99</v>
+        <v>303.99</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-70l-electronic-drum-kit-with-led-light</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Donner Starrykey-37 Play Contrôleur MIDI</t>
+          <t>Donner Banquette Piano Duo Réglable Confort</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>149.99</v>
+        <v>115.99</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-starrykey-37-play-midi-controller</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench-brown-matt</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Donner DDA-20SE Enceinte de monitoring de batterie</t>
+          <t>Donner M100 Casque de monitoring studio</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>129.99</v>
+        <v>59.99</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dda-20se-drum-monitor-speaker</t>
+          <t>https://fr.donnermusic.com/products/donner-m100-studio-monitor-headphones</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano</t>
+          <t>Donner DEP-08 Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>329.99</v>
+        <v>229.99</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>419.99</v>
+        <v>319.99</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>419.99</v>
+        <v>319.99</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>432.99</v>
+        <v>169.99</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco de Piano Noir + Tourneur de Page</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>489.99</v>
+        <v>259.99</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>489.99</v>
+        <v>269.99</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Banco + Tourneur de Page</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>502.99</v>
+        <v>367.99</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Donner DDP-50 88 touches Lestées Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>449.99</v>
+        <v>299.99</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-50-88-touches-piano-numerique-leste</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - DDP-400 Piano</t>
+          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>829.99</v>
+        <v>392.99</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano</t>
+          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>909.99</v>
+        <v>199.99</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc</t>
+          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70 + MH1 Casque + Plateau pour batterie</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>925.99</v>
+        <v>284.99</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Tourneur de Page</t>
+          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Noir</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>899.99</v>
+        <v>219.99</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Blanc</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>979.99</v>
+        <v>219.99</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Donner DDP-400 Piano Numérique à Touches Pondérées - Piano + Banc de Piano Blanc + Tourneur de Page</t>
+          <t>Donner Essential L1 Synthétiseur - L1</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>999.99</v>
+        <v>279.99</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-400-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Eastar EDA-100 Digital Aerophone Noir</t>
+          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -3266,5015 +3266,4265 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/eastar-digital-aerophone-eda-100-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare</t>
+          <t>Donner Essential L1 Synthétiseur - Pack</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>279.99</v>
+        <v>399.98</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + MH1 Casque</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>322.99</v>
+        <v>899.99</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + JW Pédale</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>418.99</v>
+        <v>899.99</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + Pocket Go Pédale</t>
+          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>419.98</v>
+        <v>899.99</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>369.98</v>
+        <v>102.99</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-dkb-100-home-style-solid-wood-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Bois naturel / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>369.98</v>
+        <v>409.99</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>299.99</v>
+        <v>498.99</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + MH1 Casque</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>341.99</v>
+        <v>499.98</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>398.99</v>
+        <v>409.99</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>399.98</v>
+        <v>498.99</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>352.98</v>
+        <v>499.98</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Rouge métallisé / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>352.98</v>
+        <v>399.99</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>279.99</v>
+        <v>474.99</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + MH1 Casque</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>322.99</v>
+        <v>499.98</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + JW Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>418.99</v>
+        <v>399.99</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>419.98</v>
+        <v>498.99</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Noir</t>
+          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>369.98</v>
+        <v>499.98</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Blanc / Guitare + DBM-100 Métronome Jaune</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>369.98</v>
+        <v>899.99</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>299.99</v>
+        <v>899.99</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + MH1 Casque</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>341.99</v>
+        <v>899.99</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + JW Pédale</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>398.99</v>
+        <v>899.99</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + Pocket Go Pédale</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>399.98</v>
+        <v>899.99</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Noir</t>
+          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>352.98</v>
+        <v>899.99</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Donner HLX-500 Guitare Électrique Moderne Sans Tête【ancienne réf. NHL-500】 - Sherwood Green / Guitare + DBM-100 Métronome Jaune</t>
+          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>352.98</v>
+        <v>109.99</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hlx-500-guitare-electrique-sans-tete</t>
+          <t>https://fr.donnermusic.com/products/pedale-de-delay-et-de-reverberation-donner-yellow-fall-ii</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Donner DKS-200 Pied Réglable Pliable Pour Clavier Noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>99.98999999999999</v>
+        <v>359.99</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dks-200-heavy-duty-keyboard-stand-black</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Donner Pocket Go Pédale Portable Multi Effets Guitare</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>99.98999999999999</v>
+        <v>446.99</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-pocket-go-portable-preset-pedal-multi-effects-processor-for-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Donner MAMP2 Puissant Amplificateur 2 Canaux</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>126.99</v>
+        <v>549.98</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-mamp2-2-channel-amplifier</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Donner Starrypad Mini-Contrôleur MIDI</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>62.99</v>
+        <v>584.99</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/starrypad-mini-midi-controller</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Noir</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>59.99</v>
+        <v>359.99</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Donner DBM-100 Métronome Accordeur 3-en-1 Rechargeable - Jaune</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>56.99</v>
+        <v>446.99</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dbm-100-metronome</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable avec Rangement</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>119.99</v>
+        <v>549.98</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-duet-adjustable-height-piano-bench-with-music-storage-black</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Sunburst</t>
+          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>303.99</v>
+        <v>584.99</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Donner HUSH C Guitare Nylon Voyage Électro-Acoustique - Noir</t>
+          <t>Donner DED-300X Batterie Electronique</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>303.99</v>
+        <v>539.99</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-c-guitar</t>
+          <t>https://fr.donnermusic.com/products/batterie-electronique-donner-ded-300x-5-tambours-4-cymbales</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Donner Banquette Piano Duo Réglable Confort</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>115.99</v>
+        <v>129.99</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-adjustable-height-piano-bench-brown-matt</t>
+          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Donner M100 Casque de monitoring studio</t>
+          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>59.99</v>
+        <v>129.99</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-m100-studio-monitor-headphones</t>
+          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>229.99</v>
+        <v>685.99</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>319.99</v>
+        <v>769.99</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Donner DEP-08 Piano Numérique - Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>319.99</v>
+        <v>749.99</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dep-08-portable-set-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>169.99</v>
+        <v>839.99</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>259.99</v>
+        <v>819.99</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>269.99</v>
+        <v>775.99</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + Banc X-Style</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>367.99</v>
+        <v>779.99</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>299.99</v>
+        <v>685.99</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Donner DEP-1 Piano Numérique Portable - Piano + Support de clavier + banc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>392.99</v>
+        <v>769.99</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-donner-dep-1</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>199.99</v>
+        <v>749.99</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Donner DED-70 Batterie électronique adaptée aux adolescents - DED-70 + MH1 Casque + Plateau pour batterie</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>284.99</v>
+        <v>839.99</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-70-electronic-drum-set</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Noir</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>219.99</v>
+        <v>819.99</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Donner DED-80 Batterie électronique adaptée aux adolescents - Blanc</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>219.99</v>
+        <v>775.99</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/batterie-electrique-donner-ded-80-5-tambours-et-3-cymbales</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - L1</t>
+          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>279.99</v>
+        <v>779.99</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - KB-32M</t>
+          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>119.99</v>
+        <v>102.99</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+          <t>https://fr.donnermusic.com/products/dkb-200-home-style-corrosion-resistant-metal-piano-bench</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Donner Essential L1 Synthétiseur - Pack</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>399.98</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-essential-l1-synthesizer</t>
+          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc【Forfait officiel】</t>
+          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>899.99</v>
+        <v>109.99</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano+Banc</t>
+          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>899.99</v>
+        <v>99</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+          <t>https://fr.donnermusic.com/products/pedale-deffet-guitare-donner-triple-threat</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA S300 Domestique Piano Numérique - Piano</t>
+          <t>Donner DT-50 Tabouret de Batterie</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>899.99</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura™-s300-a-88-touches</t>
+          <t>https://fr.donnermusic.com/products/siege-de-batterie-mince-donner-dt-50-marron</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Donner OURA S100 Tabouret Bois Massif assorti (DKB-100)</t>
+          <t>Donner DST-550 Guitare Électrique - Bleu</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>102.99</v>
+        <v>169.99</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dkb-100-home-style-solid-wood-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare</t>
+          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>409.99</v>
+        <v>199.99</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + JW Pédale</t>
+          <t>Donner DST-550 Guitare Électrique - Blanc</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>498.99</v>
+        <v>169.99</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir Aurora / Guitare + Pocket Go Pédale</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>499.98</v>
+        <v>289.99</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>409.99</v>
+        <v>379.99</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + JW Pédale</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>498.99</v>
+        <v>279.99</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc-Or / Guitare + Pocket Go Pédale</t>
+          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>499.98</v>
+        <v>379.99</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>399.99</v>
+        <v>389.99</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + JW Pédale</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>474.99</v>
+        <v>489.99</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Blanc / Guitare + Pocket Go Pédale</t>
+          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>499.98</v>
+        <v>509.99</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>399.99</v>
+        <v>389.99</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + JW Pédale</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>498.99</v>
+        <v>479.99</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Donner HUSH X PRO Guitare Électrique - Noir / Guitare + Pocket Go Pédale</t>
+          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>499.98</v>
+        <v>509.99</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-pro-multi-effects-portable-guitar</t>
+          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>899.99</v>
+        <v>179.99</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>899.99</v>
+        <v>269.99</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Gris-brun / Piano + Banc【Pack Officiel】</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>899.99</v>
+        <v>279.99</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>899.99</v>
+        <v>289.99</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>899.99</v>
+        <v>339.99</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner OURA R300 Professionnel Piano Numérique - Bois clair / Piano + Banc【Pack Officiel】</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>899.99</v>
+        <v>349.99</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-oura™-r300-88-key-home-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Donner Yellow Fall II Pédale 2-en-1 Delay &amp; Reverb</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>109.99</v>
+        <v>359.99</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/pedale-de-delay-et-de-reverberation-donner-yellow-fall-ii</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>359.99</v>
+        <v>295.99</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + noir</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>446.99</v>
+        <v>365.99</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + banc (match officiel)</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>549.98</v>
+        <v>209.99</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>584.99</v>
+        <v>284.99</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>359.99</v>
+        <v>315.99</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + noir</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>446.99</v>
+        <v>309.99</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + banc (match officiel)</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>549.98</v>
+        <v>359.99</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>【Boîte ouverte】Donner OURA S100 Domestique Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>584.99</v>
+        <v>385.99</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-domestique-donner-oura-s100-88-touches-grain-de-chene-noir</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Donner DED-300X Batterie Electronique</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>539.99</v>
+        <v>379.99</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/batterie-electronique-donner-ded-300x-5-tambours-4-cymbales</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Noir</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>129.99</v>
+        <v>319.99</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Donner DST-80 Débutant Guitare Électrique - Sunburst</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>129.99</v>
+        <v>389.99</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/kit-de-guitare-electrique-donner-dst-80-39-pouces-mat-givre-st-avec-amplificateur</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>685.99</v>
+        <v>189.99</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>769.99</v>
+        <v>269.99</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>749.99</v>
+        <v>279.99</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>839.99</v>
+        <v>282.99</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>819.99</v>
+        <v>335.99</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>775.99</v>
+        <v>343.99</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Brun foncé / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>779.99</v>
+        <v>352.99</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>685.99</v>
+        <v>285.99</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>769.99</v>
+        <v>355.99</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>749.99</v>
+        <v>209.99</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + banc + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>839.99</v>
+        <v>284.99</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>819.99</v>
+        <v>315.99</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>775.99</v>
+        <v>309.99</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Donner DDP-200 PRO Pondéré à Marteau Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>779.99</v>
+        <v>359.99</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-pondere-a-clavier-marteau-88-touches-donner-ddp-200-pro-standard</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Donner OURA S300 Coussin Épais Banquette Piano (DKB-200 )</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>102.99</v>
+        <v>385.99</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dkb-200-home-style-corrosion-resistant-metal-piano-bench</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur bois clair</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>92.98999999999999</v>
+        <v>379.99</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Donner OURA R300 Tabouret assorti avec Coussin Épais (DKB-300) - couleur noyer</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>109.99</v>
+        <v>319.99</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/dkb-300-home-style-thick-padded-piano-bench-light-wood-color</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Donner Triple Threat 3-en-1 Pédale Guitare</t>
+          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>99</v>
+        <v>389.99</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/pedale-deffet-guitare-donner-triple-threat</t>
+          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Donner DT-50 Tabouret de Batterie</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>72.98999999999999</v>
+        <v>169.99</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/siege-de-batterie-mince-donner-dt-50-marron</t>
+          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Bleu</t>
+          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>169.99</v>
+        <v>239.99</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Littoral caribéen Gradation LR</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>199.99</v>
+        <v>359.99</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Donner DST-550 Guitare Électrique - Blanc</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>169.99</v>
+        <v>496.99</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/guitare-electrique-double-coupure-donner-dst-550-de-39-pouces-avec-pickup-hss-en-corps-en-epinette-solide</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>289.99</v>
+        <v>408.99</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Noir / Piano + Banc Noir</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>379.99</v>
+        <v>359.99</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>279.99</v>
+        <v>496.99</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Donner DEP-16S Piano Numérique en Acier Lesté - Rouge / Piano + Banc Noir</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>379.99</v>
+        <v>408.99</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-electrique-noir-donner-dep-16s-88-touches-en-acier-leste-avec-support</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>389.99</v>
+        <v>359.99</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + banc de piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>489.99</v>
+        <v>496.99</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>389.99</v>
+        <v>359.99</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + banc de piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>479.99</v>
+        <v>496.99</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Donner DDP-95 lesté Piano numérique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>509.99</v>
+        <v>408.99</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/piano-numerique-ddp-95-clavier-leste-a-88-touches-blanc</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>179.99</v>
+        <v>359.99</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>269.99</v>
+        <v>496.99</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>279.99</v>
+        <v>408.99</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>289.99</v>
+        <v>359.99</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>339.99</v>
+        <v>496.99</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>349.99</v>
+        <v>408.99</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DED-200 Max Batteries Electroniques</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>359.99</v>
+        <v>499.99</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-ded-200-max-batteries-electroniques</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>295.99</v>
+        <v>1099.99</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>365.99</v>
+        <v>1114.99</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>209.99</v>
+        <v>899</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>284.99</v>
+        <v>899</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron</t>
+          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>315.99</v>
+        <v>899</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>309.99</v>
+        <v>125.99</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>359.99</v>
+        <v>166.99</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>385.99</v>
+        <v>299.99</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>379.99</v>
+        <v>486.99</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>319.99</v>
+        <v>398.99</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois naturel【Nouvelle version】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>389.99</v>
+        <v>299.99</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>189.99</v>
+        <v>486.99</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>269.99</v>
+        <v>398.99</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>279.99</v>
+        <v>299.99</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>282.99</v>
+        <v>486.99</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>335.99</v>
+        <v>398.99</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>343.99</v>
+        <v>299.99</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>352.99</v>
+        <v>486.99</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc</t>
+          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>285.99</v>
+        <v>398.99</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - couleur bois clair / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>355.99</v>
+        <v>109.99</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-banquette-de-piano-en-bois-massif-avec-espace-de-rangement</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>209.99</v>
+        <v>319.99</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>284.99</v>
+        <v>408.99</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>315.99</v>
+        <v>419.99</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>309.99</v>
+        <v>419.99</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc réglable X-Style + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>359.99</v>
+        <v>435.99</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>385.99</v>
+        <v>489.99</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>379.99</v>
+        <v>439.99</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>319.99</v>
+        <v>509.99</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Donner DEP-1S Semi-Lesté De Style Bois Piano Numérique - brun antique / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>389.99</v>
+        <v>439.99</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dep-1s-piano-numerique-clavier-de-piano-semi-leste-de-style-bois</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>169.99</v>
+        <v>329.99</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Donner DP-10 Portable Pliable Piano Numerique - Piano + Banc</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>239.99</v>
+        <v>418.99</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dp-10-piano-electroniques-clavier-portable-pliable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>359.99</v>
+        <v>429.99</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>496.99</v>
+        <v>429.99</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Noir Space Fly / Guitare + JW Pédale</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>408.99</v>
+        <v>445.99</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>359.99</v>
+        <v>499.99</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>496.99</v>
+        <v>449.99</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Blanc / Guitare + JW Pédale</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>408.99</v>
+        <v>519.99</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare</t>
+          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>359.99</v>
+        <v>449.99</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>496.99</v>
+        <v>499.99</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Bleu Hawaï / Guitare + JW Pédale</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>408.99</v>
+        <v>599.99</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>359.99</v>
+        <v>609.99</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>496.99</v>
+        <v>686.99</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Marron Dégradé Maillard / Guitare + JW Pédale</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>408.99</v>
+        <v>696.99</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>359.99</v>
+        <v>615.99</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>496.99</v>
+        <v>685.99</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>408.99</v>
+        <v>619.99</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>359.99</v>
+        <v>689.99</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>496.99</v>
+        <v>619.99</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Donner HUSH I PRO Electro-Acoustique Guitare Voyageuse - Naturel / Guitare + JW Pédale</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>408.99</v>
+        <v>629.99</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-i-pro-guitare-modes-sonores-multiples-guitare-de-voyage-portable</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Donner DED-200 Max Batteries Electroniques</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>499.99</v>
+        <v>729.99</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ded-200-max-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>1099.99</v>
+        <v>816.99</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Donner BackBeat Batterie Electronique - BackBeat + Tabouret de batterie DT-50</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>1114.99</v>
+        <v>719.99</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-backbeat-batteries-electroniques</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano Marron</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>899</v>
+        <v>749.99</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - Piano + Banc de Piano</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>899</v>
+        <v>749.99</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>【Piano + banquette offerts】Donner DDP-80 Pro Rétro esthétique Piano Numérique - DDP-80 Pro Piano</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>899</v>
+        <v>761.99</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/ddp-80-pro-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought Cutaway</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>125.99</v>
+        <v>851.99</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Donner DAG-1CB Débutant Guitare Acoustique - Dreadnought</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>166.99</v>
+        <v>927.99</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-cutaway-acoustic-guitar-package-beginner-guitar-kit-41-inch-with-bag-tuner-capo-strap-strings-picks-sunburst-dag-1cs</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>299.99</v>
+        <v>840.99</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>486.99</v>
+        <v>977.99</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - naturel / Guitare + JW Pédale</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>398.99</v>
+        <v>629.99</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>299.99</v>
+        <v>729.99</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>486.99</v>
+        <v>816.99</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Sunburst / Guitare + JW Pédale</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>398.99</v>
+        <v>745.99</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>299.99</v>
+        <v>815.99</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>486.99</v>
+        <v>749.99</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Blanc / Guitare + JW Pédale</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>398.99</v>
+        <v>819.99</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>299.99</v>
+        <v>559.99</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>486.99</v>
+        <v>659.99</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Donner HUSH X Guitare Électrique Sans Tête - Noir / Guitare + JW Pédale</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>398.99</v>
+        <v>746.99</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-hush-x-guitare-electrique-guitare-de-voyage-ultra-legere</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>109.99</v>
+        <v>675.99</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-banquette-de-piano-en-bois-massif-avec-espace-de-rangement</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>319.99</v>
+        <v>745.99</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano bois clair</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>408.99</v>
+        <v>679.99</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Blanc</t>
+          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>419.99</v>
+        <v>749.99</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc de Piano Marron</t>
+          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>419.99</v>
+        <v>186.99</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-arena-2000</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>435.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>489.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DMK-25 Pro Clavier MIDI</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>439.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dmk-25-pro-midi-keyboard</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>509.99</v>
+        <v>236.99</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Bois clair / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>439.99</v>
+        <v>335.99</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>329.99</v>
+        <v>423.99</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano bois clair</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>418.99</v>
+        <v>219.99</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Blanc</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>429.99</v>
+        <v>335.99</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc de Piano Marron</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>429.99</v>
+        <v>423.99</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>445.99</v>
+        <v>281.99</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc réglable en hauteur + Tourneur de Page</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>499.99</v>
+        <v>373.99</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur</t>
+          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>449.99</v>
+        <v>530.99</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
+          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>519.99</v>
+        <v>89</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-b1-syn-the-ti-seurs-sequencer</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Donner DDP-60 Semi-lesté Piano Numérique - Gris-brun / Piano + Beige mat Banc réglable en hauteur</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>449.99</v>
+        <v>109.99</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-60-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/banc-de-piano-tabouret-en-bois-dur-et-solide</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - DDP-80 PLUS Piano</t>
+          <t>Pour la différence de prix</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>499.99</v>
+        <v>30</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/for-the-price-difference</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>599.99</v>
+        <v>152.99</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>609.99</v>
+        <v>339.99</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano Marron + Tourneur de Page</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>686.99</v>
+        <v>152.99</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>696.99</v>
+        <v>339.99</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>615.99</v>
+        <v>152.99</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Sunburst / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>685.99</v>
+        <v>339.99</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>619.99</v>
+        <v>152.99</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Noir / Guitare + Arena 2000 Pédale</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>689.99</v>
+        <v>339.99</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Donner DDP-80 PLUS Piano Numérique Avec Couvercle Semi-Ouvert - Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Noir</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>619.99</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-80-plus-piano-numerique</t>
+          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano numérique</t>
+          <t>Donner DBM-10 Bluetooth Auto  Sans Fil Page Turner Pédale - Argent</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>629.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-wireless-page-turner-pedal-rechargeable-sheet-music-reading-controller-for-tablets-ipad-black</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>729.99</v>
+        <v>389.99</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>816.99</v>
+        <v>479.99</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano +  Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>719.99</v>
+        <v>479.99</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>749.99</v>
+        <v>489.99</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Noir / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>749.99</v>
+        <v>509.99</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano numérique</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>761.99</v>
+        <v>389.99</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano blanc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Banc X-Style</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>851.99</v>
+        <v>479.99</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano noir</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>927.99</v>
+        <v>479.99</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano +  Tabouret de piano noir</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Tabouret de piano blanc</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>840.99</v>
+        <v>489.99</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Donner DDP-100 Vertical lesté Piano Numérique - Noir / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DEP-20 lestées Piano Numerique - Blanc / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>977.99</v>
+        <v>509.99</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-home-digital-piano-88-keys-piano-keyboard-bundle-with-furniture-stand-triple-pedals-for-beginners-hobbyists-ddp-100-black-1</t>
+          <t>https://fr.donnermusic.com/products/donner-digital-piano-keyboard-weighted-88-keys-with-piano-stand-beginner-electric-piano-with-furniture-stand-and-triple-pedal-real-piano-touch-dep-20s</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano Numérique</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*2.4pouces</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>629.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano</t>
+          <t>Donner Tabouret de piano en forme de X réglable en hauteur - 15.7*11.8*1.6pouces</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>729.99</v>
+        <v>79.47</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-adjustable-high-density-sponges-keyboard-bench-non-skid-design-x-style-bench-black</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner Bois Massif Banc Piano avec Rangement</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>816.99</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-piano-bench-keyboard-stool-solid-hard-wooden-digital-piano-stool-with-large-storage-black</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / DDP-80</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>745.99</v>
+        <v>469.99</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>815.99</v>
+        <v>518.99</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>749.99</v>
+        <v>566.99</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 MK2【Son amélioré】 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>819.99</v>
+        <v>557.99</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano Numérique</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>559.99</v>
+        <v>636.99</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>659.99</v>
+        <v>627.99</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Banc de Piano + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>746.99</v>
+        <v>549.99</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>675.99</v>
+        <v>569.99</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>745.99</v>
+        <v>629.99</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>679.99</v>
+        <v>585.99</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Donner DDP-200 MK2 Piano numérique avec mécanisme de marteau gradué - DDP-200 / Piano + Duo Höhenverstellbarer banc + Tourneur de Page</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>749.99</v>
+        <v>645.99</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-ddp-200-professional-88-key-weighted-dynamic-graded-hammer-action-upright-digital-piano</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Donner Arena 2000 Pédale Multi-Effets Guitare - Arena 2000</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Son amélioré / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>186.99</v>
+        <v>589.99</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-arena-2000</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Marron</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / DDP-80</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>99.98999999999999</v>
+        <v>429.99</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Donner DKB-10 Bois Massif Banc Piano avec Rangement - Blanc</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>99.98999999999999</v>
+        <v>536.99</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dkb-10-piano-bench-white</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Donner DMK-25 Pro Clavier MIDI</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>89.98999999999999</v>
+        <v>527.99</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dmk-25-pro-midi-keyboard</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>236.99</v>
+        <v>606.99</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + JW Pédale</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>335.99</v>
+        <v>597.99</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Rouge / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>423.99</v>
+        <v>519.99</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>219.99</v>
+        <v>539.99</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + JW Pédale</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>335.99</v>
+        <v>599.99</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Noir / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>423.99</v>
+        <v>555.99</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>281.99</v>
+        <v>615.99</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + JW Pédale</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Banc Duo réglable en hauteur + Tourneur de Page</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>373.99</v>
+        <v>549.99</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Donner DJP-1000 Guitare Jazz Demi-Caisse - Marron / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Bois naturel / Piano + Blanc mat Banc réglable en hauteur</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>530.99</v>
+        <v>559.98</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-djp-1000-guitare-electrique-jazz</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Donner Essential B1 Synthétiseur de basse analogique - B1</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / DDP-80</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>89</v>
+        <v>469.99</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-b1-syn-the-ti-seurs-sequencer</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Donner Bois Massif Banc Piano avec Rangement</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Casque audio M100</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>109.99</v>
+        <v>518.99</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/banc-de-piano-tabouret-en-bois-dur-et-solide</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Pour la différence de prix</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>30</v>
+        <v>566.99</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/for-the-price-difference</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>152.99</v>
+        <v>557.99</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Bleu / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano + Tourneur de Page</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>339.99</v>
+        <v>636.99</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Marron + Tourneur de Page</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>152.99</v>
+        <v>627.99</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.com/products/donner-dst-152</t>
+          <t>https://fr.donnermusic.com/products/donner-ddp-80-88-key-full-weighted-home-digital-piano-beautiful-wooden-style-with-three-pedals</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Donner DST-152 Guitare Électrique avec Ampli et Housse - Ivoire Blanc / Guitare + Arena 2000 Pédale</t>
+          <t>Donner DDP-80 Motif de Bois Piano Numérique - Noyer【Son amélioré】 / Piano + Banc de Piano Noir</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>339.99</v>
+        <v>549.99</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>https://fr.donnermusic.